--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6F78CAA-611D-49B8-AC50-4661A86692F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1C9F3FF-FC18-41C1-948A-A9A5D2CE8431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="1062">
   <si>
     <t>Id</t>
   </si>
@@ -3192,6 +3192,36 @@
   </si>
   <si>
     <t>ACCA lecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was interviewed by a highschool student from Downers Grove about sharks for their class project (arranged by communications) </t>
+  </si>
+  <si>
+    <t>TV interview</t>
+  </si>
+  <si>
+    <t>FOX 32 Chicago Live</t>
+  </si>
+  <si>
+    <t>NBC 5</t>
+  </si>
+  <si>
+    <t>WGN, John Landecker show</t>
+  </si>
+  <si>
+    <t>Field days: The number of days working in the field conducting research, collecting, animal rescue, etc. Only the trip lead needs to enter field days, and specify the number of Shedd members of the field team, including staff, interns, and volunteers.</t>
+  </si>
+  <si>
+    <t>After School Matters career chat</t>
+  </si>
+  <si>
+    <t>Presentation to artists for Shedd related work</t>
+  </si>
+  <si>
+    <t>Presented on Shedd coral research to the two artists and CPI. The artists are designing art for Shedd. Took them on a tour of R2 and the labs (short)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited seminar speaker at Northeastern Illinois University </t>
   </si>
 </sst>
 </file>
@@ -3227,14 +3257,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3314,8 +3343,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W705" totalsRowShown="0">
-  <autoFilter ref="A1:W705" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W713" totalsRowShown="0">
+  <autoFilter ref="A1:W713" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3509,7 +3538,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="711" latestEventMarker="747">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="719" latestEventMarker="755">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -3836,13 +3865,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W705"/>
+  <dimension ref="A1:W713"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="19" customWidth="1"/>
     <col min="12" max="13" width="20" bestFit="1" customWidth="1"/>
     <col min="14" max="18" width="19" customWidth="1"/>
+    <col min="21" max="21" width="62" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -31193,7 +31223,7 @@
       <c r="W704" s="3"/>
     </row>
     <row r="705" spans="1:23">
-      <c r="A705" s="6">
+      <c r="A705">
         <v>711</v>
       </c>
       <c r="B705" s="4">
@@ -31217,20 +31247,12 @@
       <c r="H705" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I705" s="6"/>
-      <c r="J705" s="6" t="s">
+      <c r="J705" t="s">
         <v>73</v>
       </c>
-      <c r="K705" s="6"/>
       <c r="L705" s="3"/>
       <c r="M705" s="3"/>
-      <c r="N705" s="6"/>
-      <c r="O705" s="6"/>
-      <c r="P705" s="6"/>
-      <c r="Q705" s="6"/>
-      <c r="R705" s="6"/>
-      <c r="S705" s="6"/>
-      <c r="T705" s="6">
+      <c r="T705">
         <v>20</v>
       </c>
       <c r="U705" s="3" t="s">
@@ -31240,6 +31262,332 @@
         <v>29</v>
       </c>
       <c r="W705" s="3"/>
+    </row>
+    <row r="706" spans="1:23">
+      <c r="A706">
+        <v>712</v>
+      </c>
+      <c r="B706" s="4">
+        <v>46133.623495370397</v>
+      </c>
+      <c r="C706" s="4">
+        <v>46133.628252314797</v>
+      </c>
+      <c r="D706" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E706" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G706" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H706" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J706" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L706" s="3"/>
+      <c r="M706" s="3"/>
+      <c r="T706">
+        <v>1</v>
+      </c>
+      <c r="U706" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="V706" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="W706" s="3"/>
+    </row>
+    <row r="707" spans="1:23">
+      <c r="A707">
+        <v>713</v>
+      </c>
+      <c r="B707" s="4">
+        <v>46134.582824074103</v>
+      </c>
+      <c r="C707" s="4">
+        <v>46134.5866550926</v>
+      </c>
+      <c r="D707" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E707" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G707" s="1">
+        <v>46122</v>
+      </c>
+      <c r="H707" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I707" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L707" s="3"/>
+      <c r="M707" s="3"/>
+      <c r="U707" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="V707" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W707" s="3"/>
+    </row>
+    <row r="708" spans="1:23">
+      <c r="A708">
+        <v>714</v>
+      </c>
+      <c r="B708" s="4">
+        <v>46134.586689814802</v>
+      </c>
+      <c r="C708" s="4">
+        <v>46134.5874189815</v>
+      </c>
+      <c r="D708" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E708" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G708" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H708" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I708" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L708" s="3"/>
+      <c r="M708" s="3"/>
+      <c r="U708" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="V708" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W708" s="3"/>
+    </row>
+    <row r="709" spans="1:23">
+      <c r="A709">
+        <v>715</v>
+      </c>
+      <c r="B709" s="4">
+        <v>46134.587442129603</v>
+      </c>
+      <c r="C709" s="4">
+        <v>46134.5878703704</v>
+      </c>
+      <c r="D709" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E709" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F709" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G709" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H709" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I709" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L709" s="3"/>
+      <c r="M709" s="3"/>
+      <c r="U709" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="V709" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W709" s="3"/>
+    </row>
+    <row r="710" spans="1:23">
+      <c r="A710">
+        <v>716</v>
+      </c>
+      <c r="B710" s="4">
+        <v>46134.587974536997</v>
+      </c>
+      <c r="C710" s="4">
+        <v>46134.589652777802</v>
+      </c>
+      <c r="D710" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E710" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F710" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G710" s="1">
+        <v>46142</v>
+      </c>
+      <c r="H710" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L710" s="3"/>
+      <c r="M710" s="3"/>
+      <c r="O710">
+        <v>2</v>
+      </c>
+      <c r="P710">
+        <v>0</v>
+      </c>
+      <c r="Q710">
+        <v>0</v>
+      </c>
+      <c r="R710">
+        <v>0</v>
+      </c>
+      <c r="T710">
+        <v>10</v>
+      </c>
+      <c r="U710" s="3"/>
+      <c r="V710" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W710" s="3"/>
+    </row>
+    <row r="711" spans="1:23">
+      <c r="A711">
+        <v>717</v>
+      </c>
+      <c r="B711" s="4">
+        <v>46134.590092592603</v>
+      </c>
+      <c r="C711" s="4">
+        <v>46134.590624999997</v>
+      </c>
+      <c r="D711" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E711" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G711" s="1">
+        <v>46120</v>
+      </c>
+      <c r="H711" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J711" t="s">
+        <v>73</v>
+      </c>
+      <c r="L711" s="3"/>
+      <c r="M711" s="3"/>
+      <c r="T711">
+        <v>10</v>
+      </c>
+      <c r="U711" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="V711" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W711" s="3"/>
+    </row>
+    <row r="712" spans="1:23">
+      <c r="A712">
+        <v>718</v>
+      </c>
+      <c r="B712" s="4">
+        <v>46136.457719907397</v>
+      </c>
+      <c r="C712" s="4">
+        <v>46136.458854166704</v>
+      </c>
+      <c r="D712" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E712" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G712" s="1">
+        <v>46135</v>
+      </c>
+      <c r="H712" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J712" t="s">
+        <v>1059</v>
+      </c>
+      <c r="L712" s="3"/>
+      <c r="M712" s="3"/>
+      <c r="T712">
+        <v>4</v>
+      </c>
+      <c r="U712" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="V712" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="W712" s="3"/>
+    </row>
+    <row r="713" spans="1:23">
+      <c r="A713">
+        <v>719</v>
+      </c>
+      <c r="B713" s="4">
+        <v>46136.458877314799</v>
+      </c>
+      <c r="C713" s="4">
+        <v>46136.459212962996</v>
+      </c>
+      <c r="D713" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E713" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G713" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H713" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J713" t="s">
+        <v>50</v>
+      </c>
+      <c r="L713" s="3"/>
+      <c r="M713" s="3"/>
+      <c r="T713">
+        <v>30</v>
+      </c>
+      <c r="U713" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="V713" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="W713" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1C9F3FF-FC18-41C1-948A-A9A5D2CE8431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A3237A7-DF2B-4F17-9BD3-50AAFFD0A373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="1088">
   <si>
     <t>Id</t>
   </si>
@@ -3222,6 +3222,84 @@
   </si>
   <si>
     <t xml:space="preserve">Invited seminar speaker at Northeastern Illinois University </t>
+  </si>
+  <si>
+    <t>Turtle Tales lunch and learn by Melissa, Austin, and Andy</t>
+  </si>
+  <si>
+    <t>Update from the Center for Species Survival: Freshwater</t>
+  </si>
+  <si>
+    <t>History of Bahamian Rock Iguana Research to the Bahamas National Trust in Nassau</t>
+  </si>
+  <si>
+    <t>WGN AM, John Landecker Show</t>
+  </si>
+  <si>
+    <t>Turtles with Austin and Andy</t>
+  </si>
+  <si>
+    <t>Chicago Water Week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning Talk at the Seattle Aquarium </t>
+  </si>
+  <si>
+    <t>Door Co Science on Tap at Bridge Up Brewery</t>
+  </si>
+  <si>
+    <t>Coffee with Curators - Door Co Museum and Historic Society Presentation</t>
+  </si>
+  <si>
+    <t>Pop Up presentation on EPA's Lake Guardian</t>
+  </si>
+  <si>
+    <t>Creek side engagement with a group of 37 toddlers and parents to learn about sucker migrations</t>
+  </si>
+  <si>
+    <t>Peninsula State Park - tabling about migratory fishes</t>
+  </si>
+  <si>
+    <t>sucker spawning run - cit sci, acoustic tagging, PIT tagging</t>
+  </si>
+  <si>
+    <t>engaged 30 Gr 6 students from Sturgeon Bay in hands-on experience capturing and PIT tagging white suckers at Big Creek in WI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7tgfnV9O_ho</t>
+  </si>
+  <si>
+    <t>short documentary done by a graduate student on the river dying event</t>
+  </si>
+  <si>
+    <t>Presentation on StAR and Shark Ray 360 work at Sharks International Conference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pfab F, Cunning R, Detmer AR, Frederica CF, Irving LJ, Moeller HV, Nisbet RM (2026) A model for heat and light stress in photosynthesis. Ecological Modelling 519: 111631. </t>
+  </si>
+  <si>
+    <t>http://doi.org/10.1016/j.ecolmodel.2026.111631</t>
+  </si>
+  <si>
+    <t>https://www.kcur.org/environment-agriculture/2026-06-01/cleanups-rivers-pollution-wildlife-water</t>
+  </si>
+  <si>
+    <t>In Field talk with After School Matters teens from Shedd</t>
+  </si>
+  <si>
+    <t>Talk with students of Loyola's Natural Resources Club students</t>
+  </si>
+  <si>
+    <t>fish tagging days and a day to download data.</t>
+  </si>
+  <si>
+    <t>Kessel, S. T., Auger-Méthé, M., Barbosa Martins, A. P., Cooke, S. J., Fisk, A. T., Haley, A. L., Heupel, M. R., Klinard, N. V., Matley, J. K., Piczak, M. L., Robichaud, J. A., &amp; Hussey, N. E. (2026). Global distribution of aquatic animal telemetry effort reveals geographic biases and opportunities for more inclusive tracking studies. Conservation Science and Practice, e70314. https://doi.org/10.1111/csp2.70314</t>
+  </si>
+  <si>
+    <t>https://conbio.onlinelibrary.wiley.com/doi/10.1111/csp2.70314</t>
+  </si>
+  <si>
+    <t>Coral Research Trip to Dry Tortugas</t>
   </si>
 </sst>
 </file>
@@ -3257,13 +3335,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3343,8 +3422,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W713" totalsRowShown="0">
-  <autoFilter ref="A1:W713" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W739" totalsRowShown="0">
+  <autoFilter ref="A1:W739" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3538,7 +3617,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="719" latestEventMarker="755">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="745" latestEventMarker="781">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -3865,7 +3944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W713"/>
+  <dimension ref="A1:W739"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
@@ -31589,6 +31668,1105 @@
       </c>
       <c r="W713" s="3"/>
     </row>
+    <row r="714" spans="1:23">
+      <c r="A714">
+        <v>720</v>
+      </c>
+      <c r="B714" s="4">
+        <v>46142.557928240698</v>
+      </c>
+      <c r="C714" s="4">
+        <v>46142.558310185203</v>
+      </c>
+      <c r="D714" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E714" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G714" s="1">
+        <v>46134</v>
+      </c>
+      <c r="H714" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J714" t="s">
+        <v>57</v>
+      </c>
+      <c r="L714" s="3"/>
+      <c r="M714" s="3"/>
+      <c r="T714">
+        <v>53</v>
+      </c>
+      <c r="U714" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="V714" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W714" s="3"/>
+    </row>
+    <row r="715" spans="1:23">
+      <c r="A715">
+        <v>721</v>
+      </c>
+      <c r="B715" s="4">
+        <v>46146.564375000002</v>
+      </c>
+      <c r="C715" s="4">
+        <v>46146.565590277802</v>
+      </c>
+      <c r="D715" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E715" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G715" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H715" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J715" t="s">
+        <v>57</v>
+      </c>
+      <c r="L715" s="3"/>
+      <c r="M715" s="3"/>
+      <c r="T715">
+        <v>50</v>
+      </c>
+      <c r="U715" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="V715" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W715" s="3"/>
+    </row>
+    <row r="716" spans="1:23">
+      <c r="A716">
+        <v>722</v>
+      </c>
+      <c r="B716" s="4">
+        <v>46146.565671296303</v>
+      </c>
+      <c r="C716" s="4">
+        <v>46146.566446759301</v>
+      </c>
+      <c r="D716" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E716" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G716" s="1">
+        <v>46134</v>
+      </c>
+      <c r="H716" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J716" t="s">
+        <v>27</v>
+      </c>
+      <c r="L716" s="3"/>
+      <c r="M716" s="3"/>
+      <c r="T716">
+        <v>20</v>
+      </c>
+      <c r="U716" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="V716" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="W716" s="3"/>
+    </row>
+    <row r="717" spans="1:23">
+      <c r="A717">
+        <v>723</v>
+      </c>
+      <c r="B717" s="4">
+        <v>46155.589282407404</v>
+      </c>
+      <c r="C717" s="4">
+        <v>46155.591793981497</v>
+      </c>
+      <c r="D717" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E717" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G717" s="1">
+        <v>46142</v>
+      </c>
+      <c r="H717" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L717" s="3"/>
+      <c r="M717" s="3"/>
+      <c r="O717">
+        <v>2</v>
+      </c>
+      <c r="P717">
+        <v>0</v>
+      </c>
+      <c r="Q717">
+        <v>0</v>
+      </c>
+      <c r="R717">
+        <v>0</v>
+      </c>
+      <c r="T717">
+        <v>10</v>
+      </c>
+      <c r="U717" s="3"/>
+      <c r="V717" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W717" s="3"/>
+    </row>
+    <row r="718" spans="1:23">
+      <c r="A718">
+        <v>724</v>
+      </c>
+      <c r="B718" s="4">
+        <v>46155.591828703698</v>
+      </c>
+      <c r="C718" s="4">
+        <v>46155.593043981498</v>
+      </c>
+      <c r="D718" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E718" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="1">
+        <v>46122</v>
+      </c>
+      <c r="H718" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I718" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L718" s="3"/>
+      <c r="M718" s="3"/>
+      <c r="U718" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="V718" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W718" s="3"/>
+    </row>
+    <row r="719" spans="1:23">
+      <c r="A719">
+        <v>725</v>
+      </c>
+      <c r="B719" s="4">
+        <v>46155.593055555597</v>
+      </c>
+      <c r="C719" s="4">
+        <v>46155.5934375</v>
+      </c>
+      <c r="D719" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E719" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G719" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H719" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I719" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L719" s="3"/>
+      <c r="M719" s="3"/>
+      <c r="U719" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="V719" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W719" s="3"/>
+    </row>
+    <row r="720" spans="1:23">
+      <c r="A720">
+        <v>726</v>
+      </c>
+      <c r="B720" s="4">
+        <v>46155.593449074098</v>
+      </c>
+      <c r="C720" s="4">
+        <v>46155.5941087963</v>
+      </c>
+      <c r="D720" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E720" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G720" s="1">
+        <v>46133</v>
+      </c>
+      <c r="H720" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I720" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L720" s="3"/>
+      <c r="M720" s="3"/>
+      <c r="U720" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="V720" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W720" s="3"/>
+    </row>
+    <row r="721" spans="1:23">
+      <c r="A721">
+        <v>727</v>
+      </c>
+      <c r="B721" s="4">
+        <v>46155.594178240703</v>
+      </c>
+      <c r="C721" s="4">
+        <v>46155.598611111098</v>
+      </c>
+      <c r="D721" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E721" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G721" s="1">
+        <v>46134</v>
+      </c>
+      <c r="H721" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J721" t="s">
+        <v>57</v>
+      </c>
+      <c r="L721" s="3"/>
+      <c r="M721" s="3"/>
+      <c r="T721">
+        <v>53</v>
+      </c>
+      <c r="U721" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="V721" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W721" s="3"/>
+    </row>
+    <row r="722" spans="1:23">
+      <c r="A722">
+        <v>728</v>
+      </c>
+      <c r="B722" s="4">
+        <v>46155.598634259302</v>
+      </c>
+      <c r="C722" s="4">
+        <v>46155.599166666703</v>
+      </c>
+      <c r="D722" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E722" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G722" s="1">
+        <v>46147</v>
+      </c>
+      <c r="H722" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J722" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L722" s="3"/>
+      <c r="M722" s="3"/>
+      <c r="T722">
+        <v>35</v>
+      </c>
+      <c r="U722" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="V722" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W722" s="3"/>
+    </row>
+    <row r="723" spans="1:23">
+      <c r="A723">
+        <v>729</v>
+      </c>
+      <c r="B723" s="4">
+        <v>46157.569826388899</v>
+      </c>
+      <c r="C723" s="4">
+        <v>46157.570185185199</v>
+      </c>
+      <c r="D723" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E723" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G723" s="1">
+        <v>46156</v>
+      </c>
+      <c r="H723" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J723" t="s">
+        <v>27</v>
+      </c>
+      <c r="L723" s="3"/>
+      <c r="M723" s="3"/>
+      <c r="T723">
+        <v>400</v>
+      </c>
+      <c r="U723" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="V723" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W723" s="3"/>
+    </row>
+    <row r="724" spans="1:23">
+      <c r="A724">
+        <v>730</v>
+      </c>
+      <c r="B724" s="4">
+        <v>46157.603726851899</v>
+      </c>
+      <c r="C724" s="4">
+        <v>46157.604791666701</v>
+      </c>
+      <c r="D724" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E724" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G724" s="1">
+        <v>46114</v>
+      </c>
+      <c r="H724" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J724" t="s">
+        <v>27</v>
+      </c>
+      <c r="L724" s="3"/>
+      <c r="M724" s="3"/>
+      <c r="T724">
+        <v>26</v>
+      </c>
+      <c r="U724" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="V724" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W724" s="3"/>
+    </row>
+    <row r="725" spans="1:23">
+      <c r="A725">
+        <v>731</v>
+      </c>
+      <c r="B725" s="4">
+        <v>46157.604884259301</v>
+      </c>
+      <c r="C725" s="4">
+        <v>46157.605567129598</v>
+      </c>
+      <c r="D725" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E725" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G725" s="1">
+        <v>46115</v>
+      </c>
+      <c r="H725" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J725" t="s">
+        <v>27</v>
+      </c>
+      <c r="L725" s="3"/>
+      <c r="M725" s="3"/>
+      <c r="T725">
+        <v>11</v>
+      </c>
+      <c r="U725" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="V725" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W725" s="3"/>
+    </row>
+    <row r="726" spans="1:23">
+      <c r="A726">
+        <v>732</v>
+      </c>
+      <c r="B726" s="4">
+        <v>46157.606284722198</v>
+      </c>
+      <c r="C726" s="4">
+        <v>46157.607002314799</v>
+      </c>
+      <c r="D726" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E726" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G726" s="1">
+        <v>46120</v>
+      </c>
+      <c r="H726" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J726" t="s">
+        <v>27</v>
+      </c>
+      <c r="L726" s="3"/>
+      <c r="M726" s="3"/>
+      <c r="T726">
+        <v>5</v>
+      </c>
+      <c r="U726" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="V726" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W726" s="3"/>
+    </row>
+    <row r="727" spans="1:23">
+      <c r="A727">
+        <v>733</v>
+      </c>
+      <c r="B727" s="4">
+        <v>46157.607094907398</v>
+      </c>
+      <c r="C727" s="4">
+        <v>46157.607870370397</v>
+      </c>
+      <c r="D727" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E727" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G727" s="1">
+        <v>46135</v>
+      </c>
+      <c r="H727" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J727" t="s">
+        <v>27</v>
+      </c>
+      <c r="L727" s="3"/>
+      <c r="M727" s="3"/>
+      <c r="T727">
+        <v>37</v>
+      </c>
+      <c r="U727" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="V727" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W727" s="3"/>
+    </row>
+    <row r="728" spans="1:23">
+      <c r="A728">
+        <v>734</v>
+      </c>
+      <c r="B728" s="4">
+        <v>46157.607962962997</v>
+      </c>
+      <c r="C728" s="4">
+        <v>46157.6085648148</v>
+      </c>
+      <c r="D728" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E728" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G728" s="1">
+        <v>46138</v>
+      </c>
+      <c r="H728" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J728" t="s">
+        <v>82</v>
+      </c>
+      <c r="L728" s="3"/>
+      <c r="M728" s="3"/>
+      <c r="T728">
+        <v>25</v>
+      </c>
+      <c r="U728" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="V728" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W728" s="3"/>
+    </row>
+    <row r="729" spans="1:23">
+      <c r="A729">
+        <v>735</v>
+      </c>
+      <c r="B729" s="4">
+        <v>46157.608599537001</v>
+      </c>
+      <c r="C729" s="4">
+        <v>46157.609953703701</v>
+      </c>
+      <c r="D729" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E729" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G729" s="1">
+        <v>46140</v>
+      </c>
+      <c r="H729" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L729" s="3"/>
+      <c r="M729" s="3"/>
+      <c r="O729">
+        <v>1</v>
+      </c>
+      <c r="P729">
+        <v>0</v>
+      </c>
+      <c r="Q729">
+        <v>0</v>
+      </c>
+      <c r="R729">
+        <v>0</v>
+      </c>
+      <c r="T729">
+        <v>28</v>
+      </c>
+      <c r="U729" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="V729" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W729" s="3"/>
+    </row>
+    <row r="730" spans="1:23">
+      <c r="A730">
+        <v>736</v>
+      </c>
+      <c r="B730" s="4">
+        <v>46157.610069444403</v>
+      </c>
+      <c r="C730" s="4">
+        <v>46157.6113541667</v>
+      </c>
+      <c r="D730" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E730" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G730" s="1">
+        <v>46135</v>
+      </c>
+      <c r="H730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K730" t="s">
+        <v>92</v>
+      </c>
+      <c r="L730" s="3"/>
+      <c r="M730" s="3"/>
+      <c r="T730">
+        <v>30</v>
+      </c>
+      <c r="U730" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="V730" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="W730" s="3"/>
+    </row>
+    <row r="731" spans="1:23">
+      <c r="A731">
+        <v>737</v>
+      </c>
+      <c r="B731" s="4">
+        <v>46160.391585648104</v>
+      </c>
+      <c r="C731" s="4">
+        <v>46160.392025462999</v>
+      </c>
+      <c r="D731" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E731" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G731" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H731" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I731" t="s">
+        <v>70</v>
+      </c>
+      <c r="L731" s="3"/>
+      <c r="M731" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="U731" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="V731" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W731" s="3"/>
+    </row>
+    <row r="732" spans="1:23">
+      <c r="A732">
+        <v>738</v>
+      </c>
+      <c r="B732" s="4">
+        <v>46162.555277777799</v>
+      </c>
+      <c r="C732" s="4">
+        <v>46162.555925925903</v>
+      </c>
+      <c r="D732" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E732" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G732" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H732" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J732" t="s">
+        <v>108</v>
+      </c>
+      <c r="L732" s="3"/>
+      <c r="M732" s="3"/>
+      <c r="T732">
+        <v>400</v>
+      </c>
+      <c r="U732" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="V732" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="W732" s="3"/>
+    </row>
+    <row r="733" spans="1:23">
+      <c r="A733">
+        <v>739</v>
+      </c>
+      <c r="B733" s="4">
+        <v>46163.399826388901</v>
+      </c>
+      <c r="C733" s="4">
+        <v>46163.400046296301</v>
+      </c>
+      <c r="D733" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E733" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G733" s="1">
+        <v>46163</v>
+      </c>
+      <c r="H733" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L733" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M733" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="U733" s="3"/>
+      <c r="V733" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W733" s="3"/>
+    </row>
+    <row r="734" spans="1:23">
+      <c r="A734">
+        <v>740</v>
+      </c>
+      <c r="B734" s="4">
+        <v>46176.423564814802</v>
+      </c>
+      <c r="C734" s="4">
+        <v>46176.4237615741</v>
+      </c>
+      <c r="D734" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E734" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F734" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G734" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H734" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I734" t="s">
+        <v>111</v>
+      </c>
+      <c r="L734" s="3"/>
+      <c r="M734" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="U734" s="3"/>
+      <c r="V734" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W734" s="3"/>
+    </row>
+    <row r="735" spans="1:23">
+      <c r="A735">
+        <v>741</v>
+      </c>
+      <c r="B735" s="4">
+        <v>46176.424872685202</v>
+      </c>
+      <c r="C735" s="4">
+        <v>46176.425671296303</v>
+      </c>
+      <c r="D735" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E735" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F735" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G735" s="1">
+        <v>46123</v>
+      </c>
+      <c r="H735" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J735" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L735" s="3"/>
+      <c r="M735" s="3"/>
+      <c r="T735">
+        <v>12</v>
+      </c>
+      <c r="U735" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="V735" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W735" s="3"/>
+    </row>
+    <row r="736" spans="1:23">
+      <c r="A736">
+        <v>742</v>
+      </c>
+      <c r="B736" s="4">
+        <v>46176.425694444399</v>
+      </c>
+      <c r="C736" s="4">
+        <v>46176.426319444399</v>
+      </c>
+      <c r="D736" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E736" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F736" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G736" s="1">
+        <v>46170</v>
+      </c>
+      <c r="H736" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J736" t="s">
+        <v>73</v>
+      </c>
+      <c r="L736" s="3"/>
+      <c r="M736" s="3"/>
+      <c r="T736">
+        <v>12</v>
+      </c>
+      <c r="U736" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V736" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W736" s="3"/>
+    </row>
+    <row r="737" spans="1:23">
+      <c r="A737" s="6">
+        <v>743</v>
+      </c>
+      <c r="B737" s="4">
+        <v>46176.426446759302</v>
+      </c>
+      <c r="C737" s="4">
+        <v>46176.4269444444</v>
+      </c>
+      <c r="D737" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E737" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G737" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H737" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I737" s="6"/>
+      <c r="J737" s="6"/>
+      <c r="K737" s="6"/>
+      <c r="L737" s="3"/>
+      <c r="M737" s="3"/>
+      <c r="N737" s="6"/>
+      <c r="O737" s="6">
+        <v>2</v>
+      </c>
+      <c r="P737" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q737" s="6">
+        <v>0</v>
+      </c>
+      <c r="R737" s="6">
+        <v>0</v>
+      </c>
+      <c r="S737" s="6"/>
+      <c r="T737" s="6">
+        <v>3</v>
+      </c>
+      <c r="U737" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="V737" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W737" s="3"/>
+    </row>
+    <row r="738" spans="1:23">
+      <c r="A738" s="6">
+        <v>744</v>
+      </c>
+      <c r="B738" s="4">
+        <v>46178.5491203704</v>
+      </c>
+      <c r="C738" s="4">
+        <v>46178.555034722202</v>
+      </c>
+      <c r="D738" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E738" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G738" s="1">
+        <v>46178</v>
+      </c>
+      <c r="H738" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I738" s="6"/>
+      <c r="J738" s="6"/>
+      <c r="K738" s="6"/>
+      <c r="L738" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M738" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="N738" s="6"/>
+      <c r="O738" s="6"/>
+      <c r="P738" s="6"/>
+      <c r="Q738" s="6"/>
+      <c r="R738" s="6"/>
+      <c r="S738" s="6"/>
+      <c r="T738" s="6"/>
+      <c r="U738" s="3"/>
+      <c r="V738" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="W738" s="3"/>
+    </row>
+    <row r="739" spans="1:23">
+      <c r="A739" s="6">
+        <v>745</v>
+      </c>
+      <c r="B739" s="4">
+        <v>46181.760034722203</v>
+      </c>
+      <c r="C739" s="4">
+        <v>46181.761250000003</v>
+      </c>
+      <c r="D739" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E739" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G739" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H739" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I739" s="6"/>
+      <c r="J739" s="6"/>
+      <c r="K739" s="6"/>
+      <c r="L739" s="3"/>
+      <c r="M739" s="3"/>
+      <c r="N739" s="6"/>
+      <c r="O739" s="6">
+        <v>2</v>
+      </c>
+      <c r="P739" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q739" s="6">
+        <v>2</v>
+      </c>
+      <c r="R739" s="6">
+        <v>1</v>
+      </c>
+      <c r="S739" s="6"/>
+      <c r="T739" s="6">
+        <v>6</v>
+      </c>
+      <c r="U739" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V739" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W739" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30219"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DDA8B22-009D-42B7-9D67-CFABE336D20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="504" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39A8B5B5-D61D-4548-BA65-B83B7D132FB2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5258" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5315" uniqueCount="1106">
   <si>
     <t>Id</t>
   </si>
@@ -3321,6 +3321,39 @@
   </si>
   <si>
     <t>Meg and Uzma ECB Interns</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1201406391/a463e91f94?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Bahamas @ Sunrise show to discuss iguanas as ecotourism assets</t>
+  </si>
+  <si>
+    <t>Andros Business Outlook Conference to speak about iguanas as ecotourism assets</t>
+  </si>
+  <si>
+    <t>https://www.record-eagle.com/news/go/chris-smith-a-sucker-for-fishpass/article_4c9368f3-efb1-4413-9bd5-7eaff0d032ea.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Sucker for FishPass - interview by the Record Eagle </t>
+  </si>
+  <si>
+    <t>Engaged 137 volunteers in sucker migration phenology monitoring across IL, WI, MI at 14 tributaries (volunteer effort from mid-March through early May)</t>
+  </si>
+  <si>
+    <t>removal of citizen science gear and acoustic telemetry equipment</t>
+  </si>
+  <si>
+    <t>Press release by Great Lakes Fishery Commission and Shedd Aquarium</t>
+  </si>
+  <si>
+    <t>https://www.sheddaquarium.org/about-shedd/press-releases/great-lakes-fishery-commission-award</t>
+  </si>
+  <si>
+    <t>https://www.glfc.org/pubs/pressrel/2026_Murchie_Besadny_Award_Release.pdf</t>
+  </si>
+  <si>
+    <t>Short presentation at the Music Box Jaws screening</t>
   </si>
 </sst>
 </file>
@@ -3356,13 +3389,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3442,8 +3476,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W745" totalsRowShown="0">
-  <autoFilter ref="A1:W745" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W753" totalsRowShown="0">
+  <autoFilter ref="A1:W753" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="hwind@sheddaquarium.org"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W743">
     <sortCondition ref="B1:B743"/>
   </sortState>
@@ -3613,7 +3653,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="751" latestEventMarker="789">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="759" latestEventMarker="797">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -3940,13 +3980,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W745"/>
+  <dimension ref="A1:W753"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="19" customWidth="1"/>
     <col min="12" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="19" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="52.7109375" customWidth="1"/>
+    <col min="16" max="16" width="48.42578125" customWidth="1"/>
+    <col min="17" max="17" width="46.85546875" customWidth="1"/>
+    <col min="18" max="18" width="50.28515625" customWidth="1"/>
     <col min="21" max="21" width="62" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4021,7 +4065,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" hidden="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4059,7 +4103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" hidden="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4094,7 +4138,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" hidden="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4129,7 +4173,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" hidden="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4164,7 +4208,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" hidden="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4199,7 +4243,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" hidden="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4234,7 +4278,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" hidden="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4269,7 +4313,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" hidden="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4304,7 +4348,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" hidden="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4339,7 +4383,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" hidden="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4374,7 +4418,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" hidden="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4412,7 +4456,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" hidden="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4450,7 +4494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4488,7 +4532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4526,7 +4570,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4564,7 +4608,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" hidden="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4602,7 +4646,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" hidden="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4637,7 +4681,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" hidden="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4672,7 +4716,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" hidden="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4710,7 +4754,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" hidden="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4745,7 +4789,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" hidden="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4783,7 +4827,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" hidden="1">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4818,7 +4862,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" hidden="1">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4859,7 +4903,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" hidden="1">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4894,7 +4938,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" hidden="1">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4929,7 +4973,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" hidden="1">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4961,7 +5005,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" hidden="1">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4996,7 +5040,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" hidden="1">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5028,7 +5072,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" hidden="1">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5066,7 +5110,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" hidden="1">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5107,7 +5151,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" hidden="1">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5145,7 +5189,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" hidden="1">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5186,7 +5230,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" hidden="1">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5227,7 +5271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" hidden="1">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5268,7 +5312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" hidden="1">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5309,7 +5353,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" hidden="1">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5350,7 +5394,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" hidden="1">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5391,7 +5435,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" hidden="1">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5426,7 +5470,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" hidden="1">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5461,7 +5505,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" hidden="1">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5496,7 +5540,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" hidden="1">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5531,7 +5575,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" hidden="1">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5569,7 +5613,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" hidden="1">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5607,7 +5651,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" hidden="1">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5642,7 +5686,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:23" hidden="1">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5677,7 +5721,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" hidden="1">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5712,7 +5756,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" hidden="1">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5750,7 +5794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:23" hidden="1">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5782,7 +5826,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:23" hidden="1">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5820,7 +5864,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:23" hidden="1">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5855,7 +5899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:23" hidden="1">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5887,7 +5931,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:23" hidden="1">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5925,7 +5969,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:23" hidden="1">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5960,7 +6004,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:23" hidden="1">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5995,7 +6039,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:23" hidden="1">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6033,7 +6077,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:23" hidden="1">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6071,7 +6115,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:23" hidden="1">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6109,7 +6153,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:23" hidden="1">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6147,7 +6191,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:23" hidden="1">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6185,7 +6229,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:23" hidden="1">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6223,7 +6267,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:23" hidden="1">
       <c r="A62">
         <v>67</v>
       </c>
@@ -6255,7 +6299,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:23">
+    <row r="63" spans="1:23" hidden="1">
       <c r="A63">
         <v>61</v>
       </c>
@@ -6290,7 +6334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:23" hidden="1">
       <c r="A64">
         <v>62</v>
       </c>
@@ -6328,7 +6372,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:23" hidden="1">
       <c r="A65">
         <v>63</v>
       </c>
@@ -6366,7 +6410,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:23" hidden="1">
       <c r="A66">
         <v>64</v>
       </c>
@@ -6401,7 +6445,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:23" hidden="1">
       <c r="A67">
         <v>65</v>
       </c>
@@ -6436,7 +6480,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:23" hidden="1">
       <c r="A68">
         <v>66</v>
       </c>
@@ -6477,7 +6521,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
+    <row r="69" spans="1:23" hidden="1">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6509,7 +6553,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:23" hidden="1">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6544,7 +6588,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:23" hidden="1">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6579,7 +6623,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:23" hidden="1">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6617,7 +6661,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:23" hidden="1">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6655,7 +6699,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
+    <row r="74" spans="1:23" hidden="1">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6696,7 +6740,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
+    <row r="75" spans="1:23" hidden="1">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6737,7 +6781,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
+    <row r="76" spans="1:23" hidden="1">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6772,7 +6816,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
+    <row r="77" spans="1:23" hidden="1">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6810,7 +6854,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
+    <row r="78" spans="1:23" hidden="1">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6851,7 +6895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:23">
+    <row r="79" spans="1:23" hidden="1">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6886,7 +6930,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:23">
+    <row r="80" spans="1:23" hidden="1">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6927,7 +6971,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
+    <row r="81" spans="1:23" hidden="1">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6965,7 +7009,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
+    <row r="82" spans="1:23" hidden="1">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7003,7 +7047,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:23" hidden="1">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7041,7 +7085,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:23" hidden="1">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7082,7 +7126,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
+    <row r="85" spans="1:23" hidden="1">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7120,7 +7164,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
+    <row r="86" spans="1:23" hidden="1">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7263,7 +7307,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:23" hidden="1">
       <c r="A90">
         <v>88</v>
       </c>
@@ -7304,7 +7348,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:23" hidden="1">
       <c r="A91">
         <v>89</v>
       </c>
@@ -7339,7 +7383,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:23" hidden="1">
       <c r="A92">
         <v>90</v>
       </c>
@@ -7374,7 +7418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:23">
+    <row r="93" spans="1:23" hidden="1">
       <c r="A93">
         <v>91</v>
       </c>
@@ -7409,7 +7453,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:23">
+    <row r="94" spans="1:23" hidden="1">
       <c r="A94">
         <v>92</v>
       </c>
@@ -7450,7 +7494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:23">
+    <row r="95" spans="1:23" hidden="1">
       <c r="A95">
         <v>93</v>
       </c>
@@ -7488,7 +7532,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:23">
+    <row r="96" spans="1:23" hidden="1">
       <c r="A96">
         <v>94</v>
       </c>
@@ -7523,7 +7567,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:23" hidden="1">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7561,7 +7605,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:23" hidden="1">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7596,7 +7640,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:23" hidden="1">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7634,7 +7678,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:23">
+    <row r="100" spans="1:23" hidden="1">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7669,7 +7713,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
+    <row r="101" spans="1:23" hidden="1">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7704,7 +7748,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="102" spans="1:23">
+    <row r="102" spans="1:23" hidden="1">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7744,7 +7788,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="103" spans="1:23">
+    <row r="103" spans="1:23" hidden="1">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7784,7 +7828,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="104" spans="1:23">
+    <row r="104" spans="1:23" hidden="1">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7824,7 +7868,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:23">
+    <row r="105" spans="1:23" hidden="1">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7861,7 +7905,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="106" spans="1:23">
+    <row r="106" spans="1:23" hidden="1">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7898,7 +7942,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" hidden="1">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7935,7 +7979,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" hidden="1">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7972,7 +8016,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" hidden="1">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8009,7 +8053,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="110" spans="1:23">
+    <row r="110" spans="1:23" hidden="1">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8044,7 +8088,7 @@
       </c>
       <c r="W110" s="3"/>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" hidden="1">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8087,7 +8131,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:23" hidden="1">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8130,7 +8174,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:23" hidden="1">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8167,7 +8211,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:23">
+    <row r="114" spans="1:23" hidden="1">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8210,7 +8254,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:23">
+    <row r="115" spans="1:23" hidden="1">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8249,7 +8293,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="116" spans="1:23">
+    <row r="116" spans="1:23" hidden="1">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8286,7 +8330,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="117" spans="1:23">
+    <row r="117" spans="1:23" hidden="1">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8323,7 +8367,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="118" spans="1:23">
+    <row r="118" spans="1:23" hidden="1">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8362,7 +8406,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="119" spans="1:23">
+    <row r="119" spans="1:23" hidden="1">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8397,7 +8441,7 @@
       </c>
       <c r="W119" s="3"/>
     </row>
-    <row r="120" spans="1:23">
+    <row r="120" spans="1:23" hidden="1">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8435,7 +8479,7 @@
       </c>
       <c r="W120" s="3"/>
     </row>
-    <row r="121" spans="1:23">
+    <row r="121" spans="1:23" hidden="1">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8475,7 +8519,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:23" hidden="1">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8515,7 +8559,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="123" spans="1:23">
+    <row r="123" spans="1:23" hidden="1">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8555,7 +8599,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:23" hidden="1">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8595,7 +8639,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:23">
+    <row r="125" spans="1:23" hidden="1">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8635,7 +8679,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="126" spans="1:23">
+    <row r="126" spans="1:23" hidden="1">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8678,7 +8722,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:23" hidden="1">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8721,7 +8765,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="128" spans="1:23">
+    <row r="128" spans="1:23" hidden="1">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8762,7 +8806,7 @@
       </c>
       <c r="W128" s="3"/>
     </row>
-    <row r="129" spans="1:23">
+    <row r="129" spans="1:23" hidden="1">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8803,7 +8847,7 @@
       </c>
       <c r="W129" s="3"/>
     </row>
-    <row r="130" spans="1:23">
+    <row r="130" spans="1:23" hidden="1">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8846,7 +8890,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="131" spans="1:23">
+    <row r="131" spans="1:23" hidden="1">
       <c r="A131">
         <v>130</v>
       </c>
@@ -8883,7 +8927,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:23" hidden="1">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8920,7 +8964,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="133" spans="1:23">
+    <row r="133" spans="1:23" hidden="1">
       <c r="A133">
         <v>132</v>
       </c>
@@ -8957,7 +9001,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="134" spans="1:23">
+    <row r="134" spans="1:23" hidden="1">
       <c r="A134">
         <v>133</v>
       </c>
@@ -9000,7 +9044,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="135" spans="1:23">
+    <row r="135" spans="1:23" hidden="1">
       <c r="A135">
         <v>134</v>
       </c>
@@ -9040,7 +9084,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="136" spans="1:23">
+    <row r="136" spans="1:23" hidden="1">
       <c r="A136">
         <v>135</v>
       </c>
@@ -9080,7 +9124,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="137" spans="1:23">
+    <row r="137" spans="1:23" hidden="1">
       <c r="A137">
         <v>136</v>
       </c>
@@ -9119,7 +9163,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:23">
+    <row r="138" spans="1:23" hidden="1">
       <c r="A138">
         <v>137</v>
       </c>
@@ -9158,7 +9202,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="139" spans="1:23">
+    <row r="139" spans="1:23" hidden="1">
       <c r="A139">
         <v>138</v>
       </c>
@@ -9201,7 +9245,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="140" spans="1:23">
+    <row r="140" spans="1:23" hidden="1">
       <c r="A140">
         <v>139</v>
       </c>
@@ -9241,7 +9285,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="141" spans="1:23">
+    <row r="141" spans="1:23" hidden="1">
       <c r="A141">
         <v>140</v>
       </c>
@@ -9280,7 +9324,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="142" spans="1:23">
+    <row r="142" spans="1:23" hidden="1">
       <c r="A142">
         <v>141</v>
       </c>
@@ -9319,7 +9363,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="143" spans="1:23">
+    <row r="143" spans="1:23" hidden="1">
       <c r="A143">
         <v>142</v>
       </c>
@@ -9358,7 +9402,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="144" spans="1:23">
+    <row r="144" spans="1:23" hidden="1">
       <c r="A144">
         <v>143</v>
       </c>
@@ -9398,7 +9442,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="145" spans="1:23">
+    <row r="145" spans="1:23" hidden="1">
       <c r="A145">
         <v>144</v>
       </c>
@@ -9441,7 +9485,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="146" spans="1:23">
+    <row r="146" spans="1:23" hidden="1">
       <c r="A146">
         <v>145</v>
       </c>
@@ -9480,7 +9524,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="147" spans="1:23">
+    <row r="147" spans="1:23" hidden="1">
       <c r="A147">
         <v>146</v>
       </c>
@@ -9517,7 +9561,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="148" spans="1:23">
+    <row r="148" spans="1:23" hidden="1">
       <c r="A148">
         <v>147</v>
       </c>
@@ -9554,7 +9598,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="149" spans="1:23">
+    <row r="149" spans="1:23" hidden="1">
       <c r="A149">
         <v>148</v>
       </c>
@@ -9591,7 +9635,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="150" spans="1:23">
+    <row r="150" spans="1:23" hidden="1">
       <c r="A150">
         <v>149</v>
       </c>
@@ -9634,7 +9678,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="151" spans="1:23">
+    <row r="151" spans="1:23" hidden="1">
       <c r="A151">
         <v>150</v>
       </c>
@@ -9677,7 +9721,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="152" spans="1:23">
+    <row r="152" spans="1:23" hidden="1">
       <c r="A152">
         <v>151</v>
       </c>
@@ -9716,7 +9760,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="153" spans="1:23">
+    <row r="153" spans="1:23" hidden="1">
       <c r="A153">
         <v>152</v>
       </c>
@@ -9755,7 +9799,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:23" hidden="1">
       <c r="A154">
         <v>153</v>
       </c>
@@ -9792,7 +9836,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="155" spans="1:23">
+    <row r="155" spans="1:23" hidden="1">
       <c r="A155">
         <v>154</v>
       </c>
@@ -9831,7 +9875,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:23">
+    <row r="156" spans="1:23" hidden="1">
       <c r="A156">
         <v>155</v>
       </c>
@@ -9871,7 +9915,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="157" spans="1:23">
+    <row r="157" spans="1:23" hidden="1">
       <c r="A157">
         <v>156</v>
       </c>
@@ -9911,7 +9955,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="158" spans="1:23">
+    <row r="158" spans="1:23" hidden="1">
       <c r="A158">
         <v>157</v>
       </c>
@@ -9951,7 +9995,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="159" spans="1:23">
+    <row r="159" spans="1:23" hidden="1">
       <c r="A159">
         <v>158</v>
       </c>
@@ -9991,7 +10035,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="160" spans="1:23">
+    <row r="160" spans="1:23" hidden="1">
       <c r="A160">
         <v>159</v>
       </c>
@@ -10034,7 +10078,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:23">
+    <row r="161" spans="1:23" hidden="1">
       <c r="A161">
         <v>160</v>
       </c>
@@ -10077,7 +10121,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="162" spans="1:23">
+    <row r="162" spans="1:23" hidden="1">
       <c r="A162">
         <v>161</v>
       </c>
@@ -10114,7 +10158,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="163" spans="1:23">
+    <row r="163" spans="1:23" hidden="1">
       <c r="A163">
         <v>162</v>
       </c>
@@ -10153,7 +10197,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="164" spans="1:23">
+    <row r="164" spans="1:23" hidden="1">
       <c r="A164">
         <v>163</v>
       </c>
@@ -10190,7 +10234,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:23">
+    <row r="165" spans="1:23" hidden="1">
       <c r="A165">
         <v>164</v>
       </c>
@@ -10227,7 +10271,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="166" spans="1:23">
+    <row r="166" spans="1:23" hidden="1">
       <c r="A166">
         <v>165</v>
       </c>
@@ -10262,7 +10306,7 @@
       </c>
       <c r="W166" s="3"/>
     </row>
-    <row r="167" spans="1:23">
+    <row r="167" spans="1:23" hidden="1">
       <c r="A167">
         <v>166</v>
       </c>
@@ -10301,7 +10345,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="168" spans="1:23">
+    <row r="168" spans="1:23" hidden="1">
       <c r="A168">
         <v>167</v>
       </c>
@@ -10340,7 +10384,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="169" spans="1:23">
+    <row r="169" spans="1:23" hidden="1">
       <c r="A169">
         <v>168</v>
       </c>
@@ -10380,7 +10424,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="170" spans="1:23">
+    <row r="170" spans="1:23" hidden="1">
       <c r="A170">
         <v>169</v>
       </c>
@@ -10423,7 +10467,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="171" spans="1:23">
+    <row r="171" spans="1:23" hidden="1">
       <c r="A171">
         <v>170</v>
       </c>
@@ -10466,7 +10510,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="172" spans="1:23">
+    <row r="172" spans="1:23" hidden="1">
       <c r="A172">
         <v>171</v>
       </c>
@@ -10503,7 +10547,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="173" spans="1:23">
+    <row r="173" spans="1:23" hidden="1">
       <c r="A173">
         <v>172</v>
       </c>
@@ -10540,7 +10584,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="174" spans="1:23">
+    <row r="174" spans="1:23" hidden="1">
       <c r="A174">
         <v>173</v>
       </c>
@@ -10579,7 +10623,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="175" spans="1:23">
+    <row r="175" spans="1:23" hidden="1">
       <c r="A175">
         <v>174</v>
       </c>
@@ -10619,7 +10663,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="176" spans="1:23">
+    <row r="176" spans="1:23" hidden="1">
       <c r="A176">
         <v>175</v>
       </c>
@@ -10659,7 +10703,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="177" spans="1:23">
+    <row r="177" spans="1:23" hidden="1">
       <c r="A177">
         <v>176</v>
       </c>
@@ -10699,7 +10743,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="178" spans="1:23">
+    <row r="178" spans="1:23" hidden="1">
       <c r="A178">
         <v>177</v>
       </c>
@@ -10742,7 +10786,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="179" spans="1:23">
+    <row r="179" spans="1:23" hidden="1">
       <c r="A179">
         <v>178</v>
       </c>
@@ -10785,7 +10829,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="180" spans="1:23">
+    <row r="180" spans="1:23" hidden="1">
       <c r="A180">
         <v>179</v>
       </c>
@@ -10828,7 +10872,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="181" spans="1:23">
+    <row r="181" spans="1:23" hidden="1">
       <c r="A181">
         <v>180</v>
       </c>
@@ -10867,7 +10911,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="182" spans="1:23">
+    <row r="182" spans="1:23" hidden="1">
       <c r="A182">
         <v>182</v>
       </c>
@@ -10906,7 +10950,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="183" spans="1:23">
+    <row r="183" spans="1:23" hidden="1">
       <c r="A183">
         <v>183</v>
       </c>
@@ -10949,7 +10993,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="184" spans="1:23">
+    <row r="184" spans="1:23" hidden="1">
       <c r="A184">
         <v>184</v>
       </c>
@@ -10986,7 +11030,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="185" spans="1:23">
+    <row r="185" spans="1:23" hidden="1">
       <c r="A185">
         <v>185</v>
       </c>
@@ -11029,7 +11073,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="186" spans="1:23">
+    <row r="186" spans="1:23" hidden="1">
       <c r="A186">
         <v>186</v>
       </c>
@@ -11072,7 +11116,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="187" spans="1:23">
+    <row r="187" spans="1:23" hidden="1">
       <c r="A187">
         <v>187</v>
       </c>
@@ -11109,7 +11153,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="188" spans="1:23">
+    <row r="188" spans="1:23" hidden="1">
       <c r="A188">
         <v>188</v>
       </c>
@@ -11152,7 +11196,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="189" spans="1:23">
+    <row r="189" spans="1:23" hidden="1">
       <c r="A189">
         <v>189</v>
       </c>
@@ -11195,7 +11239,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="190" spans="1:23">
+    <row r="190" spans="1:23" hidden="1">
       <c r="A190">
         <v>190</v>
       </c>
@@ -11232,7 +11276,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="191" spans="1:23">
+    <row r="191" spans="1:23" hidden="1">
       <c r="A191">
         <v>191</v>
       </c>
@@ -11275,7 +11319,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="192" spans="1:23">
+    <row r="192" spans="1:23" hidden="1">
       <c r="A192">
         <v>192</v>
       </c>
@@ -11312,7 +11356,7 @@
       </c>
       <c r="W192" s="3"/>
     </row>
-    <row r="193" spans="1:23">
+    <row r="193" spans="1:23" hidden="1">
       <c r="A193">
         <v>193</v>
       </c>
@@ -11351,7 +11395,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="194" spans="1:23">
+    <row r="194" spans="1:23" hidden="1">
       <c r="A194">
         <v>194</v>
       </c>
@@ -11390,7 +11434,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="195" spans="1:23">
+    <row r="195" spans="1:23" hidden="1">
       <c r="A195">
         <v>195</v>
       </c>
@@ -11431,7 +11475,7 @@
       </c>
       <c r="W195" s="3"/>
     </row>
-    <row r="196" spans="1:23">
+    <row r="196" spans="1:23" hidden="1">
       <c r="A196">
         <v>196</v>
       </c>
@@ -11470,7 +11514,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="1:23">
+    <row r="197" spans="1:23" hidden="1">
       <c r="A197">
         <v>197</v>
       </c>
@@ -11511,7 +11555,7 @@
       </c>
       <c r="W197" s="3"/>
     </row>
-    <row r="198" spans="1:23">
+    <row r="198" spans="1:23" hidden="1">
       <c r="A198">
         <v>198</v>
       </c>
@@ -11552,7 +11596,7 @@
       </c>
       <c r="W198" s="3"/>
     </row>
-    <row r="199" spans="1:23">
+    <row r="199" spans="1:23" hidden="1">
       <c r="A199">
         <v>199</v>
       </c>
@@ -11592,7 +11636,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="200" spans="1:23">
+    <row r="200" spans="1:23" hidden="1">
       <c r="A200">
         <v>200</v>
       </c>
@@ -11629,7 +11673,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="201" spans="1:23">
+    <row r="201" spans="1:23" hidden="1">
       <c r="A201">
         <v>201</v>
       </c>
@@ -11666,7 +11710,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="202" spans="1:23">
+    <row r="202" spans="1:23" hidden="1">
       <c r="A202">
         <v>202</v>
       </c>
@@ -11703,7 +11747,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="203" spans="1:23">
+    <row r="203" spans="1:23" hidden="1">
       <c r="A203">
         <v>223</v>
       </c>
@@ -11740,7 +11784,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="204" spans="1:23">
+    <row r="204" spans="1:23" hidden="1">
       <c r="A204">
         <v>203</v>
       </c>
@@ -11777,7 +11821,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:23">
+    <row r="205" spans="1:23" hidden="1">
       <c r="A205">
         <v>204</v>
       </c>
@@ -11817,7 +11861,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="206" spans="1:23">
+    <row r="206" spans="1:23" hidden="1">
       <c r="A206">
         <v>205</v>
       </c>
@@ -11852,7 +11896,7 @@
       </c>
       <c r="W206" s="3"/>
     </row>
-    <row r="207" spans="1:23">
+    <row r="207" spans="1:23" hidden="1">
       <c r="A207">
         <v>206</v>
       </c>
@@ -11891,7 +11935,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="208" spans="1:23">
+    <row r="208" spans="1:23" hidden="1">
       <c r="A208">
         <v>207</v>
       </c>
@@ -11930,7 +11974,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="209" spans="1:23">
+    <row r="209" spans="1:23" hidden="1">
       <c r="A209">
         <v>208</v>
       </c>
@@ -11970,7 +12014,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="210" spans="1:23">
+    <row r="210" spans="1:23" hidden="1">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12005,7 +12049,7 @@
       </c>
       <c r="W210" s="3"/>
     </row>
-    <row r="211" spans="1:23">
+    <row r="211" spans="1:23" hidden="1">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12043,7 +12087,7 @@
       </c>
       <c r="W211" s="3"/>
     </row>
-    <row r="212" spans="1:23">
+    <row r="212" spans="1:23" hidden="1">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12081,7 +12125,7 @@
       </c>
       <c r="W212" s="3"/>
     </row>
-    <row r="213" spans="1:23">
+    <row r="213" spans="1:23" hidden="1">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12119,7 +12163,7 @@
       </c>
       <c r="W213" s="3"/>
     </row>
-    <row r="214" spans="1:23">
+    <row r="214" spans="1:23" hidden="1">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12156,7 +12200,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="215" spans="1:23">
+    <row r="215" spans="1:23" hidden="1">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12191,7 +12235,7 @@
       </c>
       <c r="W215" s="3"/>
     </row>
-    <row r="216" spans="1:23">
+    <row r="216" spans="1:23" hidden="1">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12226,7 +12270,7 @@
       </c>
       <c r="W216" s="3"/>
     </row>
-    <row r="217" spans="1:23">
+    <row r="217" spans="1:23" hidden="1">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12263,7 +12307,7 @@
       </c>
       <c r="W217" s="3"/>
     </row>
-    <row r="218" spans="1:23">
+    <row r="218" spans="1:23" hidden="1">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12300,7 +12344,7 @@
       </c>
       <c r="W218" s="3"/>
     </row>
-    <row r="219" spans="1:23">
+    <row r="219" spans="1:23" hidden="1">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12339,7 +12383,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="220" spans="1:23">
+    <row r="220" spans="1:23" hidden="1">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12376,7 +12420,7 @@
       </c>
       <c r="W220" s="3"/>
     </row>
-    <row r="221" spans="1:23">
+    <row r="221" spans="1:23" hidden="1">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12415,7 +12459,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:23">
+    <row r="222" spans="1:23" hidden="1">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12456,7 +12500,7 @@
       </c>
       <c r="W222" s="3"/>
     </row>
-    <row r="223" spans="1:23">
+    <row r="223" spans="1:23" hidden="1">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12496,7 +12540,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="224" spans="1:23">
+    <row r="224" spans="1:23" hidden="1">
       <c r="A224">
         <v>224</v>
       </c>
@@ -12536,7 +12580,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="225" spans="1:23">
+    <row r="225" spans="1:23" hidden="1">
       <c r="A225">
         <v>225</v>
       </c>
@@ -12579,7 +12623,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="226" spans="1:23">
+    <row r="226" spans="1:23" hidden="1">
       <c r="A226">
         <v>226</v>
       </c>
@@ -12619,7 +12663,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="227" spans="1:23">
+    <row r="227" spans="1:23" hidden="1">
       <c r="A227">
         <v>227</v>
       </c>
@@ -12659,7 +12703,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="228" spans="1:23">
+    <row r="228" spans="1:23" hidden="1">
       <c r="A228">
         <v>228</v>
       </c>
@@ -12696,7 +12740,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="229" spans="1:23">
+    <row r="229" spans="1:23" hidden="1">
       <c r="A229">
         <v>229</v>
       </c>
@@ -12739,7 +12783,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="230" spans="1:23">
+    <row r="230" spans="1:23" hidden="1">
       <c r="A230">
         <v>230</v>
       </c>
@@ -12779,7 +12823,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="231" spans="1:23">
+    <row r="231" spans="1:23" hidden="1">
       <c r="A231">
         <v>231</v>
       </c>
@@ -12819,7 +12863,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="232" spans="1:23">
+    <row r="232" spans="1:23" hidden="1">
       <c r="A232">
         <v>232</v>
       </c>
@@ -12856,7 +12900,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="233" spans="1:23">
+    <row r="233" spans="1:23" hidden="1">
       <c r="A233">
         <v>233</v>
       </c>
@@ -12899,7 +12943,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="234" spans="1:23">
+    <row r="234" spans="1:23" hidden="1">
       <c r="A234">
         <v>234</v>
       </c>
@@ -12938,7 +12982,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="235" spans="1:23">
+    <row r="235" spans="1:23" hidden="1">
       <c r="A235">
         <v>235</v>
       </c>
@@ -12977,7 +13021,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="236" spans="1:23">
+    <row r="236" spans="1:23" hidden="1">
       <c r="A236">
         <v>236</v>
       </c>
@@ -13018,7 +13062,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="237" spans="1:23">
+    <row r="237" spans="1:23" hidden="1">
       <c r="A237">
         <v>237</v>
       </c>
@@ -13055,7 +13099,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="238" spans="1:23">
+    <row r="238" spans="1:23" hidden="1">
       <c r="A238">
         <v>238</v>
       </c>
@@ -13095,7 +13139,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="239" spans="1:23">
+    <row r="239" spans="1:23" hidden="1">
       <c r="A239">
         <v>239</v>
       </c>
@@ -13280,7 +13324,7 @@
       </c>
       <c r="W243" s="3"/>
     </row>
-    <row r="244" spans="1:23">
+    <row r="244" spans="1:23" hidden="1">
       <c r="A244">
         <v>244</v>
       </c>
@@ -13319,7 +13363,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="245" spans="1:23">
+    <row r="245" spans="1:23" hidden="1">
       <c r="A245">
         <v>246</v>
       </c>
@@ -13436,7 +13480,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="248" spans="1:23">
+    <row r="248" spans="1:23" hidden="1">
       <c r="A248">
         <v>248</v>
       </c>
@@ -13473,7 +13517,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="249" spans="1:23">
+    <row r="249" spans="1:23" hidden="1">
       <c r="A249">
         <v>249</v>
       </c>
@@ -13512,7 +13556,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="250" spans="1:23">
+    <row r="250" spans="1:23" hidden="1">
       <c r="A250">
         <v>251</v>
       </c>
@@ -13555,7 +13599,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="251" spans="1:23">
+    <row r="251" spans="1:23" hidden="1">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13631,7 +13675,7 @@
       </c>
       <c r="W252" s="3"/>
     </row>
-    <row r="253" spans="1:23">
+    <row r="253" spans="1:23" hidden="1">
       <c r="A253">
         <v>256</v>
       </c>
@@ -13671,7 +13715,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="254" spans="1:23">
+    <row r="254" spans="1:23" hidden="1">
       <c r="A254">
         <v>253</v>
       </c>
@@ -13708,7 +13752,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="255" spans="1:23">
+    <row r="255" spans="1:23" hidden="1">
       <c r="A255">
         <v>255</v>
       </c>
@@ -13745,7 +13789,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="256" spans="1:23">
+    <row r="256" spans="1:23" hidden="1">
       <c r="A256">
         <v>254</v>
       </c>
@@ -13782,7 +13826,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="257" spans="1:23">
+    <row r="257" spans="1:23" hidden="1">
       <c r="A257">
         <v>257</v>
       </c>
@@ -13825,7 +13869,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="258" spans="1:23">
+    <row r="258" spans="1:23" hidden="1">
       <c r="A258">
         <v>258</v>
       </c>
@@ -13862,7 +13906,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="259" spans="1:23">
+    <row r="259" spans="1:23" hidden="1">
       <c r="A259">
         <v>259</v>
       </c>
@@ -13902,7 +13946,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="260" spans="1:23">
+    <row r="260" spans="1:23" hidden="1">
       <c r="A260">
         <v>260</v>
       </c>
@@ -13942,7 +13986,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="261" spans="1:23">
+    <row r="261" spans="1:23" hidden="1">
       <c r="A261">
         <v>261</v>
       </c>
@@ -13979,7 +14023,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="262" spans="1:23">
+    <row r="262" spans="1:23" hidden="1">
       <c r="A262">
         <v>262</v>
       </c>
@@ -14019,7 +14063,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="263" spans="1:23">
+    <row r="263" spans="1:23" hidden="1">
       <c r="A263">
         <v>263</v>
       </c>
@@ -14059,7 +14103,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="264" spans="1:23">
+    <row r="264" spans="1:23" hidden="1">
       <c r="A264">
         <v>264</v>
       </c>
@@ -14099,7 +14143,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="265" spans="1:23">
+    <row r="265" spans="1:23" hidden="1">
       <c r="A265">
         <v>265</v>
       </c>
@@ -14136,7 +14180,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" hidden="1">
       <c r="A266">
         <v>266</v>
       </c>
@@ -14176,7 +14220,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="267" spans="1:23">
+    <row r="267" spans="1:23" hidden="1">
       <c r="A267">
         <v>267</v>
       </c>
@@ -14213,7 +14257,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" hidden="1">
       <c r="A268">
         <v>268</v>
       </c>
@@ -14250,7 +14294,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" hidden="1">
       <c r="A269">
         <v>269</v>
       </c>
@@ -14293,7 +14337,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="270" spans="1:23">
+    <row r="270" spans="1:23" hidden="1">
       <c r="A270">
         <v>270</v>
       </c>
@@ -14373,7 +14417,7 @@
       </c>
       <c r="W271" s="3"/>
     </row>
-    <row r="272" spans="1:23">
+    <row r="272" spans="1:23" hidden="1">
       <c r="A272">
         <v>272</v>
       </c>
@@ -14457,7 +14501,7 @@
       </c>
       <c r="W273" s="3"/>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" hidden="1">
       <c r="A274">
         <v>273</v>
       </c>
@@ -14500,7 +14544,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" hidden="1">
       <c r="A275">
         <v>274</v>
       </c>
@@ -14540,7 +14584,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" hidden="1">
       <c r="A276">
         <v>275</v>
       </c>
@@ -14694,7 +14738,7 @@
       </c>
       <c r="W279" s="3"/>
     </row>
-    <row r="280" spans="1:23">
+    <row r="280" spans="1:23" hidden="1">
       <c r="A280">
         <v>280</v>
       </c>
@@ -14737,7 +14781,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="281" spans="1:23">
+    <row r="281" spans="1:23" hidden="1">
       <c r="A281">
         <v>281</v>
       </c>
@@ -14777,7 +14821,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="282" spans="1:23">
+    <row r="282" spans="1:23" hidden="1">
       <c r="A282">
         <v>282</v>
       </c>
@@ -14817,7 +14861,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="283" spans="1:23">
+    <row r="283" spans="1:23" hidden="1">
       <c r="A283">
         <v>283</v>
       </c>
@@ -14857,7 +14901,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="284" spans="1:23">
+    <row r="284" spans="1:23" hidden="1">
       <c r="A284">
         <v>284</v>
       </c>
@@ -14897,7 +14941,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="285" spans="1:23">
+    <row r="285" spans="1:23" hidden="1">
       <c r="A285">
         <v>285</v>
       </c>
@@ -14934,7 +14978,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="286" spans="1:23">
+    <row r="286" spans="1:23" hidden="1">
       <c r="A286">
         <v>286</v>
       </c>
@@ -14977,7 +15021,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="287" spans="1:23">
+    <row r="287" spans="1:23" hidden="1">
       <c r="A287">
         <v>287</v>
       </c>
@@ -15014,7 +15058,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="288" spans="1:23">
+    <row r="288" spans="1:23" hidden="1">
       <c r="A288">
         <v>288</v>
       </c>
@@ -15057,7 +15101,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="289" spans="1:23">
+    <row r="289" spans="1:23" hidden="1">
       <c r="A289">
         <v>289</v>
       </c>
@@ -15097,7 +15141,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="290" spans="1:23">
+    <row r="290" spans="1:23" hidden="1">
       <c r="A290">
         <v>290</v>
       </c>
@@ -15134,7 +15178,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="291" spans="1:23">
+    <row r="291" spans="1:23" hidden="1">
       <c r="A291">
         <v>291</v>
       </c>
@@ -15177,7 +15221,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="292" spans="1:23">
+    <row r="292" spans="1:23" hidden="1">
       <c r="A292">
         <v>292</v>
       </c>
@@ -15220,7 +15264,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="293" spans="1:23">
+    <row r="293" spans="1:23" hidden="1">
       <c r="A293">
         <v>294</v>
       </c>
@@ -15259,7 +15303,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="294" spans="1:23">
+    <row r="294" spans="1:23" hidden="1">
       <c r="A294">
         <v>293</v>
       </c>
@@ -15302,7 +15346,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="295" spans="1:23">
+    <row r="295" spans="1:23" hidden="1">
       <c r="A295">
         <v>295</v>
       </c>
@@ -15339,7 +15383,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" hidden="1">
       <c r="A296">
         <v>296</v>
       </c>
@@ -15378,7 +15422,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="297" spans="1:23">
+    <row r="297" spans="1:23" hidden="1">
       <c r="A297">
         <v>297</v>
       </c>
@@ -15417,7 +15461,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="298" spans="1:23">
+    <row r="298" spans="1:23" hidden="1">
       <c r="A298">
         <v>298</v>
       </c>
@@ -15456,7 +15500,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="299" spans="1:23">
+    <row r="299" spans="1:23" hidden="1">
       <c r="A299">
         <v>299</v>
       </c>
@@ -15495,7 +15539,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="300" spans="1:23">
+    <row r="300" spans="1:23" hidden="1">
       <c r="A300">
         <v>300</v>
       </c>
@@ -15534,7 +15578,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="301" spans="1:23">
+    <row r="301" spans="1:23" hidden="1">
       <c r="A301">
         <v>301</v>
       </c>
@@ -15573,7 +15617,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="302" spans="1:23">
+    <row r="302" spans="1:23" hidden="1">
       <c r="A302">
         <v>302</v>
       </c>
@@ -15612,7 +15656,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="303" spans="1:23">
+    <row r="303" spans="1:23" hidden="1">
       <c r="A303">
         <v>303</v>
       </c>
@@ -15651,7 +15695,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="304" spans="1:23">
+    <row r="304" spans="1:23" hidden="1">
       <c r="A304">
         <v>304</v>
       </c>
@@ -15690,7 +15734,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="305" spans="1:23">
+    <row r="305" spans="1:23" hidden="1">
       <c r="A305">
         <v>305</v>
       </c>
@@ -15729,7 +15773,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="306" spans="1:23">
+    <row r="306" spans="1:23" hidden="1">
       <c r="A306">
         <v>306</v>
       </c>
@@ -15767,7 +15811,7 @@
       </c>
       <c r="W306" s="3"/>
     </row>
-    <row r="307" spans="1:23">
+    <row r="307" spans="1:23" hidden="1">
       <c r="A307">
         <v>307</v>
       </c>
@@ -15806,7 +15850,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="308" spans="1:23">
+    <row r="308" spans="1:23" hidden="1">
       <c r="A308">
         <v>308</v>
       </c>
@@ -15845,7 +15889,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="309" spans="1:23">
+    <row r="309" spans="1:23" hidden="1">
       <c r="A309">
         <v>309</v>
       </c>
@@ -15882,7 +15926,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="310" spans="1:23">
+    <row r="310" spans="1:23" hidden="1">
       <c r="A310">
         <v>310</v>
       </c>
@@ -15919,7 +15963,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="311" spans="1:23">
+    <row r="311" spans="1:23" hidden="1">
       <c r="A311">
         <v>311</v>
       </c>
@@ -15956,7 +16000,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="312" spans="1:23">
+    <row r="312" spans="1:23" hidden="1">
       <c r="A312">
         <v>312</v>
       </c>
@@ -15996,7 +16040,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="313" spans="1:23">
+    <row r="313" spans="1:23" hidden="1">
       <c r="A313">
         <v>313</v>
       </c>
@@ -16033,7 +16077,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="314" spans="1:23">
+    <row r="314" spans="1:23" hidden="1">
       <c r="A314">
         <v>314</v>
       </c>
@@ -16068,7 +16112,7 @@
       </c>
       <c r="W314" s="3"/>
     </row>
-    <row r="315" spans="1:23">
+    <row r="315" spans="1:23" hidden="1">
       <c r="A315">
         <v>315</v>
       </c>
@@ -16105,7 +16149,7 @@
       </c>
       <c r="W315" s="3"/>
     </row>
-    <row r="316" spans="1:23">
+    <row r="316" spans="1:23" hidden="1">
       <c r="A316">
         <v>316</v>
       </c>
@@ -16140,7 +16184,7 @@
       </c>
       <c r="W316" s="3"/>
     </row>
-    <row r="317" spans="1:23">
+    <row r="317" spans="1:23" hidden="1">
       <c r="A317">
         <v>317</v>
       </c>
@@ -16177,7 +16221,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="318" spans="1:23">
+    <row r="318" spans="1:23" hidden="1">
       <c r="A318">
         <v>318</v>
       </c>
@@ -16212,7 +16256,7 @@
       </c>
       <c r="W318" s="3"/>
     </row>
-    <row r="319" spans="1:23">
+    <row r="319" spans="1:23" hidden="1">
       <c r="A319">
         <v>319</v>
       </c>
@@ -16251,7 +16295,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="320" spans="1:23">
+    <row r="320" spans="1:23" hidden="1">
       <c r="A320">
         <v>320</v>
       </c>
@@ -16286,7 +16330,7 @@
       </c>
       <c r="W320" s="3"/>
     </row>
-    <row r="321" spans="1:23">
+    <row r="321" spans="1:23" hidden="1">
       <c r="A321">
         <v>321</v>
       </c>
@@ -16323,7 +16367,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:23" hidden="1">
       <c r="A322">
         <v>322</v>
       </c>
@@ -16360,7 +16404,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="323" spans="1:23">
+    <row r="323" spans="1:23" hidden="1">
       <c r="A323">
         <v>323</v>
       </c>
@@ -16397,7 +16441,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="324" spans="1:23">
+    <row r="324" spans="1:23" hidden="1">
       <c r="A324">
         <v>324</v>
       </c>
@@ -16436,7 +16480,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="325" spans="1:23">
+    <row r="325" spans="1:23" hidden="1">
       <c r="A325">
         <v>325</v>
       </c>
@@ -16473,7 +16517,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="326" spans="1:23">
+    <row r="326" spans="1:23" hidden="1">
       <c r="A326">
         <v>326</v>
       </c>
@@ -16547,7 +16591,7 @@
       </c>
       <c r="W327" s="3"/>
     </row>
-    <row r="328" spans="1:23">
+    <row r="328" spans="1:23" hidden="1">
       <c r="A328">
         <v>328</v>
       </c>
@@ -16582,7 +16626,7 @@
       </c>
       <c r="W328" s="3"/>
     </row>
-    <row r="329" spans="1:23">
+    <row r="329" spans="1:23" hidden="1">
       <c r="A329">
         <v>329</v>
       </c>
@@ -16617,7 +16661,7 @@
       </c>
       <c r="W329" s="3"/>
     </row>
-    <row r="330" spans="1:23">
+    <row r="330" spans="1:23" hidden="1">
       <c r="A330">
         <v>330</v>
       </c>
@@ -16652,7 +16696,7 @@
       </c>
       <c r="W330" s="3"/>
     </row>
-    <row r="331" spans="1:23">
+    <row r="331" spans="1:23" hidden="1">
       <c r="A331">
         <v>331</v>
       </c>
@@ -16687,7 +16731,7 @@
       </c>
       <c r="W331" s="3"/>
     </row>
-    <row r="332" spans="1:23">
+    <row r="332" spans="1:23" hidden="1">
       <c r="A332">
         <v>332</v>
       </c>
@@ -16726,7 +16770,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="333" spans="1:23">
+    <row r="333" spans="1:23" hidden="1">
       <c r="A333">
         <v>333</v>
       </c>
@@ -16763,7 +16807,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="334" spans="1:23">
+    <row r="334" spans="1:23" hidden="1">
       <c r="A334">
         <v>334</v>
       </c>
@@ -16803,7 +16847,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="335" spans="1:23">
+    <row r="335" spans="1:23" hidden="1">
       <c r="A335">
         <v>335</v>
       </c>
@@ -16842,7 +16886,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="336" spans="1:23">
+    <row r="336" spans="1:23" hidden="1">
       <c r="A336">
         <v>336</v>
       </c>
@@ -16879,7 +16923,7 @@
       </c>
       <c r="W336" s="3"/>
     </row>
-    <row r="337" spans="1:23">
+    <row r="337" spans="1:23" hidden="1">
       <c r="A337">
         <v>337</v>
       </c>
@@ -16916,7 +16960,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="338" spans="1:23">
+    <row r="338" spans="1:23" hidden="1">
       <c r="A338">
         <v>338</v>
       </c>
@@ -16953,7 +16997,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="339" spans="1:23">
+    <row r="339" spans="1:23" hidden="1">
       <c r="A339">
         <v>339</v>
       </c>
@@ -16990,7 +17034,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="340" spans="1:23">
+    <row r="340" spans="1:23" hidden="1">
       <c r="A340">
         <v>340</v>
       </c>
@@ -17027,7 +17071,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="341" spans="1:23">
+    <row r="341" spans="1:23" hidden="1">
       <c r="A341">
         <v>341</v>
       </c>
@@ -17070,7 +17114,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="342" spans="1:23">
+    <row r="342" spans="1:23" hidden="1">
       <c r="A342">
         <v>342</v>
       </c>
@@ -17107,7 +17151,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="343" spans="1:23">
+    <row r="343" spans="1:23" hidden="1">
       <c r="A343">
         <v>343</v>
       </c>
@@ -17142,7 +17186,7 @@
       </c>
       <c r="W343" s="3"/>
     </row>
-    <row r="344" spans="1:23">
+    <row r="344" spans="1:23" hidden="1">
       <c r="A344">
         <v>344</v>
       </c>
@@ -17183,7 +17227,7 @@
       </c>
       <c r="W344" s="3"/>
     </row>
-    <row r="345" spans="1:23">
+    <row r="345" spans="1:23" hidden="1">
       <c r="A345">
         <v>345</v>
       </c>
@@ -17226,7 +17270,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="346" spans="1:23">
+    <row r="346" spans="1:23" hidden="1">
       <c r="A346">
         <v>346</v>
       </c>
@@ -17269,7 +17313,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="347" spans="1:23">
+    <row r="347" spans="1:23" hidden="1">
       <c r="A347">
         <v>347</v>
       </c>
@@ -17308,7 +17352,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="348" spans="1:23">
+    <row r="348" spans="1:23" hidden="1">
       <c r="A348">
         <v>348</v>
       </c>
@@ -17351,7 +17395,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="349" spans="1:23">
+    <row r="349" spans="1:23" hidden="1">
       <c r="A349">
         <v>349</v>
       </c>
@@ -17388,7 +17432,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="350" spans="1:23">
+    <row r="350" spans="1:23" hidden="1">
       <c r="A350">
         <v>350</v>
       </c>
@@ -17428,7 +17472,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="351" spans="1:23">
+    <row r="351" spans="1:23" hidden="1">
       <c r="A351">
         <v>351</v>
       </c>
@@ -17463,7 +17507,7 @@
       </c>
       <c r="W351" s="3"/>
     </row>
-    <row r="352" spans="1:23">
+    <row r="352" spans="1:23" hidden="1">
       <c r="A352">
         <v>352</v>
       </c>
@@ -17506,7 +17550,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="353" spans="1:23">
+    <row r="353" spans="1:23" hidden="1">
       <c r="A353">
         <v>353</v>
       </c>
@@ -17543,7 +17587,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="354" spans="1:23">
+    <row r="354" spans="1:23" hidden="1">
       <c r="A354">
         <v>354</v>
       </c>
@@ -17582,7 +17626,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="355" spans="1:23">
+    <row r="355" spans="1:23" hidden="1">
       <c r="A355">
         <v>355</v>
       </c>
@@ -17619,7 +17663,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="356" spans="1:23">
+    <row r="356" spans="1:23" hidden="1">
       <c r="A356">
         <v>356</v>
       </c>
@@ -17656,7 +17700,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="357" spans="1:23">
+    <row r="357" spans="1:23" hidden="1">
       <c r="A357">
         <v>357</v>
       </c>
@@ -17695,7 +17739,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="358" spans="1:23">
+    <row r="358" spans="1:23" hidden="1">
       <c r="A358">
         <v>358</v>
       </c>
@@ -17734,7 +17778,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="359" spans="1:23">
+    <row r="359" spans="1:23" hidden="1">
       <c r="A359">
         <v>359</v>
       </c>
@@ -17774,7 +17818,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="360" spans="1:23">
+    <row r="360" spans="1:23" hidden="1">
       <c r="A360">
         <v>360</v>
       </c>
@@ -17817,7 +17861,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="361" spans="1:23">
+    <row r="361" spans="1:23" hidden="1">
       <c r="A361">
         <v>361</v>
       </c>
@@ -17854,7 +17898,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="362" spans="1:23">
+    <row r="362" spans="1:23" hidden="1">
       <c r="A362">
         <v>362</v>
       </c>
@@ -17893,7 +17937,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="363" spans="1:23">
+    <row r="363" spans="1:23" hidden="1">
       <c r="A363">
         <v>363</v>
       </c>
@@ -17932,7 +17976,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="364" spans="1:23">
+    <row r="364" spans="1:23" hidden="1">
       <c r="A364">
         <v>364</v>
       </c>
@@ -17969,7 +18013,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="365" spans="1:23">
+    <row r="365" spans="1:23" hidden="1">
       <c r="A365">
         <v>365</v>
       </c>
@@ -18008,7 +18052,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="366" spans="1:23">
+    <row r="366" spans="1:23" hidden="1">
       <c r="A366">
         <v>366</v>
       </c>
@@ -18047,7 +18091,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="367" spans="1:23">
+    <row r="367" spans="1:23" hidden="1">
       <c r="A367">
         <v>367</v>
       </c>
@@ -18084,7 +18128,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="368" spans="1:23">
+    <row r="368" spans="1:23" hidden="1">
       <c r="A368">
         <v>368</v>
       </c>
@@ -18121,7 +18165,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="369" spans="1:23">
+    <row r="369" spans="1:23" hidden="1">
       <c r="A369">
         <v>369</v>
       </c>
@@ -18158,7 +18202,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="370" spans="1:23">
+    <row r="370" spans="1:23" hidden="1">
       <c r="A370">
         <v>370</v>
       </c>
@@ -18201,7 +18245,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="371" spans="1:23">
+    <row r="371" spans="1:23" hidden="1">
       <c r="A371">
         <v>371</v>
       </c>
@@ -18238,7 +18282,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="372" spans="1:23">
+    <row r="372" spans="1:23" hidden="1">
       <c r="A372">
         <v>372</v>
       </c>
@@ -18275,7 +18319,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="373" spans="1:23">
+    <row r="373" spans="1:23" hidden="1">
       <c r="A373">
         <v>373</v>
       </c>
@@ -18318,7 +18362,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="374" spans="1:23">
+    <row r="374" spans="1:23" hidden="1">
       <c r="A374">
         <v>374</v>
       </c>
@@ -18355,7 +18399,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="375" spans="1:23">
+    <row r="375" spans="1:23" hidden="1">
       <c r="A375">
         <v>375</v>
       </c>
@@ -18398,7 +18442,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="376" spans="1:23">
+    <row r="376" spans="1:23" hidden="1">
       <c r="A376">
         <v>376</v>
       </c>
@@ -18438,7 +18482,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="377" spans="1:23">
+    <row r="377" spans="1:23" hidden="1">
       <c r="A377">
         <v>377</v>
       </c>
@@ -18475,7 +18519,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="378" spans="1:23">
+    <row r="378" spans="1:23" hidden="1">
       <c r="A378">
         <v>378</v>
       </c>
@@ -18512,7 +18556,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="379" spans="1:23">
+    <row r="379" spans="1:23" hidden="1">
       <c r="A379">
         <v>379</v>
       </c>
@@ -18549,7 +18593,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="380" spans="1:23">
+    <row r="380" spans="1:23" hidden="1">
       <c r="A380">
         <v>380</v>
       </c>
@@ -18589,7 +18633,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="381" spans="1:23">
+    <row r="381" spans="1:23" hidden="1">
       <c r="A381">
         <v>381</v>
       </c>
@@ -18629,7 +18673,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="382" spans="1:23">
+    <row r="382" spans="1:23" hidden="1">
       <c r="A382">
         <v>382</v>
       </c>
@@ -18666,7 +18710,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="383" spans="1:23">
+    <row r="383" spans="1:23" hidden="1">
       <c r="A383">
         <v>383</v>
       </c>
@@ -18705,7 +18749,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="384" spans="1:23">
+    <row r="384" spans="1:23" hidden="1">
       <c r="A384">
         <v>384</v>
       </c>
@@ -18744,7 +18788,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="385" spans="1:23">
+    <row r="385" spans="1:23" hidden="1">
       <c r="A385">
         <v>385</v>
       </c>
@@ -18783,7 +18827,7 @@
       </c>
       <c r="W385" s="3"/>
     </row>
-    <row r="386" spans="1:23">
+    <row r="386" spans="1:23" hidden="1">
       <c r="A386">
         <v>386</v>
       </c>
@@ -18822,7 +18866,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="387" spans="1:23">
+    <row r="387" spans="1:23" hidden="1">
       <c r="A387">
         <v>387</v>
       </c>
@@ -18862,7 +18906,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="388" spans="1:23">
+    <row r="388" spans="1:23" hidden="1">
       <c r="A388">
         <v>388</v>
       </c>
@@ -18902,7 +18946,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="389" spans="1:23">
+    <row r="389" spans="1:23" hidden="1">
       <c r="A389">
         <v>389</v>
       </c>
@@ -18943,7 +18987,7 @@
       </c>
       <c r="W389" s="3"/>
     </row>
-    <row r="390" spans="1:23">
+    <row r="390" spans="1:23" hidden="1">
       <c r="A390">
         <v>390</v>
       </c>
@@ -18984,7 +19028,7 @@
       </c>
       <c r="W390" s="3"/>
     </row>
-    <row r="391" spans="1:23">
+    <row r="391" spans="1:23" hidden="1">
       <c r="A391">
         <v>391</v>
       </c>
@@ -19025,7 +19069,7 @@
       </c>
       <c r="W391" s="3"/>
     </row>
-    <row r="392" spans="1:23">
+    <row r="392" spans="1:23" hidden="1">
       <c r="A392">
         <v>392</v>
       </c>
@@ -19066,7 +19110,7 @@
       </c>
       <c r="W392" s="3"/>
     </row>
-    <row r="393" spans="1:23">
+    <row r="393" spans="1:23" hidden="1">
       <c r="A393">
         <v>393</v>
       </c>
@@ -19103,7 +19147,7 @@
       </c>
       <c r="W393" s="3"/>
     </row>
-    <row r="394" spans="1:23">
+    <row r="394" spans="1:23" hidden="1">
       <c r="A394">
         <v>394</v>
       </c>
@@ -19138,7 +19182,7 @@
       </c>
       <c r="W394" s="3"/>
     </row>
-    <row r="395" spans="1:23">
+    <row r="395" spans="1:23" hidden="1">
       <c r="A395">
         <v>395</v>
       </c>
@@ -19175,7 +19219,7 @@
       </c>
       <c r="W395" s="3"/>
     </row>
-    <row r="396" spans="1:23">
+    <row r="396" spans="1:23" hidden="1">
       <c r="A396">
         <v>396</v>
       </c>
@@ -19210,7 +19254,7 @@
       </c>
       <c r="W396" s="3"/>
     </row>
-    <row r="397" spans="1:23">
+    <row r="397" spans="1:23" hidden="1">
       <c r="A397">
         <v>397</v>
       </c>
@@ -19245,7 +19289,7 @@
       </c>
       <c r="W397" s="3"/>
     </row>
-    <row r="398" spans="1:23">
+    <row r="398" spans="1:23" hidden="1">
       <c r="A398">
         <v>398</v>
       </c>
@@ -19280,7 +19324,7 @@
       </c>
       <c r="W398" s="3"/>
     </row>
-    <row r="399" spans="1:23">
+    <row r="399" spans="1:23" hidden="1">
       <c r="A399">
         <v>399</v>
       </c>
@@ -19315,7 +19359,7 @@
       </c>
       <c r="W399" s="3"/>
     </row>
-    <row r="400" spans="1:23">
+    <row r="400" spans="1:23" hidden="1">
       <c r="A400">
         <v>400</v>
       </c>
@@ -19356,7 +19400,7 @@
       </c>
       <c r="W400" s="3"/>
     </row>
-    <row r="401" spans="1:23">
+    <row r="401" spans="1:23" hidden="1">
       <c r="A401">
         <v>401</v>
       </c>
@@ -19395,7 +19439,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="402" spans="1:23">
+    <row r="402" spans="1:23" hidden="1">
       <c r="A402">
         <v>402</v>
       </c>
@@ -19434,7 +19478,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="403" spans="1:23">
+    <row r="403" spans="1:23" hidden="1">
       <c r="A403">
         <v>403</v>
       </c>
@@ -19477,7 +19521,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="404" spans="1:23">
+    <row r="404" spans="1:23" hidden="1">
       <c r="A404">
         <v>404</v>
       </c>
@@ -19520,7 +19564,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="405" spans="1:23">
+    <row r="405" spans="1:23" hidden="1">
       <c r="A405">
         <v>405</v>
       </c>
@@ -19563,7 +19607,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="406" spans="1:23">
+    <row r="406" spans="1:23" hidden="1">
       <c r="A406">
         <v>406</v>
       </c>
@@ -19600,7 +19644,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="407" spans="1:23">
+    <row r="407" spans="1:23" hidden="1">
       <c r="A407">
         <v>407</v>
       </c>
@@ -19643,7 +19687,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="408" spans="1:23">
+    <row r="408" spans="1:23" hidden="1">
       <c r="A408">
         <v>408</v>
       </c>
@@ -19686,7 +19730,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="409" spans="1:23">
+    <row r="409" spans="1:23" hidden="1">
       <c r="A409">
         <v>409</v>
       </c>
@@ -19729,7 +19773,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="410" spans="1:23">
+    <row r="410" spans="1:23" hidden="1">
       <c r="A410">
         <v>410</v>
       </c>
@@ -19768,7 +19812,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="411" spans="1:23">
+    <row r="411" spans="1:23" hidden="1">
       <c r="A411">
         <v>411</v>
       </c>
@@ -19807,7 +19851,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="412" spans="1:23">
+    <row r="412" spans="1:23" hidden="1">
       <c r="A412">
         <v>412</v>
       </c>
@@ -19842,7 +19886,7 @@
       </c>
       <c r="W412" s="3"/>
     </row>
-    <row r="413" spans="1:23">
+    <row r="413" spans="1:23" hidden="1">
       <c r="A413">
         <v>413</v>
       </c>
@@ -19881,7 +19925,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="414" spans="1:23">
+    <row r="414" spans="1:23" hidden="1">
       <c r="A414">
         <v>414</v>
       </c>
@@ -19924,7 +19968,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="415" spans="1:23">
+    <row r="415" spans="1:23" hidden="1">
       <c r="A415">
         <v>415</v>
       </c>
@@ -19963,7 +20007,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="416" spans="1:23">
+    <row r="416" spans="1:23" hidden="1">
       <c r="A416">
         <v>416</v>
       </c>
@@ -20006,7 +20050,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="417" spans="1:23">
+    <row r="417" spans="1:23" hidden="1">
       <c r="A417">
         <v>417</v>
       </c>
@@ -20045,7 +20089,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="418" spans="1:23">
+    <row r="418" spans="1:23" hidden="1">
       <c r="A418">
         <v>418</v>
       </c>
@@ -20082,7 +20126,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="419" spans="1:23">
+    <row r="419" spans="1:23" hidden="1">
       <c r="A419">
         <v>419</v>
       </c>
@@ -20125,7 +20169,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="420" spans="1:23">
+    <row r="420" spans="1:23" hidden="1">
       <c r="A420">
         <v>420</v>
       </c>
@@ -20165,7 +20209,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="421" spans="1:23">
+    <row r="421" spans="1:23" hidden="1">
       <c r="A421">
         <v>421</v>
       </c>
@@ -20202,7 +20246,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="422" spans="1:23">
+    <row r="422" spans="1:23" hidden="1">
       <c r="A422">
         <v>422</v>
       </c>
@@ -20245,7 +20289,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="423" spans="1:23">
+    <row r="423" spans="1:23" hidden="1">
       <c r="A423">
         <v>423</v>
       </c>
@@ -20288,7 +20332,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="424" spans="1:23">
+    <row r="424" spans="1:23" hidden="1">
       <c r="A424">
         <v>424</v>
       </c>
@@ -20331,7 +20375,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="425" spans="1:23">
+    <row r="425" spans="1:23" hidden="1">
       <c r="A425">
         <v>425</v>
       </c>
@@ -20372,7 +20416,7 @@
       </c>
       <c r="W425" s="3"/>
     </row>
-    <row r="426" spans="1:23">
+    <row r="426" spans="1:23" hidden="1">
       <c r="A426">
         <v>426</v>
       </c>
@@ -20415,7 +20459,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="427" spans="1:23">
+    <row r="427" spans="1:23" hidden="1">
       <c r="A427">
         <v>427</v>
       </c>
@@ -20458,7 +20502,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="428" spans="1:23">
+    <row r="428" spans="1:23" hidden="1">
       <c r="A428">
         <v>428</v>
       </c>
@@ -20501,7 +20545,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="429" spans="1:23">
+    <row r="429" spans="1:23" hidden="1">
       <c r="A429">
         <v>429</v>
       </c>
@@ -20538,7 +20582,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="430" spans="1:23">
+    <row r="430" spans="1:23" hidden="1">
       <c r="A430">
         <v>430</v>
       </c>
@@ -20577,7 +20621,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="431" spans="1:23">
+    <row r="431" spans="1:23" hidden="1">
       <c r="A431">
         <v>431</v>
       </c>
@@ -20616,7 +20660,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="432" spans="1:23">
+    <row r="432" spans="1:23" hidden="1">
       <c r="A432">
         <v>432</v>
       </c>
@@ -20654,7 +20698,7 @@
       </c>
       <c r="W432" s="3"/>
     </row>
-    <row r="433" spans="1:23">
+    <row r="433" spans="1:23" hidden="1">
       <c r="A433">
         <v>433</v>
       </c>
@@ -20692,7 +20736,7 @@
       </c>
       <c r="W433" s="3"/>
     </row>
-    <row r="434" spans="1:23">
+    <row r="434" spans="1:23" hidden="1">
       <c r="A434">
         <v>434</v>
       </c>
@@ -20730,7 +20774,7 @@
       </c>
       <c r="W434" s="3"/>
     </row>
-    <row r="435" spans="1:23">
+    <row r="435" spans="1:23" hidden="1">
       <c r="A435">
         <v>435</v>
       </c>
@@ -20768,7 +20812,7 @@
       </c>
       <c r="W435" s="3"/>
     </row>
-    <row r="436" spans="1:23">
+    <row r="436" spans="1:23" hidden="1">
       <c r="A436">
         <v>436</v>
       </c>
@@ -20806,7 +20850,7 @@
       </c>
       <c r="W436" s="3"/>
     </row>
-    <row r="437" spans="1:23">
+    <row r="437" spans="1:23" hidden="1">
       <c r="A437">
         <v>437</v>
       </c>
@@ -20841,7 +20885,7 @@
       </c>
       <c r="W437" s="3"/>
     </row>
-    <row r="438" spans="1:23">
+    <row r="438" spans="1:23" hidden="1">
       <c r="A438">
         <v>438</v>
       </c>
@@ -20878,7 +20922,7 @@
       </c>
       <c r="W438" s="3"/>
     </row>
-    <row r="439" spans="1:23">
+    <row r="439" spans="1:23" hidden="1">
       <c r="A439">
         <v>439</v>
       </c>
@@ -20915,7 +20959,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="440" spans="1:23">
+    <row r="440" spans="1:23" hidden="1">
       <c r="A440">
         <v>440</v>
       </c>
@@ -20952,7 +20996,7 @@
       </c>
       <c r="W440" s="3"/>
     </row>
-    <row r="441" spans="1:23">
+    <row r="441" spans="1:23" hidden="1">
       <c r="A441">
         <v>441</v>
       </c>
@@ -20989,7 +21033,7 @@
       </c>
       <c r="W441" s="3"/>
     </row>
-    <row r="442" spans="1:23">
+    <row r="442" spans="1:23" hidden="1">
       <c r="A442">
         <v>442</v>
       </c>
@@ -21030,7 +21074,7 @@
       </c>
       <c r="W442" s="3"/>
     </row>
-    <row r="443" spans="1:23">
+    <row r="443" spans="1:23" hidden="1">
       <c r="A443">
         <v>443</v>
       </c>
@@ -21069,7 +21113,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="444" spans="1:23">
+    <row r="444" spans="1:23" hidden="1">
       <c r="A444">
         <v>444</v>
       </c>
@@ -21110,7 +21154,7 @@
       </c>
       <c r="W444" s="3"/>
     </row>
-    <row r="445" spans="1:23">
+    <row r="445" spans="1:23" hidden="1">
       <c r="A445">
         <v>445</v>
       </c>
@@ -21150,7 +21194,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="446" spans="1:23">
+    <row r="446" spans="1:23" hidden="1">
       <c r="A446">
         <v>446</v>
       </c>
@@ -21190,7 +21234,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="447" spans="1:23">
+    <row r="447" spans="1:23" hidden="1">
       <c r="A447">
         <v>447</v>
       </c>
@@ -21227,7 +21271,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="448" spans="1:23">
+    <row r="448" spans="1:23" hidden="1">
       <c r="A448">
         <v>448</v>
       </c>
@@ -21266,7 +21310,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="449" spans="1:23">
+    <row r="449" spans="1:23" hidden="1">
       <c r="A449">
         <v>449</v>
       </c>
@@ -21305,7 +21349,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="450" spans="1:23">
+    <row r="450" spans="1:23" hidden="1">
       <c r="A450">
         <v>450</v>
       </c>
@@ -21344,7 +21388,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="451" spans="1:23">
+    <row r="451" spans="1:23" hidden="1">
       <c r="A451">
         <v>451</v>
       </c>
@@ -21384,7 +21428,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="452" spans="1:23">
+    <row r="452" spans="1:23" hidden="1">
       <c r="A452">
         <v>452</v>
       </c>
@@ -21421,7 +21465,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="453" spans="1:23">
+    <row r="453" spans="1:23" hidden="1">
       <c r="A453">
         <v>453</v>
       </c>
@@ -21456,7 +21500,7 @@
       </c>
       <c r="W453" s="3"/>
     </row>
-    <row r="454" spans="1:23">
+    <row r="454" spans="1:23" hidden="1">
       <c r="A454">
         <v>454</v>
       </c>
@@ -21495,7 +21539,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="455" spans="1:23">
+    <row r="455" spans="1:23" hidden="1">
       <c r="A455">
         <v>455</v>
       </c>
@@ -21534,7 +21578,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="456" spans="1:23">
+    <row r="456" spans="1:23" hidden="1">
       <c r="A456">
         <v>456</v>
       </c>
@@ -21573,7 +21617,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="457" spans="1:23">
+    <row r="457" spans="1:23" hidden="1">
       <c r="A457">
         <v>457</v>
       </c>
@@ -21612,7 +21656,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="458" spans="1:23">
+    <row r="458" spans="1:23" hidden="1">
       <c r="A458">
         <v>458</v>
       </c>
@@ -21651,7 +21695,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="459" spans="1:23">
+    <row r="459" spans="1:23" hidden="1">
       <c r="A459">
         <v>459</v>
       </c>
@@ -21690,7 +21734,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="460" spans="1:23">
+    <row r="460" spans="1:23" hidden="1">
       <c r="A460">
         <v>460</v>
       </c>
@@ -21729,7 +21773,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="461" spans="1:23">
+    <row r="461" spans="1:23" hidden="1">
       <c r="A461">
         <v>461</v>
       </c>
@@ -21768,7 +21812,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="462" spans="1:23">
+    <row r="462" spans="1:23" hidden="1">
       <c r="A462">
         <v>462</v>
       </c>
@@ -21807,7 +21851,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="463" spans="1:23">
+    <row r="463" spans="1:23" hidden="1">
       <c r="A463">
         <v>463</v>
       </c>
@@ -21846,7 +21890,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="464" spans="1:23">
+    <row r="464" spans="1:23" hidden="1">
       <c r="A464">
         <v>464</v>
       </c>
@@ -21885,7 +21929,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="465" spans="1:23">
+    <row r="465" spans="1:23" hidden="1">
       <c r="A465">
         <v>465</v>
       </c>
@@ -21924,7 +21968,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="466" spans="1:23">
+    <row r="466" spans="1:23" hidden="1">
       <c r="A466">
         <v>466</v>
       </c>
@@ -21963,7 +22007,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="467" spans="1:23">
+    <row r="467" spans="1:23" hidden="1">
       <c r="A467">
         <v>467</v>
       </c>
@@ -22002,7 +22046,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="468" spans="1:23">
+    <row r="468" spans="1:23" hidden="1">
       <c r="A468">
         <v>468</v>
       </c>
@@ -22041,7 +22085,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="469" spans="1:23">
+    <row r="469" spans="1:23" hidden="1">
       <c r="A469">
         <v>469</v>
       </c>
@@ -22080,7 +22124,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="470" spans="1:23">
+    <row r="470" spans="1:23" hidden="1">
       <c r="A470">
         <v>470</v>
       </c>
@@ -22117,7 +22161,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="471" spans="1:23">
+    <row r="471" spans="1:23" hidden="1">
       <c r="A471">
         <v>471</v>
       </c>
@@ -22157,7 +22201,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="472" spans="1:23">
+    <row r="472" spans="1:23" hidden="1">
       <c r="A472">
         <v>472</v>
       </c>
@@ -22194,7 +22238,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="473" spans="1:23">
+    <row r="473" spans="1:23" hidden="1">
       <c r="A473">
         <v>473</v>
       </c>
@@ -22233,7 +22277,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="474" spans="1:23">
+    <row r="474" spans="1:23" hidden="1">
       <c r="A474">
         <v>474</v>
       </c>
@@ -22272,7 +22316,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="475" spans="1:23">
+    <row r="475" spans="1:23" hidden="1">
       <c r="A475">
         <v>475</v>
       </c>
@@ -22309,7 +22353,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="476" spans="1:23">
+    <row r="476" spans="1:23" hidden="1">
       <c r="A476">
         <v>476</v>
       </c>
@@ -22346,7 +22390,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="477" spans="1:23">
+    <row r="477" spans="1:23" hidden="1">
       <c r="A477">
         <v>477</v>
       </c>
@@ -22389,7 +22433,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="478" spans="1:23">
+    <row r="478" spans="1:23" hidden="1">
       <c r="A478">
         <v>478</v>
       </c>
@@ -22428,7 +22472,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="479" spans="1:23">
+    <row r="479" spans="1:23" hidden="1">
       <c r="A479">
         <v>479</v>
       </c>
@@ -22467,7 +22511,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="480" spans="1:23">
+    <row r="480" spans="1:23" hidden="1">
       <c r="A480">
         <v>480</v>
       </c>
@@ -22504,7 +22548,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="481" spans="1:23">
+    <row r="481" spans="1:23" hidden="1">
       <c r="A481">
         <v>481</v>
       </c>
@@ -22541,7 +22585,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="482" spans="1:23">
+    <row r="482" spans="1:23" hidden="1">
       <c r="A482">
         <v>482</v>
       </c>
@@ -22578,7 +22622,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="483" spans="1:23">
+    <row r="483" spans="1:23" hidden="1">
       <c r="A483">
         <v>483</v>
       </c>
@@ -22617,7 +22661,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="484" spans="1:23">
+    <row r="484" spans="1:23" hidden="1">
       <c r="A484">
         <v>484</v>
       </c>
@@ -22656,7 +22700,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="485" spans="1:23">
+    <row r="485" spans="1:23" hidden="1">
       <c r="A485">
         <v>485</v>
       </c>
@@ -22693,7 +22737,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="486" spans="1:23">
+    <row r="486" spans="1:23" hidden="1">
       <c r="A486">
         <v>486</v>
       </c>
@@ -22730,7 +22774,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="487" spans="1:23">
+    <row r="487" spans="1:23" hidden="1">
       <c r="A487">
         <v>487</v>
       </c>
@@ -22767,7 +22811,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="488" spans="1:23">
+    <row r="488" spans="1:23" hidden="1">
       <c r="A488">
         <v>488</v>
       </c>
@@ -22805,7 +22849,7 @@
       </c>
       <c r="W488" s="3"/>
     </row>
-    <row r="489" spans="1:23">
+    <row r="489" spans="1:23" hidden="1">
       <c r="A489">
         <v>489</v>
       </c>
@@ -22844,7 +22888,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="490" spans="1:23">
+    <row r="490" spans="1:23" hidden="1">
       <c r="A490">
         <v>490</v>
       </c>
@@ -22883,7 +22927,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="491" spans="1:23">
+    <row r="491" spans="1:23" hidden="1">
       <c r="A491">
         <v>491</v>
       </c>
@@ -22920,7 +22964,7 @@
       </c>
       <c r="W491" s="3"/>
     </row>
-    <row r="492" spans="1:23">
+    <row r="492" spans="1:23" hidden="1">
       <c r="A492">
         <v>492</v>
       </c>
@@ -22957,7 +23001,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="493" spans="1:23">
+    <row r="493" spans="1:23" hidden="1">
       <c r="A493">
         <v>493</v>
       </c>
@@ -22995,7 +23039,7 @@
       </c>
       <c r="W493" s="3"/>
     </row>
-    <row r="494" spans="1:23">
+    <row r="494" spans="1:23" hidden="1">
       <c r="A494">
         <v>494</v>
       </c>
@@ -23032,7 +23076,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="495" spans="1:23">
+    <row r="495" spans="1:23" hidden="1">
       <c r="A495">
         <v>495</v>
       </c>
@@ -23069,7 +23113,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="496" spans="1:23">
+    <row r="496" spans="1:23" hidden="1">
       <c r="A496">
         <v>496</v>
       </c>
@@ -23112,7 +23156,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="497" spans="1:23">
+    <row r="497" spans="1:23" hidden="1">
       <c r="A497">
         <v>497</v>
       </c>
@@ -23149,7 +23193,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="498" spans="1:23">
+    <row r="498" spans="1:23" hidden="1">
       <c r="A498">
         <v>498</v>
       </c>
@@ -23188,7 +23232,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="499" spans="1:23">
+    <row r="499" spans="1:23" hidden="1">
       <c r="A499">
         <v>499</v>
       </c>
@@ -23231,7 +23275,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="500" spans="1:23">
+    <row r="500" spans="1:23" hidden="1">
       <c r="A500">
         <v>500</v>
       </c>
@@ -23274,7 +23318,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="501" spans="1:23">
+    <row r="501" spans="1:23" hidden="1">
       <c r="A501">
         <v>501</v>
       </c>
@@ -23311,7 +23355,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="502" spans="1:23">
+    <row r="502" spans="1:23" hidden="1">
       <c r="A502">
         <v>502</v>
       </c>
@@ -23350,7 +23394,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="503" spans="1:23">
+    <row r="503" spans="1:23" hidden="1">
       <c r="A503">
         <v>503</v>
       </c>
@@ -23387,7 +23431,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="504" spans="1:23">
+    <row r="504" spans="1:23" hidden="1">
       <c r="A504">
         <v>504</v>
       </c>
@@ -23430,7 +23474,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="505" spans="1:23">
+    <row r="505" spans="1:23" hidden="1">
       <c r="A505">
         <v>505</v>
       </c>
@@ -23469,7 +23513,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="506" spans="1:23">
+    <row r="506" spans="1:23" hidden="1">
       <c r="A506">
         <v>506</v>
       </c>
@@ -23508,7 +23552,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="507" spans="1:23">
+    <row r="507" spans="1:23" hidden="1">
       <c r="A507">
         <v>507</v>
       </c>
@@ -23547,7 +23591,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="508" spans="1:23">
+    <row r="508" spans="1:23" hidden="1">
       <c r="A508">
         <v>508</v>
       </c>
@@ -23590,7 +23634,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="509" spans="1:23">
+    <row r="509" spans="1:23" hidden="1">
       <c r="A509">
         <v>509</v>
       </c>
@@ -23627,7 +23671,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="510" spans="1:23">
+    <row r="510" spans="1:23" hidden="1">
       <c r="A510">
         <v>510</v>
       </c>
@@ -23666,7 +23710,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="511" spans="1:23">
+    <row r="511" spans="1:23" hidden="1">
       <c r="A511">
         <v>511</v>
       </c>
@@ -23705,7 +23749,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="512" spans="1:23">
+    <row r="512" spans="1:23" hidden="1">
       <c r="A512">
         <v>512</v>
       </c>
@@ -23744,7 +23788,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="513" spans="1:23">
+    <row r="513" spans="1:23" hidden="1">
       <c r="A513">
         <v>513</v>
       </c>
@@ -23783,7 +23827,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="514" spans="1:23">
+    <row r="514" spans="1:23" hidden="1">
       <c r="A514">
         <v>514</v>
       </c>
@@ -23822,7 +23866,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="515" spans="1:23">
+    <row r="515" spans="1:23" hidden="1">
       <c r="A515">
         <v>515</v>
       </c>
@@ -23865,7 +23909,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="516" spans="1:23">
+    <row r="516" spans="1:23" hidden="1">
       <c r="A516">
         <v>516</v>
       </c>
@@ -23904,7 +23948,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="517" spans="1:23">
+    <row r="517" spans="1:23" hidden="1">
       <c r="A517">
         <v>517</v>
       </c>
@@ -23943,7 +23987,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="518" spans="1:23">
+    <row r="518" spans="1:23" hidden="1">
       <c r="A518">
         <v>518</v>
       </c>
@@ -23980,7 +24024,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="519" spans="1:23">
+    <row r="519" spans="1:23" hidden="1">
       <c r="A519">
         <v>519</v>
       </c>
@@ -24020,7 +24064,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="520" spans="1:23">
+    <row r="520" spans="1:23" hidden="1">
       <c r="A520">
         <v>520</v>
       </c>
@@ -24057,7 +24101,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="521" spans="1:23">
+    <row r="521" spans="1:23" hidden="1">
       <c r="A521">
         <v>521</v>
       </c>
@@ -24100,7 +24144,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="522" spans="1:23">
+    <row r="522" spans="1:23" hidden="1">
       <c r="A522">
         <v>522</v>
       </c>
@@ -24139,7 +24183,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="523" spans="1:23">
+    <row r="523" spans="1:23" hidden="1">
       <c r="A523">
         <v>523</v>
       </c>
@@ -24178,7 +24222,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="524" spans="1:23">
+    <row r="524" spans="1:23" hidden="1">
       <c r="A524">
         <v>524</v>
       </c>
@@ -24215,7 +24259,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="525" spans="1:23">
+    <row r="525" spans="1:23" hidden="1">
       <c r="A525">
         <v>525</v>
       </c>
@@ -24252,7 +24296,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="526" spans="1:23">
+    <row r="526" spans="1:23" hidden="1">
       <c r="A526">
         <v>526</v>
       </c>
@@ -24295,7 +24339,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="527" spans="1:23">
+    <row r="527" spans="1:23" hidden="1">
       <c r="A527">
         <v>527</v>
       </c>
@@ -24338,7 +24382,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="528" spans="1:23">
+    <row r="528" spans="1:23" hidden="1">
       <c r="A528">
         <v>528</v>
       </c>
@@ -24381,7 +24425,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="529" spans="1:23">
+    <row r="529" spans="1:23" hidden="1">
       <c r="A529">
         <v>529</v>
       </c>
@@ -24422,7 +24466,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="530" spans="1:23">
+    <row r="530" spans="1:23" hidden="1">
       <c r="A530">
         <v>530</v>
       </c>
@@ -24461,7 +24505,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="531" spans="1:23">
+    <row r="531" spans="1:23" hidden="1">
       <c r="A531">
         <v>531</v>
       </c>
@@ -24886,7 +24930,7 @@
       </c>
       <c r="W541" s="3"/>
     </row>
-    <row r="542" spans="1:23">
+    <row r="542" spans="1:23" hidden="1">
       <c r="A542">
         <v>542</v>
       </c>
@@ -24923,7 +24967,7 @@
       </c>
       <c r="W542" s="3"/>
     </row>
-    <row r="543" spans="1:23">
+    <row r="543" spans="1:23" hidden="1">
       <c r="A543">
         <v>543</v>
       </c>
@@ -24962,7 +25006,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="544" spans="1:23">
+    <row r="544" spans="1:23" hidden="1">
       <c r="A544">
         <v>544</v>
       </c>
@@ -24999,7 +25043,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="545" spans="1:23">
+    <row r="545" spans="1:23" hidden="1">
       <c r="A545">
         <v>545</v>
       </c>
@@ -25036,7 +25080,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="546" spans="1:23">
+    <row r="546" spans="1:23" hidden="1">
       <c r="A546">
         <v>546</v>
       </c>
@@ -25076,7 +25120,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="547" spans="1:23">
+    <row r="547" spans="1:23" hidden="1">
       <c r="A547">
         <v>547</v>
       </c>
@@ -25113,7 +25157,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="548" spans="1:23">
+    <row r="548" spans="1:23" hidden="1">
       <c r="A548">
         <v>548</v>
       </c>
@@ -25150,7 +25194,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="549" spans="1:23">
+    <row r="549" spans="1:23" hidden="1">
       <c r="A549">
         <v>549</v>
       </c>
@@ -25187,7 +25231,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="550" spans="1:23">
+    <row r="550" spans="1:23" hidden="1">
       <c r="A550">
         <v>550</v>
       </c>
@@ -25224,7 +25268,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="551" spans="1:23">
+    <row r="551" spans="1:23" hidden="1">
       <c r="A551">
         <v>551</v>
       </c>
@@ -25261,7 +25305,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="552" spans="1:23">
+    <row r="552" spans="1:23" hidden="1">
       <c r="A552">
         <v>552</v>
       </c>
@@ -25298,7 +25342,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="553" spans="1:23">
+    <row r="553" spans="1:23" hidden="1">
       <c r="A553">
         <v>553</v>
       </c>
@@ -25335,7 +25379,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="554" spans="1:23">
+    <row r="554" spans="1:23" hidden="1">
       <c r="A554">
         <v>554</v>
       </c>
@@ -25372,7 +25416,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="555" spans="1:23">
+    <row r="555" spans="1:23" hidden="1">
       <c r="A555">
         <v>555</v>
       </c>
@@ -25409,7 +25453,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="556" spans="1:23">
+    <row r="556" spans="1:23" hidden="1">
       <c r="A556">
         <v>556</v>
       </c>
@@ -25446,7 +25490,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="557" spans="1:23">
+    <row r="557" spans="1:23" hidden="1">
       <c r="A557">
         <v>557</v>
       </c>
@@ -25483,7 +25527,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="558" spans="1:23">
+    <row r="558" spans="1:23" hidden="1">
       <c r="A558">
         <v>558</v>
       </c>
@@ -25520,7 +25564,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="559" spans="1:23">
+    <row r="559" spans="1:23" hidden="1">
       <c r="A559">
         <v>559</v>
       </c>
@@ -25559,7 +25603,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="560" spans="1:23">
+    <row r="560" spans="1:23" hidden="1">
       <c r="A560">
         <v>560</v>
       </c>
@@ -25596,7 +25640,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="561" spans="1:23">
+    <row r="561" spans="1:23" hidden="1">
       <c r="A561">
         <v>561</v>
       </c>
@@ -25631,7 +25675,7 @@
       </c>
       <c r="W561" s="3"/>
     </row>
-    <row r="562" spans="1:23">
+    <row r="562" spans="1:23" hidden="1">
       <c r="A562">
         <v>562</v>
       </c>
@@ -25666,7 +25710,7 @@
       </c>
       <c r="W562" s="3"/>
     </row>
-    <row r="563" spans="1:23">
+    <row r="563" spans="1:23" hidden="1">
       <c r="A563">
         <v>563</v>
       </c>
@@ -25701,7 +25745,7 @@
       </c>
       <c r="W563" s="3"/>
     </row>
-    <row r="564" spans="1:23">
+    <row r="564" spans="1:23" hidden="1">
       <c r="A564">
         <v>564</v>
       </c>
@@ -25736,7 +25780,7 @@
       </c>
       <c r="W564" s="3"/>
     </row>
-    <row r="565" spans="1:23">
+    <row r="565" spans="1:23" hidden="1">
       <c r="A565">
         <v>565</v>
       </c>
@@ -25771,7 +25815,7 @@
       </c>
       <c r="W565" s="3"/>
     </row>
-    <row r="566" spans="1:23">
+    <row r="566" spans="1:23" hidden="1">
       <c r="A566">
         <v>566</v>
       </c>
@@ -25810,7 +25854,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="567" spans="1:23">
+    <row r="567" spans="1:23" hidden="1">
       <c r="A567">
         <v>567</v>
       </c>
@@ -25849,7 +25893,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="568" spans="1:23">
+    <row r="568" spans="1:23" hidden="1">
       <c r="A568">
         <v>568</v>
       </c>
@@ -25888,7 +25932,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="569" spans="1:23">
+    <row r="569" spans="1:23" hidden="1">
       <c r="A569">
         <v>569</v>
       </c>
@@ -25923,7 +25967,7 @@
       </c>
       <c r="W569" s="3"/>
     </row>
-    <row r="570" spans="1:23">
+    <row r="570" spans="1:23" hidden="1">
       <c r="A570">
         <v>570</v>
       </c>
@@ -25962,7 +26006,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="571" spans="1:23">
+    <row r="571" spans="1:23" hidden="1">
       <c r="A571">
         <v>571</v>
       </c>
@@ -26003,7 +26047,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="572" spans="1:23">
+    <row r="572" spans="1:23" hidden="1">
       <c r="A572">
         <v>572</v>
       </c>
@@ -26042,7 +26086,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="573" spans="1:23">
+    <row r="573" spans="1:23" hidden="1">
       <c r="A573">
         <v>573</v>
       </c>
@@ -26079,7 +26123,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="574" spans="1:23">
+    <row r="574" spans="1:23" hidden="1">
       <c r="A574">
         <v>574</v>
       </c>
@@ -26118,7 +26162,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="575" spans="1:23">
+    <row r="575" spans="1:23" hidden="1">
       <c r="A575">
         <v>575</v>
       </c>
@@ -26157,7 +26201,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="576" spans="1:23">
+    <row r="576" spans="1:23" hidden="1">
       <c r="A576">
         <v>576</v>
       </c>
@@ -26194,7 +26238,7 @@
       </c>
       <c r="W576" s="3"/>
     </row>
-    <row r="577" spans="1:23">
+    <row r="577" spans="1:23" hidden="1">
       <c r="A577">
         <v>577</v>
       </c>
@@ -26231,7 +26275,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="578" spans="1:23">
+    <row r="578" spans="1:23" hidden="1">
       <c r="A578">
         <v>578</v>
       </c>
@@ -26270,7 +26314,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="579" spans="1:23">
+    <row r="579" spans="1:23" hidden="1">
       <c r="A579">
         <v>579</v>
       </c>
@@ -26307,7 +26351,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="580" spans="1:23">
+    <row r="580" spans="1:23" hidden="1">
       <c r="A580">
         <v>580</v>
       </c>
@@ -26342,7 +26386,7 @@
       </c>
       <c r="W580" s="3"/>
     </row>
-    <row r="581" spans="1:23">
+    <row r="581" spans="1:23" hidden="1">
       <c r="A581">
         <v>581</v>
       </c>
@@ -26381,7 +26425,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="582" spans="1:23">
+    <row r="582" spans="1:23" hidden="1">
       <c r="A582">
         <v>582</v>
       </c>
@@ -26419,7 +26463,7 @@
       </c>
       <c r="W582" s="3"/>
     </row>
-    <row r="583" spans="1:23">
+    <row r="583" spans="1:23" hidden="1">
       <c r="A583">
         <v>583</v>
       </c>
@@ -26457,7 +26501,7 @@
       </c>
       <c r="W583" s="3"/>
     </row>
-    <row r="584" spans="1:23">
+    <row r="584" spans="1:23" hidden="1">
       <c r="A584">
         <v>584</v>
       </c>
@@ -26492,7 +26536,7 @@
       </c>
       <c r="W584" s="3"/>
     </row>
-    <row r="585" spans="1:23">
+    <row r="585" spans="1:23" hidden="1">
       <c r="A585">
         <v>585</v>
       </c>
@@ -26527,7 +26571,7 @@
       </c>
       <c r="W585" s="3"/>
     </row>
-    <row r="586" spans="1:23">
+    <row r="586" spans="1:23" hidden="1">
       <c r="A586">
         <v>586</v>
       </c>
@@ -26562,7 +26606,7 @@
       </c>
       <c r="W586" s="3"/>
     </row>
-    <row r="587" spans="1:23">
+    <row r="587" spans="1:23" hidden="1">
       <c r="A587">
         <v>587</v>
       </c>
@@ -26597,7 +26641,7 @@
       </c>
       <c r="W587" s="3"/>
     </row>
-    <row r="588" spans="1:23">
+    <row r="588" spans="1:23" hidden="1">
       <c r="A588">
         <v>588</v>
       </c>
@@ -26632,7 +26676,7 @@
       </c>
       <c r="W588" s="3"/>
     </row>
-    <row r="589" spans="1:23">
+    <row r="589" spans="1:23" hidden="1">
       <c r="A589">
         <v>589</v>
       </c>
@@ -26667,7 +26711,7 @@
       </c>
       <c r="W589" s="3"/>
     </row>
-    <row r="590" spans="1:23">
+    <row r="590" spans="1:23" hidden="1">
       <c r="A590">
         <v>590</v>
       </c>
@@ -26702,7 +26746,7 @@
       </c>
       <c r="W590" s="3"/>
     </row>
-    <row r="591" spans="1:23">
+    <row r="591" spans="1:23" hidden="1">
       <c r="A591">
         <v>591</v>
       </c>
@@ -26737,7 +26781,7 @@
       </c>
       <c r="W591" s="3"/>
     </row>
-    <row r="592" spans="1:23">
+    <row r="592" spans="1:23" hidden="1">
       <c r="A592">
         <v>592</v>
       </c>
@@ -26774,7 +26818,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="593" spans="1:23">
+    <row r="593" spans="1:23" hidden="1">
       <c r="A593">
         <v>593</v>
       </c>
@@ -26811,7 +26855,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="594" spans="1:23">
+    <row r="594" spans="1:23" hidden="1">
       <c r="A594">
         <v>594</v>
       </c>
@@ -26854,7 +26898,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="595" spans="1:23">
+    <row r="595" spans="1:23" hidden="1">
       <c r="A595">
         <v>595</v>
       </c>
@@ -26897,7 +26941,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="596" spans="1:23">
+    <row r="596" spans="1:23" hidden="1">
       <c r="A596">
         <v>596</v>
       </c>
@@ -26940,7 +26984,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="597" spans="1:23">
+    <row r="597" spans="1:23" hidden="1">
       <c r="A597">
         <v>597</v>
       </c>
@@ -26983,7 +27027,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="598" spans="1:23">
+    <row r="598" spans="1:23" hidden="1">
       <c r="A598">
         <v>598</v>
       </c>
@@ -27026,7 +27070,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="599" spans="1:23">
+    <row r="599" spans="1:23" hidden="1">
       <c r="A599">
         <v>599</v>
       </c>
@@ -27069,7 +27113,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="600" spans="1:23">
+    <row r="600" spans="1:23" hidden="1">
       <c r="A600">
         <v>600</v>
       </c>
@@ -27109,7 +27153,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="601" spans="1:23">
+    <row r="601" spans="1:23" hidden="1">
       <c r="A601">
         <v>601</v>
       </c>
@@ -27152,7 +27196,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="602" spans="1:23">
+    <row r="602" spans="1:23" hidden="1">
       <c r="A602">
         <v>602</v>
       </c>
@@ -27195,7 +27239,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="603" spans="1:23">
+    <row r="603" spans="1:23" hidden="1">
       <c r="A603">
         <v>605</v>
       </c>
@@ -27233,7 +27277,7 @@
       </c>
       <c r="W603" s="3"/>
     </row>
-    <row r="604" spans="1:23">
+    <row r="604" spans="1:23" hidden="1">
       <c r="A604">
         <v>607</v>
       </c>
@@ -27274,7 +27318,7 @@
       </c>
       <c r="W604" s="3"/>
     </row>
-    <row r="605" spans="1:23">
+    <row r="605" spans="1:23" hidden="1">
       <c r="A605">
         <v>608</v>
       </c>
@@ -27315,7 +27359,7 @@
       </c>
       <c r="W605" s="3"/>
     </row>
-    <row r="606" spans="1:23">
+    <row r="606" spans="1:23" hidden="1">
       <c r="A606">
         <v>611</v>
       </c>
@@ -27353,7 +27397,7 @@
       </c>
       <c r="W606" s="3"/>
     </row>
-    <row r="607" spans="1:23">
+    <row r="607" spans="1:23" hidden="1">
       <c r="A607">
         <v>612</v>
       </c>
@@ -27391,7 +27435,7 @@
       </c>
       <c r="W607" s="3"/>
     </row>
-    <row r="608" spans="1:23">
+    <row r="608" spans="1:23" hidden="1">
       <c r="A608">
         <v>613</v>
       </c>
@@ -27429,7 +27473,7 @@
       </c>
       <c r="W608" s="3"/>
     </row>
-    <row r="609" spans="1:23">
+    <row r="609" spans="1:23" hidden="1">
       <c r="A609">
         <v>614</v>
       </c>
@@ -27467,7 +27511,7 @@
       </c>
       <c r="W609" s="3"/>
     </row>
-    <row r="610" spans="1:23">
+    <row r="610" spans="1:23" hidden="1">
       <c r="A610">
         <v>615</v>
       </c>
@@ -27505,7 +27549,7 @@
       </c>
       <c r="W610" s="3"/>
     </row>
-    <row r="611" spans="1:23">
+    <row r="611" spans="1:23" hidden="1">
       <c r="A611">
         <v>616</v>
       </c>
@@ -27543,7 +27587,7 @@
       </c>
       <c r="W611" s="3"/>
     </row>
-    <row r="612" spans="1:23">
+    <row r="612" spans="1:23" hidden="1">
       <c r="A612">
         <v>617</v>
       </c>
@@ -27584,7 +27628,7 @@
       </c>
       <c r="W612" s="3"/>
     </row>
-    <row r="613" spans="1:23">
+    <row r="613" spans="1:23" hidden="1">
       <c r="A613">
         <v>618</v>
       </c>
@@ -27625,7 +27669,7 @@
       </c>
       <c r="W613" s="3"/>
     </row>
-    <row r="614" spans="1:23">
+    <row r="614" spans="1:23" hidden="1">
       <c r="A614">
         <v>619</v>
       </c>
@@ -27666,7 +27710,7 @@
       </c>
       <c r="W614" s="3"/>
     </row>
-    <row r="615" spans="1:23">
+    <row r="615" spans="1:23" hidden="1">
       <c r="A615">
         <v>620</v>
       </c>
@@ -27707,7 +27751,7 @@
       </c>
       <c r="W615" s="3"/>
     </row>
-    <row r="616" spans="1:23">
+    <row r="616" spans="1:23" hidden="1">
       <c r="A616">
         <v>621</v>
       </c>
@@ -27748,7 +27792,7 @@
       </c>
       <c r="W616" s="3"/>
     </row>
-    <row r="617" spans="1:23">
+    <row r="617" spans="1:23" hidden="1">
       <c r="A617">
         <v>622</v>
       </c>
@@ -27789,7 +27833,7 @@
       </c>
       <c r="W617" s="3"/>
     </row>
-    <row r="618" spans="1:23">
+    <row r="618" spans="1:23" hidden="1">
       <c r="A618">
         <v>623</v>
       </c>
@@ -27830,7 +27874,7 @@
       </c>
       <c r="W618" s="3"/>
     </row>
-    <row r="619" spans="1:23">
+    <row r="619" spans="1:23" hidden="1">
       <c r="A619">
         <v>624</v>
       </c>
@@ -27871,7 +27915,7 @@
       </c>
       <c r="W619" s="3"/>
     </row>
-    <row r="620" spans="1:23">
+    <row r="620" spans="1:23" hidden="1">
       <c r="A620">
         <v>625</v>
       </c>
@@ -27912,7 +27956,7 @@
       </c>
       <c r="W620" s="3"/>
     </row>
-    <row r="621" spans="1:23">
+    <row r="621" spans="1:23" hidden="1">
       <c r="A621">
         <v>626</v>
       </c>
@@ -27953,7 +27997,7 @@
       </c>
       <c r="W621" s="3"/>
     </row>
-    <row r="622" spans="1:23">
+    <row r="622" spans="1:23" hidden="1">
       <c r="A622">
         <v>627</v>
       </c>
@@ -27994,7 +28038,7 @@
       </c>
       <c r="W622" s="3"/>
     </row>
-    <row r="623" spans="1:23">
+    <row r="623" spans="1:23" hidden="1">
       <c r="A623">
         <v>628</v>
       </c>
@@ -28032,7 +28076,7 @@
       </c>
       <c r="W623" s="3"/>
     </row>
-    <row r="624" spans="1:23">
+    <row r="624" spans="1:23" hidden="1">
       <c r="A624">
         <v>629</v>
       </c>
@@ -28070,7 +28114,7 @@
       </c>
       <c r="W624" s="3"/>
     </row>
-    <row r="625" spans="1:23">
+    <row r="625" spans="1:23" hidden="1">
       <c r="A625">
         <v>630</v>
       </c>
@@ -28111,7 +28155,7 @@
       </c>
       <c r="W625" s="3"/>
     </row>
-    <row r="626" spans="1:23">
+    <row r="626" spans="1:23" hidden="1">
       <c r="A626">
         <v>631</v>
       </c>
@@ -28149,7 +28193,7 @@
       </c>
       <c r="W626" s="3"/>
     </row>
-    <row r="627" spans="1:23">
+    <row r="627" spans="1:23" hidden="1">
       <c r="A627">
         <v>632</v>
       </c>
@@ -28187,7 +28231,7 @@
       </c>
       <c r="W627" s="3"/>
     </row>
-    <row r="628" spans="1:23">
+    <row r="628" spans="1:23" hidden="1">
       <c r="A628">
         <v>633</v>
       </c>
@@ -28228,7 +28272,7 @@
       </c>
       <c r="W628" s="3"/>
     </row>
-    <row r="629" spans="1:23">
+    <row r="629" spans="1:23" hidden="1">
       <c r="A629">
         <v>634</v>
       </c>
@@ -28269,7 +28313,7 @@
       </c>
       <c r="W629" s="3"/>
     </row>
-    <row r="630" spans="1:23">
+    <row r="630" spans="1:23" hidden="1">
       <c r="A630">
         <v>635</v>
       </c>
@@ -28308,7 +28352,7 @@
       </c>
       <c r="W630" s="3"/>
     </row>
-    <row r="631" spans="1:23">
+    <row r="631" spans="1:23" hidden="1">
       <c r="A631">
         <v>636</v>
       </c>
@@ -28345,7 +28389,7 @@
       </c>
       <c r="W631" s="3"/>
     </row>
-    <row r="632" spans="1:23">
+    <row r="632" spans="1:23" hidden="1">
       <c r="A632">
         <v>637</v>
       </c>
@@ -28386,7 +28430,7 @@
       </c>
       <c r="W632" s="3"/>
     </row>
-    <row r="633" spans="1:23">
+    <row r="633" spans="1:23" hidden="1">
       <c r="A633">
         <v>638</v>
       </c>
@@ -28427,7 +28471,7 @@
       </c>
       <c r="W633" s="3"/>
     </row>
-    <row r="634" spans="1:23">
+    <row r="634" spans="1:23" hidden="1">
       <c r="A634">
         <v>639</v>
       </c>
@@ -28468,7 +28512,7 @@
       </c>
       <c r="W634" s="3"/>
     </row>
-    <row r="635" spans="1:23">
+    <row r="635" spans="1:23" hidden="1">
       <c r="A635">
         <v>640</v>
       </c>
@@ -28508,7 +28552,7 @@
       </c>
       <c r="W635" s="3"/>
     </row>
-    <row r="636" spans="1:23">
+    <row r="636" spans="1:23" hidden="1">
       <c r="A636">
         <v>641</v>
       </c>
@@ -28549,7 +28593,7 @@
       </c>
       <c r="W636" s="3"/>
     </row>
-    <row r="637" spans="1:23">
+    <row r="637" spans="1:23" hidden="1">
       <c r="A637">
         <v>642</v>
       </c>
@@ -28590,7 +28634,7 @@
       </c>
       <c r="W637" s="3"/>
     </row>
-    <row r="638" spans="1:23">
+    <row r="638" spans="1:23" hidden="1">
       <c r="A638">
         <v>643</v>
       </c>
@@ -28631,7 +28675,7 @@
       </c>
       <c r="W638" s="3"/>
     </row>
-    <row r="639" spans="1:23">
+    <row r="639" spans="1:23" hidden="1">
       <c r="A639">
         <v>644</v>
       </c>
@@ -28668,7 +28712,7 @@
       </c>
       <c r="W639" s="3"/>
     </row>
-    <row r="640" spans="1:23">
+    <row r="640" spans="1:23" hidden="1">
       <c r="A640">
         <v>650</v>
       </c>
@@ -28709,7 +28753,7 @@
       </c>
       <c r="W640" s="3"/>
     </row>
-    <row r="641" spans="1:23">
+    <row r="641" spans="1:23" hidden="1">
       <c r="A641">
         <v>645</v>
       </c>
@@ -28750,7 +28794,7 @@
       </c>
       <c r="W641" s="3"/>
     </row>
-    <row r="642" spans="1:23">
+    <row r="642" spans="1:23" hidden="1">
       <c r="A642">
         <v>646</v>
       </c>
@@ -28786,7 +28830,7 @@
       </c>
       <c r="W642" s="3"/>
     </row>
-    <row r="643" spans="1:23">
+    <row r="643" spans="1:23" hidden="1">
       <c r="A643">
         <v>647</v>
       </c>
@@ -28827,7 +28871,7 @@
       </c>
       <c r="W643" s="3"/>
     </row>
-    <row r="644" spans="1:23">
+    <row r="644" spans="1:23" hidden="1">
       <c r="A644">
         <v>648</v>
       </c>
@@ -28865,7 +28909,7 @@
       </c>
       <c r="W644" s="3"/>
     </row>
-    <row r="645" spans="1:23">
+    <row r="645" spans="1:23" hidden="1">
       <c r="A645">
         <v>649</v>
       </c>
@@ -28906,7 +28950,7 @@
       </c>
       <c r="W645" s="3"/>
     </row>
-    <row r="646" spans="1:23">
+    <row r="646" spans="1:23" hidden="1">
       <c r="A646">
         <v>651</v>
       </c>
@@ -28947,7 +28991,7 @@
       </c>
       <c r="W646" s="3"/>
     </row>
-    <row r="647" spans="1:23">
+    <row r="647" spans="1:23" hidden="1">
       <c r="A647">
         <v>652</v>
       </c>
@@ -28988,7 +29032,7 @@
       </c>
       <c r="W647" s="3"/>
     </row>
-    <row r="648" spans="1:23">
+    <row r="648" spans="1:23" hidden="1">
       <c r="A648">
         <v>653</v>
       </c>
@@ -29029,7 +29073,7 @@
       </c>
       <c r="W648" s="3"/>
     </row>
-    <row r="649" spans="1:23">
+    <row r="649" spans="1:23" hidden="1">
       <c r="A649">
         <v>654</v>
       </c>
@@ -29070,7 +29114,7 @@
       </c>
       <c r="W649" s="3"/>
     </row>
-    <row r="650" spans="1:23">
+    <row r="650" spans="1:23" hidden="1">
       <c r="A650">
         <v>655</v>
       </c>
@@ -29111,7 +29155,7 @@
       </c>
       <c r="W650" s="3"/>
     </row>
-    <row r="651" spans="1:23">
+    <row r="651" spans="1:23" hidden="1">
       <c r="A651">
         <v>656</v>
       </c>
@@ -29152,7 +29196,7 @@
       </c>
       <c r="W651" s="3"/>
     </row>
-    <row r="652" spans="1:23">
+    <row r="652" spans="1:23" hidden="1">
       <c r="A652">
         <v>657</v>
       </c>
@@ -29193,7 +29237,7 @@
       </c>
       <c r="W652" s="3"/>
     </row>
-    <row r="653" spans="1:23">
+    <row r="653" spans="1:23" hidden="1">
       <c r="A653">
         <v>658</v>
       </c>
@@ -29234,7 +29278,7 @@
       </c>
       <c r="W653" s="3"/>
     </row>
-    <row r="654" spans="1:23">
+    <row r="654" spans="1:23" hidden="1">
       <c r="A654">
         <v>659</v>
       </c>
@@ -29271,7 +29315,7 @@
       </c>
       <c r="W654" s="3"/>
     </row>
-    <row r="655" spans="1:23">
+    <row r="655" spans="1:23" hidden="1">
       <c r="A655">
         <v>660</v>
       </c>
@@ -29312,7 +29356,7 @@
       </c>
       <c r="W655" s="3"/>
     </row>
-    <row r="656" spans="1:23">
+    <row r="656" spans="1:23" hidden="1">
       <c r="A656">
         <v>661</v>
       </c>
@@ -29352,7 +29396,7 @@
       </c>
       <c r="W656" s="3"/>
     </row>
-    <row r="657" spans="1:23">
+    <row r="657" spans="1:23" hidden="1">
       <c r="A657">
         <v>662</v>
       </c>
@@ -29393,7 +29437,7 @@
       </c>
       <c r="W657" s="3"/>
     </row>
-    <row r="658" spans="1:23">
+    <row r="658" spans="1:23" hidden="1">
       <c r="A658">
         <v>663</v>
       </c>
@@ -29434,7 +29478,7 @@
       </c>
       <c r="W658" s="3"/>
     </row>
-    <row r="659" spans="1:23">
+    <row r="659" spans="1:23" hidden="1">
       <c r="A659">
         <v>664</v>
       </c>
@@ -29471,7 +29515,7 @@
       </c>
       <c r="W659" s="3"/>
     </row>
-    <row r="660" spans="1:23">
+    <row r="660" spans="1:23" hidden="1">
       <c r="A660">
         <v>665</v>
       </c>
@@ -29553,7 +29597,7 @@
       </c>
       <c r="W661" s="3"/>
     </row>
-    <row r="662" spans="1:23">
+    <row r="662" spans="1:23" hidden="1">
       <c r="A662">
         <v>668</v>
       </c>
@@ -29591,7 +29635,7 @@
       </c>
       <c r="W662" s="3"/>
     </row>
-    <row r="663" spans="1:23">
+    <row r="663" spans="1:23" hidden="1">
       <c r="A663">
         <v>667</v>
       </c>
@@ -29632,7 +29676,7 @@
       </c>
       <c r="W663" s="3"/>
     </row>
-    <row r="664" spans="1:23">
+    <row r="664" spans="1:23" hidden="1">
       <c r="A664">
         <v>669</v>
       </c>
@@ -29673,7 +29717,7 @@
       </c>
       <c r="W664" s="3"/>
     </row>
-    <row r="665" spans="1:23">
+    <row r="665" spans="1:23" hidden="1">
       <c r="A665">
         <v>670</v>
       </c>
@@ -29713,7 +29757,7 @@
       </c>
       <c r="W665" s="3"/>
     </row>
-    <row r="666" spans="1:23">
+    <row r="666" spans="1:23" hidden="1">
       <c r="A666">
         <v>671</v>
       </c>
@@ -29754,7 +29798,7 @@
       </c>
       <c r="W666" s="3"/>
     </row>
-    <row r="667" spans="1:23">
+    <row r="667" spans="1:23" hidden="1">
       <c r="A667">
         <v>672</v>
       </c>
@@ -29795,7 +29839,7 @@
       </c>
       <c r="W667" s="3"/>
     </row>
-    <row r="668" spans="1:23">
+    <row r="668" spans="1:23" hidden="1">
       <c r="A668">
         <v>674</v>
       </c>
@@ -29836,7 +29880,7 @@
       </c>
       <c r="W668" s="3"/>
     </row>
-    <row r="669" spans="1:23">
+    <row r="669" spans="1:23" hidden="1">
       <c r="A669">
         <v>675</v>
       </c>
@@ -29877,7 +29921,7 @@
       </c>
       <c r="W669" s="3"/>
     </row>
-    <row r="670" spans="1:23">
+    <row r="670" spans="1:23" hidden="1">
       <c r="A670">
         <v>676</v>
       </c>
@@ -29917,7 +29961,7 @@
       </c>
       <c r="W670" s="3"/>
     </row>
-    <row r="671" spans="1:23">
+    <row r="671" spans="1:23" hidden="1">
       <c r="A671">
         <v>677</v>
       </c>
@@ -29957,7 +30001,7 @@
       </c>
       <c r="W671" s="3"/>
     </row>
-    <row r="672" spans="1:23">
+    <row r="672" spans="1:23" hidden="1">
       <c r="A672">
         <v>678</v>
       </c>
@@ -29997,7 +30041,7 @@
       </c>
       <c r="W672" s="3"/>
     </row>
-    <row r="673" spans="1:23">
+    <row r="673" spans="1:23" hidden="1">
       <c r="A673">
         <v>679</v>
       </c>
@@ -30038,7 +30082,7 @@
       </c>
       <c r="W673" s="3"/>
     </row>
-    <row r="674" spans="1:23">
+    <row r="674" spans="1:23" hidden="1">
       <c r="A674">
         <v>680</v>
       </c>
@@ -30120,7 +30164,7 @@
       </c>
       <c r="W675" s="3"/>
     </row>
-    <row r="676" spans="1:23">
+    <row r="676" spans="1:23" hidden="1">
       <c r="A676">
         <v>682</v>
       </c>
@@ -30161,7 +30205,7 @@
       </c>
       <c r="W676" s="3"/>
     </row>
-    <row r="677" spans="1:23">
+    <row r="677" spans="1:23" hidden="1">
       <c r="A677">
         <v>683</v>
       </c>
@@ -30202,7 +30246,7 @@
       </c>
       <c r="W677" s="3"/>
     </row>
-    <row r="678" spans="1:23">
+    <row r="678" spans="1:23" hidden="1">
       <c r="A678">
         <v>684</v>
       </c>
@@ -30243,7 +30287,7 @@
       </c>
       <c r="W678" s="3"/>
     </row>
-    <row r="679" spans="1:23">
+    <row r="679" spans="1:23" hidden="1">
       <c r="A679">
         <v>685</v>
       </c>
@@ -30284,7 +30328,7 @@
       </c>
       <c r="W679" s="3"/>
     </row>
-    <row r="680" spans="1:23">
+    <row r="680" spans="1:23" hidden="1">
       <c r="A680">
         <v>686</v>
       </c>
@@ -30325,7 +30369,7 @@
       </c>
       <c r="W680" s="3"/>
     </row>
-    <row r="681" spans="1:23">
+    <row r="681" spans="1:23" hidden="1">
       <c r="A681">
         <v>687</v>
       </c>
@@ -30366,7 +30410,7 @@
       </c>
       <c r="W681" s="3"/>
     </row>
-    <row r="682" spans="1:23">
+    <row r="682" spans="1:23" hidden="1">
       <c r="A682">
         <v>688</v>
       </c>
@@ -30407,7 +30451,7 @@
       </c>
       <c r="W682" s="3"/>
     </row>
-    <row r="683" spans="1:23">
+    <row r="683" spans="1:23" hidden="1">
       <c r="A683">
         <v>689</v>
       </c>
@@ -30445,7 +30489,7 @@
       </c>
       <c r="W683" s="3"/>
     </row>
-    <row r="684" spans="1:23">
+    <row r="684" spans="1:23" hidden="1">
       <c r="A684">
         <v>690</v>
       </c>
@@ -30486,7 +30530,7 @@
       </c>
       <c r="W684" s="3"/>
     </row>
-    <row r="685" spans="1:23">
+    <row r="685" spans="1:23" hidden="1">
       <c r="A685">
         <v>691</v>
       </c>
@@ -30527,7 +30571,7 @@
       </c>
       <c r="W685" s="3"/>
     </row>
-    <row r="686" spans="1:23">
+    <row r="686" spans="1:23" hidden="1">
       <c r="A686">
         <v>692</v>
       </c>
@@ -30568,7 +30612,7 @@
       </c>
       <c r="W686" s="3"/>
     </row>
-    <row r="687" spans="1:23">
+    <row r="687" spans="1:23" hidden="1">
       <c r="A687">
         <v>693</v>
       </c>
@@ -30609,7 +30653,7 @@
       </c>
       <c r="W687" s="3"/>
     </row>
-    <row r="688" spans="1:23">
+    <row r="688" spans="1:23" hidden="1">
       <c r="A688">
         <v>694</v>
       </c>
@@ -30650,7 +30694,7 @@
       </c>
       <c r="W688" s="3"/>
     </row>
-    <row r="689" spans="1:23">
+    <row r="689" spans="1:23" hidden="1">
       <c r="A689">
         <v>695</v>
       </c>
@@ -30691,7 +30735,7 @@
       </c>
       <c r="W689" s="3"/>
     </row>
-    <row r="690" spans="1:23">
+    <row r="690" spans="1:23" hidden="1">
       <c r="A690">
         <v>696</v>
       </c>
@@ -30732,7 +30776,7 @@
       </c>
       <c r="W690" s="3"/>
     </row>
-    <row r="691" spans="1:23">
+    <row r="691" spans="1:23" hidden="1">
       <c r="A691">
         <v>697</v>
       </c>
@@ -30769,7 +30813,7 @@
       </c>
       <c r="W691" s="3"/>
     </row>
-    <row r="692" spans="1:23">
+    <row r="692" spans="1:23" hidden="1">
       <c r="A692">
         <v>698</v>
       </c>
@@ -30809,7 +30853,7 @@
       </c>
       <c r="W692" s="3"/>
     </row>
-    <row r="693" spans="1:23">
+    <row r="693" spans="1:23" hidden="1">
       <c r="A693">
         <v>699</v>
       </c>
@@ -30850,7 +30894,7 @@
       </c>
       <c r="W693" s="3"/>
     </row>
-    <row r="694" spans="1:23">
+    <row r="694" spans="1:23" hidden="1">
       <c r="A694">
         <v>700</v>
       </c>
@@ -30887,7 +30931,7 @@
       </c>
       <c r="W694" s="3"/>
     </row>
-    <row r="695" spans="1:23">
+    <row r="695" spans="1:23" hidden="1">
       <c r="A695">
         <v>701</v>
       </c>
@@ -30928,7 +30972,7 @@
       </c>
       <c r="W695" s="3"/>
     </row>
-    <row r="696" spans="1:23">
+    <row r="696" spans="1:23" hidden="1">
       <c r="A696">
         <v>702</v>
       </c>
@@ -30969,7 +31013,7 @@
       </c>
       <c r="W696" s="3"/>
     </row>
-    <row r="697" spans="1:23">
+    <row r="697" spans="1:23" hidden="1">
       <c r="A697">
         <v>703</v>
       </c>
@@ -31010,7 +31054,7 @@
       </c>
       <c r="W697" s="3"/>
     </row>
-    <row r="698" spans="1:23">
+    <row r="698" spans="1:23" hidden="1">
       <c r="A698">
         <v>704</v>
       </c>
@@ -31051,7 +31095,7 @@
       </c>
       <c r="W698" s="3"/>
     </row>
-    <row r="699" spans="1:23">
+    <row r="699" spans="1:23" hidden="1">
       <c r="A699">
         <v>705</v>
       </c>
@@ -31092,7 +31136,7 @@
       </c>
       <c r="W699" s="3"/>
     </row>
-    <row r="700" spans="1:23">
+    <row r="700" spans="1:23" hidden="1">
       <c r="A700">
         <v>706</v>
       </c>
@@ -31133,7 +31177,7 @@
       </c>
       <c r="W700" s="3"/>
     </row>
-    <row r="701" spans="1:23">
+    <row r="701" spans="1:23" hidden="1">
       <c r="A701">
         <v>707</v>
       </c>
@@ -31174,7 +31218,7 @@
       </c>
       <c r="W701" s="3"/>
     </row>
-    <row r="702" spans="1:23">
+    <row r="702" spans="1:23" hidden="1">
       <c r="A702">
         <v>708</v>
       </c>
@@ -31215,7 +31259,7 @@
       </c>
       <c r="W702" s="3"/>
     </row>
-    <row r="703" spans="1:23">
+    <row r="703" spans="1:23" hidden="1">
       <c r="A703">
         <v>709</v>
       </c>
@@ -31256,7 +31300,7 @@
       </c>
       <c r="W703" s="3"/>
     </row>
-    <row r="704" spans="1:23">
+    <row r="704" spans="1:23" hidden="1">
       <c r="A704">
         <v>710</v>
       </c>
@@ -31297,7 +31341,7 @@
       </c>
       <c r="W704" s="3"/>
     </row>
-    <row r="705" spans="1:23">
+    <row r="705" spans="1:23" hidden="1">
       <c r="A705">
         <v>711</v>
       </c>
@@ -31338,7 +31382,7 @@
       </c>
       <c r="W705" s="3"/>
     </row>
-    <row r="706" spans="1:23">
+    <row r="706" spans="1:23" hidden="1">
       <c r="A706">
         <v>712</v>
       </c>
@@ -31379,7 +31423,7 @@
       </c>
       <c r="W706" s="3"/>
     </row>
-    <row r="707" spans="1:23">
+    <row r="707" spans="1:23" hidden="1">
       <c r="A707">
         <v>713</v>
       </c>
@@ -31417,7 +31461,7 @@
       </c>
       <c r="W707" s="3"/>
     </row>
-    <row r="708" spans="1:23">
+    <row r="708" spans="1:23" hidden="1">
       <c r="A708">
         <v>714</v>
       </c>
@@ -31455,7 +31499,7 @@
       </c>
       <c r="W708" s="3"/>
     </row>
-    <row r="709" spans="1:23">
+    <row r="709" spans="1:23" hidden="1">
       <c r="A709">
         <v>715</v>
       </c>
@@ -31493,7 +31537,7 @@
       </c>
       <c r="W709" s="3"/>
     </row>
-    <row r="710" spans="1:23">
+    <row r="710" spans="1:23" hidden="1">
       <c r="A710">
         <v>716</v>
       </c>
@@ -31541,7 +31585,7 @@
       </c>
       <c r="W710" s="3"/>
     </row>
-    <row r="711" spans="1:23">
+    <row r="711" spans="1:23" hidden="1">
       <c r="A711">
         <v>717</v>
       </c>
@@ -31582,7 +31626,7 @@
       </c>
       <c r="W711" s="3"/>
     </row>
-    <row r="712" spans="1:23">
+    <row r="712" spans="1:23" hidden="1">
       <c r="A712">
         <v>718</v>
       </c>
@@ -31623,7 +31667,7 @@
       </c>
       <c r="W712" s="3"/>
     </row>
-    <row r="713" spans="1:23">
+    <row r="713" spans="1:23" hidden="1">
       <c r="A713">
         <v>719</v>
       </c>
@@ -31664,7 +31708,7 @@
       </c>
       <c r="W713" s="3"/>
     </row>
-    <row r="714" spans="1:23">
+    <row r="714" spans="1:23" hidden="1">
       <c r="A714">
         <v>720</v>
       </c>
@@ -31705,7 +31749,7 @@
       </c>
       <c r="W714" s="3"/>
     </row>
-    <row r="715" spans="1:23">
+    <row r="715" spans="1:23" hidden="1">
       <c r="A715">
         <v>721</v>
       </c>
@@ -31746,7 +31790,7 @@
       </c>
       <c r="W715" s="3"/>
     </row>
-    <row r="716" spans="1:23">
+    <row r="716" spans="1:23" hidden="1">
       <c r="A716">
         <v>722</v>
       </c>
@@ -31787,7 +31831,7 @@
       </c>
       <c r="W716" s="3"/>
     </row>
-    <row r="717" spans="1:23">
+    <row r="717" spans="1:23" hidden="1">
       <c r="A717">
         <v>723</v>
       </c>
@@ -31835,7 +31879,7 @@
       </c>
       <c r="W717" s="3"/>
     </row>
-    <row r="718" spans="1:23">
+    <row r="718" spans="1:23" hidden="1">
       <c r="A718">
         <v>724</v>
       </c>
@@ -31873,7 +31917,7 @@
       </c>
       <c r="W718" s="3"/>
     </row>
-    <row r="719" spans="1:23">
+    <row r="719" spans="1:23" hidden="1">
       <c r="A719">
         <v>725</v>
       </c>
@@ -31911,7 +31955,7 @@
       </c>
       <c r="W719" s="3"/>
     </row>
-    <row r="720" spans="1:23">
+    <row r="720" spans="1:23" hidden="1">
       <c r="A720">
         <v>726</v>
       </c>
@@ -31949,7 +31993,7 @@
       </c>
       <c r="W720" s="3"/>
     </row>
-    <row r="721" spans="1:23">
+    <row r="721" spans="1:23" hidden="1">
       <c r="A721">
         <v>727</v>
       </c>
@@ -31990,7 +32034,7 @@
       </c>
       <c r="W721" s="3"/>
     </row>
-    <row r="722" spans="1:23">
+    <row r="722" spans="1:23" hidden="1">
       <c r="A722">
         <v>728</v>
       </c>
@@ -32031,7 +32075,7 @@
       </c>
       <c r="W722" s="3"/>
     </row>
-    <row r="723" spans="1:23">
+    <row r="723" spans="1:23" hidden="1">
       <c r="A723">
         <v>729</v>
       </c>
@@ -32072,7 +32116,7 @@
       </c>
       <c r="W723" s="3"/>
     </row>
-    <row r="724" spans="1:23">
+    <row r="724" spans="1:23" hidden="1">
       <c r="A724">
         <v>730</v>
       </c>
@@ -32113,7 +32157,7 @@
       </c>
       <c r="W724" s="3"/>
     </row>
-    <row r="725" spans="1:23">
+    <row r="725" spans="1:23" hidden="1">
       <c r="A725">
         <v>731</v>
       </c>
@@ -32154,7 +32198,7 @@
       </c>
       <c r="W725" s="3"/>
     </row>
-    <row r="726" spans="1:23">
+    <row r="726" spans="1:23" hidden="1">
       <c r="A726">
         <v>732</v>
       </c>
@@ -32195,7 +32239,7 @@
       </c>
       <c r="W726" s="3"/>
     </row>
-    <row r="727" spans="1:23">
+    <row r="727" spans="1:23" hidden="1">
       <c r="A727">
         <v>733</v>
       </c>
@@ -32236,7 +32280,7 @@
       </c>
       <c r="W727" s="3"/>
     </row>
-    <row r="728" spans="1:23">
+    <row r="728" spans="1:23" hidden="1">
       <c r="A728">
         <v>734</v>
       </c>
@@ -32277,7 +32321,7 @@
       </c>
       <c r="W728" s="3"/>
     </row>
-    <row r="729" spans="1:23">
+    <row r="729" spans="1:23" hidden="1">
       <c r="A729">
         <v>735</v>
       </c>
@@ -32327,7 +32371,7 @@
       </c>
       <c r="W729" s="3"/>
     </row>
-    <row r="730" spans="1:23">
+    <row r="730" spans="1:23" hidden="1">
       <c r="A730">
         <v>736</v>
       </c>
@@ -32368,7 +32412,7 @@
       </c>
       <c r="W730" s="3"/>
     </row>
-    <row r="731" spans="1:23">
+    <row r="731" spans="1:23" hidden="1">
       <c r="A731">
         <v>737</v>
       </c>
@@ -32408,7 +32452,7 @@
       </c>
       <c r="W731" s="3"/>
     </row>
-    <row r="732" spans="1:23">
+    <row r="732" spans="1:23" hidden="1">
       <c r="A732">
         <v>738</v>
       </c>
@@ -32449,7 +32493,7 @@
       </c>
       <c r="W732" s="3"/>
     </row>
-    <row r="733" spans="1:23">
+    <row r="733" spans="1:23" hidden="1">
       <c r="A733">
         <v>739</v>
       </c>
@@ -32486,7 +32530,7 @@
       </c>
       <c r="W733" s="3"/>
     </row>
-    <row r="734" spans="1:23">
+    <row r="734" spans="1:23" hidden="1">
       <c r="A734">
         <v>740</v>
       </c>
@@ -32524,7 +32568,7 @@
       </c>
       <c r="W734" s="3"/>
     </row>
-    <row r="735" spans="1:23">
+    <row r="735" spans="1:23" hidden="1">
       <c r="A735">
         <v>741</v>
       </c>
@@ -32565,7 +32609,7 @@
       </c>
       <c r="W735" s="3"/>
     </row>
-    <row r="736" spans="1:23">
+    <row r="736" spans="1:23" hidden="1">
       <c r="A736">
         <v>742</v>
       </c>
@@ -32606,7 +32650,7 @@
       </c>
       <c r="W736" s="3"/>
     </row>
-    <row r="737" spans="1:23">
+    <row r="737" spans="1:23" hidden="1">
       <c r="A737">
         <v>743</v>
       </c>
@@ -32656,7 +32700,7 @@
       </c>
       <c r="W737" s="3"/>
     </row>
-    <row r="738" spans="1:23">
+    <row r="738" spans="1:23" hidden="1">
       <c r="A738">
         <v>744</v>
       </c>
@@ -32693,7 +32737,7 @@
       </c>
       <c r="W738" s="3"/>
     </row>
-    <row r="739" spans="1:23">
+    <row r="739" spans="1:23" hidden="1">
       <c r="A739">
         <v>745</v>
       </c>
@@ -32743,7 +32787,7 @@
       </c>
       <c r="W739" s="3"/>
     </row>
-    <row r="740" spans="1:23">
+    <row r="740" spans="1:23" hidden="1">
       <c r="A740">
         <v>746</v>
       </c>
@@ -32793,7 +32837,7 @@
       </c>
       <c r="W740" s="3"/>
     </row>
-    <row r="741" spans="1:23">
+    <row r="741" spans="1:23" hidden="1">
       <c r="A741">
         <v>747</v>
       </c>
@@ -32834,7 +32878,7 @@
       </c>
       <c r="W741" s="3"/>
     </row>
-    <row r="742" spans="1:23">
+    <row r="742" spans="1:23" hidden="1">
       <c r="A742">
         <v>748</v>
       </c>
@@ -32875,7 +32919,7 @@
       </c>
       <c r="W742" s="3"/>
     </row>
-    <row r="743" spans="1:23">
+    <row r="743" spans="1:23" hidden="1">
       <c r="A743">
         <v>749</v>
       </c>
@@ -32915,7 +32959,7 @@
       </c>
       <c r="W743" s="3"/>
     </row>
-    <row r="744" spans="1:23">
+    <row r="744" spans="1:23" hidden="1">
       <c r="A744">
         <v>750</v>
       </c>
@@ -32956,7 +33000,7 @@
       </c>
       <c r="W744" s="3"/>
     </row>
-    <row r="745" spans="1:23">
+    <row r="745" spans="1:23" hidden="1">
       <c r="A745">
         <v>751</v>
       </c>
@@ -32996,6 +33040,357 @@
         <v>219</v>
       </c>
       <c r="W745" s="3"/>
+    </row>
+    <row r="746" spans="1:23" hidden="1">
+      <c r="A746">
+        <v>752</v>
+      </c>
+      <c r="B746" s="4">
+        <v>46198.479733796303</v>
+      </c>
+      <c r="C746" s="4">
+        <v>46198.480671296304</v>
+      </c>
+      <c r="D746" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E746" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G746" s="1">
+        <v>46188</v>
+      </c>
+      <c r="H746" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I746" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L746" s="3"/>
+      <c r="M746" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="U746" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="V746" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="W746" s="3"/>
+    </row>
+    <row r="747" spans="1:23" hidden="1">
+      <c r="A747">
+        <v>753</v>
+      </c>
+      <c r="B747" s="4">
+        <v>46198.480740740699</v>
+      </c>
+      <c r="C747" s="4">
+        <v>46198.481261574103</v>
+      </c>
+      <c r="D747" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E747" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G747" s="1">
+        <v>46191</v>
+      </c>
+      <c r="H747" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J747" t="s">
+        <v>894</v>
+      </c>
+      <c r="L747" s="3"/>
+      <c r="M747" s="3"/>
+      <c r="T747">
+        <v>50</v>
+      </c>
+      <c r="U747" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="V747" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="W747" s="3"/>
+    </row>
+    <row r="748" spans="1:23" hidden="1">
+      <c r="A748">
+        <v>754</v>
+      </c>
+      <c r="B748" s="4">
+        <v>46198.481296296297</v>
+      </c>
+      <c r="C748" s="4">
+        <v>46198.481967592597</v>
+      </c>
+      <c r="D748" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E748" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G748" s="1">
+        <v>46136</v>
+      </c>
+      <c r="H748" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L748" s="3"/>
+      <c r="M748" s="3"/>
+      <c r="O748">
+        <v>2</v>
+      </c>
+      <c r="P748">
+        <v>0</v>
+      </c>
+      <c r="Q748">
+        <v>2</v>
+      </c>
+      <c r="R748">
+        <v>0</v>
+      </c>
+      <c r="T748">
+        <v>7</v>
+      </c>
+      <c r="U748" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="V748" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="W748" s="3"/>
+    </row>
+    <row r="749" spans="1:23" hidden="1">
+      <c r="A749">
+        <v>755</v>
+      </c>
+      <c r="B749" s="4">
+        <v>46199.639618055597</v>
+      </c>
+      <c r="C749" s="4">
+        <v>46199.640601851803</v>
+      </c>
+      <c r="D749" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E749" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G749" s="1">
+        <v>46184</v>
+      </c>
+      <c r="H749" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I749" t="s">
+        <v>944</v>
+      </c>
+      <c r="L749" s="3"/>
+      <c r="M749" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="U749" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="V749" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W749" s="3"/>
+    </row>
+    <row r="750" spans="1:23" hidden="1">
+      <c r="A750">
+        <v>756</v>
+      </c>
+      <c r="B750" s="4">
+        <v>46199.640798611101</v>
+      </c>
+      <c r="C750" s="4">
+        <v>46199.642638888901</v>
+      </c>
+      <c r="D750" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E750" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G750" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H750" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="K750" t="s">
+        <v>948</v>
+      </c>
+      <c r="L750" s="3"/>
+      <c r="M750" s="3"/>
+      <c r="T750">
+        <v>137</v>
+      </c>
+      <c r="U750" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="V750" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W750" s="3"/>
+    </row>
+    <row r="751" spans="1:23" hidden="1">
+      <c r="A751">
+        <v>757</v>
+      </c>
+      <c r="B751" s="4">
+        <v>46199.642719907402</v>
+      </c>
+      <c r="C751" s="4">
+        <v>46199.643379629597</v>
+      </c>
+      <c r="D751" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E751" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G751" s="1">
+        <v>46185</v>
+      </c>
+      <c r="H751" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L751" s="3"/>
+      <c r="M751" s="3"/>
+      <c r="O751">
+        <v>1</v>
+      </c>
+      <c r="P751">
+        <v>0</v>
+      </c>
+      <c r="Q751">
+        <v>0</v>
+      </c>
+      <c r="R751">
+        <v>0</v>
+      </c>
+      <c r="T751">
+        <v>5</v>
+      </c>
+      <c r="U751" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="V751" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W751" s="3"/>
+    </row>
+    <row r="752" spans="1:23" hidden="1">
+      <c r="A752">
+        <v>758</v>
+      </c>
+      <c r="B752" s="4">
+        <v>46199.643402777801</v>
+      </c>
+      <c r="C752" s="4">
+        <v>46199.646134259303</v>
+      </c>
+      <c r="D752" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E752" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G752" s="1">
+        <v>46190</v>
+      </c>
+      <c r="H752" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I752" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L752" s="3"/>
+      <c r="M752" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="U752" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="V752" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W752" s="3"/>
+    </row>
+    <row r="753" spans="1:23" hidden="1">
+      <c r="A753" s="6">
+        <v>759</v>
+      </c>
+      <c r="B753" s="4">
+        <v>46199.661099536999</v>
+      </c>
+      <c r="C753" s="4">
+        <v>46199.661608796298</v>
+      </c>
+      <c r="D753" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E753" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G753" s="1">
+        <v>46197</v>
+      </c>
+      <c r="H753" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I753" s="6"/>
+      <c r="J753" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="K753" s="6"/>
+      <c r="L753" s="3"/>
+      <c r="M753" s="3"/>
+      <c r="N753" s="6"/>
+      <c r="O753" s="6"/>
+      <c r="P753" s="6"/>
+      <c r="Q753" s="6"/>
+      <c r="R753" s="6"/>
+      <c r="S753" s="6"/>
+      <c r="T753" s="6">
+        <v>650</v>
+      </c>
+      <c r="U753" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="V753" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W753" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Research metrics new 1.xlsx
+++ b/data/Research metrics new 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sheddaquarium-my.sharepoint.com/personal/rcunning_sheddaquarium_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="565" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1E4632D-8426-411F-AF3B-D654A0D7D555}"/>
+  <xr:revisionPtr revIDLastSave="579" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0354CB33-FBFD-5346-8C20-368C96E91644}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5493" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5599" uniqueCount="1162">
   <si>
     <t>Id</t>
   </si>
@@ -3450,13 +3450,85 @@
   </si>
   <si>
     <t>Participated as facilitator for the IUCN Red List Assessment workshop for North American freshwater molluscs</t>
+  </si>
+  <si>
+    <t>https://www.cbsnews.com/chicago/news/holiday-weekend-storms-chicago-untreated-water-rivers/</t>
+  </si>
+  <si>
+    <t>https://www.fox32chicago.com/video/fmc-9wg9jc466neb7uoj</t>
+  </si>
+  <si>
+    <t>Provided lab tour and discussion with a visiting water quality manager from Vancouver Aquarium</t>
+  </si>
+  <si>
+    <t>Provided lab tour for vendor reps from Illumina</t>
+  </si>
+  <si>
+    <t>Provided lab tour for vendor rep from IDT</t>
+  </si>
+  <si>
+    <t>Staff from Loyola</t>
+  </si>
+  <si>
+    <t>Guided two staff members from Loyola (Larsen Lab) in the process of water sample collection and membrane filtration</t>
+  </si>
+  <si>
+    <t>Presented Lunch and Learn celebrating 10 year anniversary of the Microbiome Project and Lab and select studies.</t>
+  </si>
+  <si>
+    <t>Trapping and processing Blanding's turtles with Forest Preserve District of DuPage County</t>
+  </si>
+  <si>
+    <t>Press release</t>
+  </si>
+  <si>
+    <t>https://www.glfc.org/pubs/pressrel/2026_Advisors_Urge_Action_Invasive_Mussels.pdf</t>
+  </si>
+  <si>
+    <t>Press release related to US and Canadian Advisor resolutions - Murchie is public at large advisor for IL</t>
+  </si>
+  <si>
+    <t>PENIP coral and conch surveys with SeaKeepers</t>
+  </si>
+  <si>
+    <t>Career chat with student</t>
+  </si>
+  <si>
+    <t>Met with an aspiring Marine Biology student from Miami University, Ohio, to discuss career paths and opportunities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuder, J., Kessel, S.T., Brunnschweiler, J., Kerstetter, D. (2026). Crossing the Gulf Stream: Movements of Adult Lemon Sharks (Negaprion brevirostris) Between the Southeastern Florida and Western Bahamas Shelves. Caribbean Journal of Science, 56(2), 404-415. https://doi.org/10.18475/cjos.v56i2.a2 </t>
+  </si>
+  <si>
+    <t>https://bioone.org/journals/caribbean-journal-of-science/volume-56/issue-2/cjos.v56i2.a2/Crossing-the-Gulf-Stream--Movements-of-Adult-Lemon-Sharks/10.18475/cjos.v56i2.a2.full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon shark depth and horizontal movement </t>
+  </si>
+  <si>
+    <t>Emerging Leaders Program for Chicago Council on Global Affairs</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Huffmyer AS, Strand EL, Hackerott S, Wong KH, Becker DM, Conetta D, Terpis KX, Pfab F, Wong JM, Dellaert Z, Oliaro FJ, Cunning R, Eirin-Lopez JM, Roberts SB, Nisbet RM, Putnam HM (2026) Seasonal physiological strategies reveal contrasting host–symbiont dynamics among dominant Indo-Pacific reef-building corals. Ecology and Evolution 16:e74044. http://doi.org/10.1002/ece3.74044</t>
+  </si>
+  <si>
+    <t>http://doi.org/10.1002/ece3.74044</t>
+  </si>
+  <si>
+    <t>https://www.sierraclub.org/sierra/financial-and-ecological-risks-contested-florida-dredging-project</t>
+  </si>
+  <si>
+    <t>Sierra Club magazine story on Port Everglades dredging, with interview from me</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3572,8 +3644,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W780" totalsRowShown="0">
-  <autoFilter ref="A1:W780" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W795" totalsRowShown="0">
+  <autoFilter ref="A1:W795" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W744">
     <sortCondition ref="B1:B744"/>
   </sortState>
@@ -3743,7 +3815,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="786" latestEventMarker="824">
+      <xlmsforms:msForm id="WmKV9QsF-ESGzEsfiGZoTb83Sl3n5wlHr3isCMIkazlUREdPWjQwWjdHU1IxNFdNOVVTSVpHNktFSi4u" isFormConnected="1" maxResponseId="801" latestEventMarker="839">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4070,21 +4142,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W780"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:W795"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="19" customWidth="1"/>
     <col min="12" max="13" width="20" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="52.7109375" customWidth="1"/>
-    <col min="16" max="16" width="48.42578125" customWidth="1"/>
-    <col min="17" max="17" width="46.85546875" customWidth="1"/>
-    <col min="18" max="18" width="50.28515625" customWidth="1"/>
+    <col min="15" max="15" width="52.6640625" customWidth="1"/>
+    <col min="16" max="16" width="48.5" customWidth="1"/>
+    <col min="17" max="17" width="46.83203125" customWidth="1"/>
+    <col min="18" max="18" width="50.33203125" customWidth="1"/>
     <col min="21" max="21" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4155,7 +4227,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4193,7 +4265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4228,7 +4300,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4263,7 +4335,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4298,7 +4370,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4333,7 +4405,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4368,7 +4440,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4403,7 +4475,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4438,7 +4510,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4473,7 +4545,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4508,7 +4580,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4546,7 +4618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4584,7 +4656,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4622,7 +4694,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4660,7 +4732,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4698,7 +4770,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4736,7 +4808,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4771,7 +4843,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4806,7 +4878,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4844,7 +4916,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4879,7 +4951,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4917,7 +4989,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4952,7 +5024,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4993,7 +5065,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5028,7 +5100,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5063,7 +5135,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5095,7 +5167,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5130,7 +5202,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5162,7 +5234,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5200,7 +5272,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5241,7 +5313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5279,7 +5351,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5320,7 +5392,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5361,7 +5433,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5402,7 +5474,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5443,7 +5515,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5484,7 +5556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5525,7 +5597,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5560,7 +5632,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5595,7 +5667,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5630,7 +5702,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5665,7 +5737,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5703,7 +5775,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5741,7 +5813,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5776,7 +5848,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5811,7 +5883,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5846,7 +5918,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5884,7 +5956,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5916,7 +5988,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5954,7 +6026,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5989,7 +6061,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6021,7 +6093,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6059,7 +6131,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6094,7 +6166,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6129,7 +6201,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6167,7 +6239,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6205,7 +6277,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6243,7 +6315,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6281,7 +6353,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6319,7 +6391,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6357,7 +6429,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>67</v>
       </c>
@@ -6389,7 +6461,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:23">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>61</v>
       </c>
@@ -6424,7 +6496,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>62</v>
       </c>
@@ -6462,7 +6534,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>63</v>
       </c>
@@ -6500,7 +6572,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>64</v>
       </c>
@@ -6535,7 +6607,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>65</v>
       </c>
@@ -6570,7 +6642,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>66</v>
       </c>
@@ -6611,7 +6683,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6643,7 +6715,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6678,7 +6750,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6713,7 +6785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6751,7 +6823,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6789,7 +6861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6830,7 +6902,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6871,7 +6943,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6906,7 +6978,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6944,7 +7016,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6985,7 +7057,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:23">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7020,7 +7092,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:23">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7061,7 +7133,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7099,7 +7171,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7137,7 +7209,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7175,7 +7247,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7216,7 +7288,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7254,7 +7326,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7295,7 +7367,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" spans="1:23">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7327,7 +7399,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:23">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7359,7 +7431,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="89" spans="1:23">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>95</v>
       </c>
@@ -7397,7 +7469,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>88</v>
       </c>
@@ -7438,7 +7510,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>89</v>
       </c>
@@ -7473,7 +7545,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>90</v>
       </c>
@@ -7508,7 +7580,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:23">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>91</v>
       </c>
@@ -7543,7 +7615,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:23">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>92</v>
       </c>
@@ -7584,7 +7656,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:23">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>93</v>
       </c>
@@ -7622,7 +7694,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:23">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>94</v>
       </c>
@@ -7657,7 +7729,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7695,7 +7767,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7730,7 +7802,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7768,7 +7840,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:23">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7803,7 +7875,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7838,7 +7910,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="102" spans="1:23">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7878,7 +7950,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="103" spans="1:23">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7918,7 +7990,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="104" spans="1:23">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7958,7 +8030,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:23">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7995,7 +8067,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="106" spans="1:23">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8032,7 +8104,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8069,7 +8141,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8106,7 +8178,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8143,7 +8215,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="110" spans="1:23">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8178,7 +8250,7 @@
       </c>
       <c r="W110" s="3"/>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8221,7 +8293,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8264,7 +8336,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8301,7 +8373,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:23">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8344,7 +8416,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:23">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8383,7 +8455,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="116" spans="1:23">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8420,7 +8492,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="117" spans="1:23">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8457,7 +8529,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="118" spans="1:23">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8496,7 +8568,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="119" spans="1:23">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8531,7 +8603,7 @@
       </c>
       <c r="W119" s="3"/>
     </row>
-    <row r="120" spans="1:23">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8569,7 +8641,7 @@
       </c>
       <c r="W120" s="3"/>
     </row>
-    <row r="121" spans="1:23">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8609,7 +8681,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8649,7 +8721,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="123" spans="1:23">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8689,7 +8761,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8729,7 +8801,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:23">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8769,7 +8841,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="126" spans="1:23">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8812,7 +8884,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8855,7 +8927,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="128" spans="1:23">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8896,7 +8968,7 @@
       </c>
       <c r="W128" s="3"/>
     </row>
-    <row r="129" spans="1:23">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8937,7 +9009,7 @@
       </c>
       <c r="W129" s="3"/>
     </row>
-    <row r="130" spans="1:23">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8980,7 +9052,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="131" spans="1:23">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -9017,7 +9089,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -9054,7 +9126,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="133" spans="1:23">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -9091,7 +9163,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="134" spans="1:23">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -9134,7 +9206,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="135" spans="1:23">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -9174,7 +9246,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="136" spans="1:23">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -9214,7 +9286,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="137" spans="1:23">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -9253,7 +9325,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:23">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -9292,7 +9364,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="139" spans="1:23">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -9335,7 +9407,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="140" spans="1:23">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -9375,7 +9447,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="141" spans="1:23">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -9414,7 +9486,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="142" spans="1:23">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -9453,7 +9525,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="143" spans="1:23">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -9492,7 +9564,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="144" spans="1:23">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -9532,7 +9604,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="145" spans="1:23">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -9575,7 +9647,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="146" spans="1:23">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -9614,7 +9686,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="147" spans="1:23">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -9651,7 +9723,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="148" spans="1:23">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
@@ -9688,7 +9760,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="149" spans="1:23">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
@@ -9725,7 +9797,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="150" spans="1:23">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>149</v>
       </c>
@@ -9768,7 +9840,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="151" spans="1:23">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -9811,7 +9883,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="152" spans="1:23">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
@@ -9850,7 +9922,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="153" spans="1:23">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>152</v>
       </c>
@@ -9889,7 +9961,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
@@ -9926,7 +9998,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="155" spans="1:23">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -9965,7 +10037,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:23">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -10005,7 +10077,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="157" spans="1:23">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>156</v>
       </c>
@@ -10045,7 +10117,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="158" spans="1:23">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>157</v>
       </c>
@@ -10085,7 +10157,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="159" spans="1:23">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -10125,7 +10197,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="160" spans="1:23">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>159</v>
       </c>
@@ -10168,7 +10240,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:23">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>160</v>
       </c>
@@ -10211,7 +10283,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="162" spans="1:23">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>161</v>
       </c>
@@ -10248,7 +10320,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="163" spans="1:23">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>162</v>
       </c>
@@ -10287,7 +10359,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="164" spans="1:23">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>163</v>
       </c>
@@ -10324,7 +10396,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:23">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -10361,7 +10433,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="166" spans="1:23">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165</v>
       </c>
@@ -10396,7 +10468,7 @@
       </c>
       <c r="W166" s="3"/>
     </row>
-    <row r="167" spans="1:23">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166</v>
       </c>
@@ -10435,7 +10507,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="168" spans="1:23">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -10474,7 +10546,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="169" spans="1:23">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
@@ -10514,7 +10586,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="170" spans="1:23">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>169</v>
       </c>
@@ -10557,7 +10629,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="171" spans="1:23">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>170</v>
       </c>
@@ -10600,7 +10672,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="172" spans="1:23">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -10637,7 +10709,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="173" spans="1:23">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>172</v>
       </c>
@@ -10674,7 +10746,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="174" spans="1:23">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>173</v>
       </c>
@@ -10713,7 +10785,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="175" spans="1:23">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>174</v>
       </c>
@@ -10753,7 +10825,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="176" spans="1:23">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -10793,7 +10865,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="177" spans="1:23">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -10833,7 +10905,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="178" spans="1:23">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>177</v>
       </c>
@@ -10876,7 +10948,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="179" spans="1:23">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>178</v>
       </c>
@@ -10919,7 +10991,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="180" spans="1:23">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>179</v>
       </c>
@@ -10962,7 +11034,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="181" spans="1:23">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11001,7 +11073,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="182" spans="1:23">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>182</v>
       </c>
@@ -11040,7 +11112,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="183" spans="1:23">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>183</v>
       </c>
@@ -11083,7 +11155,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="184" spans="1:23">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>184</v>
       </c>
@@ -11120,7 +11192,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="185" spans="1:23">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>185</v>
       </c>
@@ -11163,7 +11235,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="186" spans="1:23">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>186</v>
       </c>
@@ -11206,7 +11278,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="187" spans="1:23">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>187</v>
       </c>
@@ -11243,7 +11315,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="188" spans="1:23">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>188</v>
       </c>
@@ -11286,7 +11358,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="189" spans="1:23">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>189</v>
       </c>
@@ -11329,7 +11401,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="190" spans="1:23">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>190</v>
       </c>
@@ -11366,7 +11438,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="191" spans="1:23">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>191</v>
       </c>
@@ -11409,7 +11481,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="192" spans="1:23">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>192</v>
       </c>
@@ -11446,7 +11518,7 @@
       </c>
       <c r="W192" s="3"/>
     </row>
-    <row r="193" spans="1:23">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>193</v>
       </c>
@@ -11485,7 +11557,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="194" spans="1:23">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>194</v>
       </c>
@@ -11524,7 +11596,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="195" spans="1:23">
+    <row r="195" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>195</v>
       </c>
@@ -11565,7 +11637,7 @@
       </c>
       <c r="W195" s="3"/>
     </row>
-    <row r="196" spans="1:23">
+    <row r="196" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>196</v>
       </c>
@@ -11604,7 +11676,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="1:23">
+    <row r="197" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>197</v>
       </c>
@@ -11645,7 +11717,7 @@
       </c>
       <c r="W197" s="3"/>
     </row>
-    <row r="198" spans="1:23">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>198</v>
       </c>
@@ -11686,7 +11758,7 @@
       </c>
       <c r="W198" s="3"/>
     </row>
-    <row r="199" spans="1:23">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>199</v>
       </c>
@@ -11726,7 +11798,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="200" spans="1:23">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>200</v>
       </c>
@@ -11763,7 +11835,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="201" spans="1:23">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>201</v>
       </c>
@@ -11800,7 +11872,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="202" spans="1:23">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>202</v>
       </c>
@@ -11837,7 +11909,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="203" spans="1:23">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>223</v>
       </c>
@@ -11874,7 +11946,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="204" spans="1:23">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>203</v>
       </c>
@@ -11911,7 +11983,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:23">
+    <row r="205" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>204</v>
       </c>
@@ -11951,7 +12023,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="206" spans="1:23">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>205</v>
       </c>
@@ -11986,7 +12058,7 @@
       </c>
       <c r="W206" s="3"/>
     </row>
-    <row r="207" spans="1:23">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12025,7 +12097,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="208" spans="1:23">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12064,7 +12136,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="209" spans="1:23">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12104,7 +12176,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="210" spans="1:23">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12139,7 +12211,7 @@
       </c>
       <c r="W210" s="3"/>
     </row>
-    <row r="211" spans="1:23">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12177,7 +12249,7 @@
       </c>
       <c r="W211" s="3"/>
     </row>
-    <row r="212" spans="1:23">
+    <row r="212" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12215,7 +12287,7 @@
       </c>
       <c r="W212" s="3"/>
     </row>
-    <row r="213" spans="1:23">
+    <row r="213" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12253,7 +12325,7 @@
       </c>
       <c r="W213" s="3"/>
     </row>
-    <row r="214" spans="1:23">
+    <row r="214" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12290,7 +12362,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="215" spans="1:23">
+    <row r="215" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12325,7 +12397,7 @@
       </c>
       <c r="W215" s="3"/>
     </row>
-    <row r="216" spans="1:23">
+    <row r="216" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12360,7 +12432,7 @@
       </c>
       <c r="W216" s="3"/>
     </row>
-    <row r="217" spans="1:23">
+    <row r="217" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12397,7 +12469,7 @@
       </c>
       <c r="W217" s="3"/>
     </row>
-    <row r="218" spans="1:23">
+    <row r="218" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12434,7 +12506,7 @@
       </c>
       <c r="W218" s="3"/>
     </row>
-    <row r="219" spans="1:23">
+    <row r="219" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12473,7 +12545,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="220" spans="1:23">
+    <row r="220" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12510,7 +12582,7 @@
       </c>
       <c r="W220" s="3"/>
     </row>
-    <row r="221" spans="1:23">
+    <row r="221" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12549,7 +12621,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:23">
+    <row r="222" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12590,7 +12662,7 @@
       </c>
       <c r="W222" s="3"/>
     </row>
-    <row r="223" spans="1:23">
+    <row r="223" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12630,7 +12702,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="224" spans="1:23">
+    <row r="224" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>224</v>
       </c>
@@ -12670,7 +12742,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="225" spans="1:23">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>225</v>
       </c>
@@ -12713,7 +12785,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="226" spans="1:23">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>226</v>
       </c>
@@ -12753,7 +12825,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="227" spans="1:23">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>227</v>
       </c>
@@ -12793,7 +12865,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="228" spans="1:23">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>228</v>
       </c>
@@ -12830,7 +12902,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="229" spans="1:23">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>229</v>
       </c>
@@ -12873,7 +12945,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="230" spans="1:23">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>230</v>
       </c>
@@ -12913,7 +12985,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="231" spans="1:23">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>231</v>
       </c>
@@ -12953,7 +13025,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="232" spans="1:23">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>232</v>
       </c>
@@ -12990,7 +13062,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="233" spans="1:23">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>233</v>
       </c>
@@ -13033,7 +13105,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="234" spans="1:23">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>234</v>
       </c>
@@ -13072,7 +13144,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="235" spans="1:23">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>235</v>
       </c>
@@ -13111,7 +13183,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="236" spans="1:23">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>236</v>
       </c>
@@ -13152,7 +13224,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="237" spans="1:23">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>237</v>
       </c>
@@ -13189,7 +13261,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="238" spans="1:23">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>238</v>
       </c>
@@ -13229,7 +13301,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="239" spans="1:23">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>239</v>
       </c>
@@ -13269,7 +13341,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="240" spans="1:23">
+    <row r="240" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>240</v>
       </c>
@@ -13304,7 +13376,7 @@
       </c>
       <c r="W240" s="3"/>
     </row>
-    <row r="241" spans="1:23">
+    <row r="241" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>241</v>
       </c>
@@ -13339,7 +13411,7 @@
       </c>
       <c r="W241" s="3"/>
     </row>
-    <row r="242" spans="1:23">
+    <row r="242" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>242</v>
       </c>
@@ -13379,7 +13451,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="243" spans="1:23">
+    <row r="243" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>243</v>
       </c>
@@ -13414,7 +13486,7 @@
       </c>
       <c r="W243" s="3"/>
     </row>
-    <row r="244" spans="1:23">
+    <row r="244" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>244</v>
       </c>
@@ -13453,7 +13525,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="245" spans="1:23">
+    <row r="245" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>246</v>
       </c>
@@ -13490,7 +13562,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:23">
+    <row r="246" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>245</v>
       </c>
@@ -13530,7 +13602,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="247" spans="1:23">
+    <row r="247" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>247</v>
       </c>
@@ -13570,7 +13642,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="248" spans="1:23">
+    <row r="248" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>248</v>
       </c>
@@ -13607,7 +13679,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="249" spans="1:23">
+    <row r="249" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>249</v>
       </c>
@@ -13646,7 +13718,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="250" spans="1:23">
+    <row r="250" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>251</v>
       </c>
@@ -13689,7 +13761,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="251" spans="1:23">
+    <row r="251" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13724,7 +13796,7 @@
       </c>
       <c r="W251" s="3"/>
     </row>
-    <row r="252" spans="1:23">
+    <row r="252" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>252</v>
       </c>
@@ -13765,7 +13837,7 @@
       </c>
       <c r="W252" s="3"/>
     </row>
-    <row r="253" spans="1:23">
+    <row r="253" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
       <c r="D253" s="3"/>
@@ -13779,7 +13851,7 @@
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
     </row>
-    <row r="254" spans="1:23">
+    <row r="254" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>256</v>
       </c>
@@ -13819,7 +13891,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="255" spans="1:23">
+    <row r="255" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>253</v>
       </c>
@@ -13856,7 +13928,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="256" spans="1:23">
+    <row r="256" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>255</v>
       </c>
@@ -13893,7 +13965,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="257" spans="1:23">
+    <row r="257" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>254</v>
       </c>
@@ -13930,7 +14002,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="258" spans="1:23">
+    <row r="258" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>257</v>
       </c>
@@ -13973,7 +14045,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="259" spans="1:23">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>258</v>
       </c>
@@ -14010,7 +14082,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="260" spans="1:23">
+    <row r="260" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>259</v>
       </c>
@@ -14050,7 +14122,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="261" spans="1:23">
+    <row r="261" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>260</v>
       </c>
@@ -14090,7 +14162,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="262" spans="1:23">
+    <row r="262" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>261</v>
       </c>
@@ -14127,7 +14199,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="263" spans="1:23">
+    <row r="263" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>262</v>
       </c>
@@ -14167,7 +14239,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="264" spans="1:23">
+    <row r="264" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>263</v>
       </c>
@@ -14207,7 +14279,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="265" spans="1:23">
+    <row r="265" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>264</v>
       </c>
@@ -14247,7 +14319,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>265</v>
       </c>
@@ -14284,7 +14356,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="267" spans="1:23">
+    <row r="267" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>266</v>
       </c>
@@ -14324,7 +14396,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>267</v>
       </c>
@@ -14361,7 +14433,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>268</v>
       </c>
@@ -14398,7 +14470,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="270" spans="1:23">
+    <row r="270" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>269</v>
       </c>
@@ -14441,7 +14513,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="271" spans="1:23">
+    <row r="271" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>270</v>
       </c>
@@ -14480,7 +14552,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="272" spans="1:23">
+    <row r="272" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>271</v>
       </c>
@@ -14521,7 +14593,7 @@
       </c>
       <c r="W272" s="3"/>
     </row>
-    <row r="273" spans="1:23">
+    <row r="273" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>272</v>
       </c>
@@ -14564,7 +14636,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>276</v>
       </c>
@@ -14605,7 +14677,7 @@
       </c>
       <c r="W274" s="3"/>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>273</v>
       </c>
@@ -14648,7 +14720,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>274</v>
       </c>
@@ -14688,7 +14760,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="277" spans="1:23">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>275</v>
       </c>
@@ -14728,7 +14800,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="278" spans="1:23">
+    <row r="278" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>277</v>
       </c>
@@ -14769,7 +14841,7 @@
       </c>
       <c r="W278" s="3"/>
     </row>
-    <row r="279" spans="1:23">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>278</v>
       </c>
@@ -14804,7 +14876,7 @@
       </c>
       <c r="W279" s="3"/>
     </row>
-    <row r="280" spans="1:23">
+    <row r="280" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>279</v>
       </c>
@@ -14842,7 +14914,7 @@
       </c>
       <c r="W280" s="3"/>
     </row>
-    <row r="281" spans="1:23">
+    <row r="281" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>280</v>
       </c>
@@ -14885,7 +14957,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="282" spans="1:23">
+    <row r="282" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>281</v>
       </c>
@@ -14925,7 +14997,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="283" spans="1:23">
+    <row r="283" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>282</v>
       </c>
@@ -14965,7 +15037,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="284" spans="1:23">
+    <row r="284" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>283</v>
       </c>
@@ -15005,7 +15077,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="285" spans="1:23">
+    <row r="285" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>284</v>
       </c>
@@ -15045,7 +15117,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="286" spans="1:23">
+    <row r="286" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>285</v>
       </c>
@@ -15082,7 +15154,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="287" spans="1:23">
+    <row r="287" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>286</v>
       </c>
@@ -15125,7 +15197,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="288" spans="1:23">
+    <row r="288" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>287</v>
       </c>
@@ -15162,7 +15234,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="289" spans="1:23">
+    <row r="289" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>288</v>
       </c>
@@ -15205,7 +15277,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="290" spans="1:23">
+    <row r="290" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>289</v>
       </c>
@@ -15245,7 +15317,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="291" spans="1:23">
+    <row r="291" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>290</v>
       </c>
@@ -15282,7 +15354,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="292" spans="1:23">
+    <row r="292" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>291</v>
       </c>
@@ -15325,7 +15397,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="293" spans="1:23">
+    <row r="293" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>292</v>
       </c>
@@ -15368,7 +15440,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="294" spans="1:23">
+    <row r="294" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>294</v>
       </c>
@@ -15407,7 +15479,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="295" spans="1:23">
+    <row r="295" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>293</v>
       </c>
@@ -15450,7 +15522,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
@@ -15487,7 +15559,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="297" spans="1:23">
+    <row r="297" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
@@ -15526,7 +15598,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="298" spans="1:23">
+    <row r="298" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
@@ -15565,7 +15637,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="299" spans="1:23">
+    <row r="299" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
@@ -15604,7 +15676,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="300" spans="1:23">
+    <row r="300" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
@@ -15643,7 +15715,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="301" spans="1:23">
+    <row r="301" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
@@ -15682,7 +15754,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="302" spans="1:23">
+    <row r="302" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>301</v>
       </c>
@@ -15721,7 +15793,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="303" spans="1:23">
+    <row r="303" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>302</v>
       </c>
@@ -15760,7 +15832,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="304" spans="1:23">
+    <row r="304" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>303</v>
       </c>
@@ -15799,7 +15871,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="305" spans="1:23">
+    <row r="305" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>304</v>
       </c>
@@ -15838,7 +15910,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="306" spans="1:23">
+    <row r="306" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>305</v>
       </c>
@@ -15877,7 +15949,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="307" spans="1:23">
+    <row r="307" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>306</v>
       </c>
@@ -15915,7 +15987,7 @@
       </c>
       <c r="W307" s="3"/>
     </row>
-    <row r="308" spans="1:23">
+    <row r="308" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>307</v>
       </c>
@@ -15954,7 +16026,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="309" spans="1:23">
+    <row r="309" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>308</v>
       </c>
@@ -15993,7 +16065,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="310" spans="1:23">
+    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>309</v>
       </c>
@@ -16030,7 +16102,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="311" spans="1:23">
+    <row r="311" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>310</v>
       </c>
@@ -16067,7 +16139,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="312" spans="1:23">
+    <row r="312" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>311</v>
       </c>
@@ -16104,7 +16176,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="313" spans="1:23">
+    <row r="313" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>312</v>
       </c>
@@ -16144,7 +16216,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="314" spans="1:23">
+    <row r="314" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>313</v>
       </c>
@@ -16181,7 +16253,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="315" spans="1:23">
+    <row r="315" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>314</v>
       </c>
@@ -16216,7 +16288,7 @@
       </c>
       <c r="W315" s="3"/>
     </row>
-    <row r="316" spans="1:23">
+    <row r="316" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>315</v>
       </c>
@@ -16253,7 +16325,7 @@
       </c>
       <c r="W316" s="3"/>
     </row>
-    <row r="317" spans="1:23">
+    <row r="317" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>316</v>
       </c>
@@ -16288,7 +16360,7 @@
       </c>
       <c r="W317" s="3"/>
     </row>
-    <row r="318" spans="1:23">
+    <row r="318" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>317</v>
       </c>
@@ -16325,7 +16397,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="319" spans="1:23">
+    <row r="319" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>318</v>
       </c>
@@ -16360,7 +16432,7 @@
       </c>
       <c r="W319" s="3"/>
     </row>
-    <row r="320" spans="1:23">
+    <row r="320" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>319</v>
       </c>
@@ -16399,7 +16471,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="321" spans="1:23">
+    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>320</v>
       </c>
@@ -16434,7 +16506,7 @@
       </c>
       <c r="W321" s="3"/>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>321</v>
       </c>
@@ -16471,7 +16543,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="323" spans="1:23">
+    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>322</v>
       </c>
@@ -16508,7 +16580,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="324" spans="1:23">
+    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>323</v>
       </c>
@@ -16545,7 +16617,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="325" spans="1:23">
+    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>324</v>
       </c>
@@ -16584,7 +16656,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="326" spans="1:23">
+    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>325</v>
       </c>
@@ -16621,7 +16693,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="327" spans="1:23">
+    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>326</v>
       </c>
@@ -16660,7 +16732,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="328" spans="1:23">
+    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>327</v>
       </c>
@@ -16695,7 +16767,7 @@
       </c>
       <c r="W328" s="3"/>
     </row>
-    <row r="329" spans="1:23">
+    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>328</v>
       </c>
@@ -16730,7 +16802,7 @@
       </c>
       <c r="W329" s="3"/>
     </row>
-    <row r="330" spans="1:23">
+    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>329</v>
       </c>
@@ -16765,7 +16837,7 @@
       </c>
       <c r="W330" s="3"/>
     </row>
-    <row r="331" spans="1:23">
+    <row r="331" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>330</v>
       </c>
@@ -16800,7 +16872,7 @@
       </c>
       <c r="W331" s="3"/>
     </row>
-    <row r="332" spans="1:23">
+    <row r="332" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>331</v>
       </c>
@@ -16835,7 +16907,7 @@
       </c>
       <c r="W332" s="3"/>
     </row>
-    <row r="333" spans="1:23">
+    <row r="333" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>332</v>
       </c>
@@ -16874,7 +16946,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="334" spans="1:23">
+    <row r="334" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>333</v>
       </c>
@@ -16911,7 +16983,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="335" spans="1:23">
+    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>334</v>
       </c>
@@ -16951,7 +17023,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="336" spans="1:23">
+    <row r="336" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>335</v>
       </c>
@@ -16990,7 +17062,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="337" spans="1:23">
+    <row r="337" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>336</v>
       </c>
@@ -17027,7 +17099,7 @@
       </c>
       <c r="W337" s="3"/>
     </row>
-    <row r="338" spans="1:23">
+    <row r="338" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>337</v>
       </c>
@@ -17064,7 +17136,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="339" spans="1:23">
+    <row r="339" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>338</v>
       </c>
@@ -17101,7 +17173,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="340" spans="1:23">
+    <row r="340" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>339</v>
       </c>
@@ -17138,7 +17210,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="341" spans="1:23">
+    <row r="341" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>340</v>
       </c>
@@ -17175,7 +17247,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="342" spans="1:23">
+    <row r="342" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>341</v>
       </c>
@@ -17218,7 +17290,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="343" spans="1:23">
+    <row r="343" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>342</v>
       </c>
@@ -17255,7 +17327,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="344" spans="1:23">
+    <row r="344" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>343</v>
       </c>
@@ -17290,7 +17362,7 @@
       </c>
       <c r="W344" s="3"/>
     </row>
-    <row r="345" spans="1:23">
+    <row r="345" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>344</v>
       </c>
@@ -17331,7 +17403,7 @@
       </c>
       <c r="W345" s="3"/>
     </row>
-    <row r="346" spans="1:23">
+    <row r="346" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>345</v>
       </c>
@@ -17374,7 +17446,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="347" spans="1:23">
+    <row r="347" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>346</v>
       </c>
@@ -17417,7 +17489,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="348" spans="1:23">
+    <row r="348" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>347</v>
       </c>
@@ -17456,7 +17528,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="349" spans="1:23">
+    <row r="349" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>348</v>
       </c>
@@ -17499,7 +17571,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="350" spans="1:23">
+    <row r="350" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>349</v>
       </c>
@@ -17536,7 +17608,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="351" spans="1:23">
+    <row r="351" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>350</v>
       </c>
@@ -17576,7 +17648,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="352" spans="1:23">
+    <row r="352" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>351</v>
       </c>
@@ -17611,7 +17683,7 @@
       </c>
       <c r="W352" s="3"/>
     </row>
-    <row r="353" spans="1:23">
+    <row r="353" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>352</v>
       </c>
@@ -17654,7 +17726,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="354" spans="1:23">
+    <row r="354" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>353</v>
       </c>
@@ -17691,7 +17763,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="355" spans="1:23">
+    <row r="355" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>354</v>
       </c>
@@ -17730,7 +17802,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="356" spans="1:23">
+    <row r="356" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>355</v>
       </c>
@@ -17767,7 +17839,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="357" spans="1:23">
+    <row r="357" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>356</v>
       </c>
@@ -17804,7 +17876,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="358" spans="1:23">
+    <row r="358" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>357</v>
       </c>
@@ -17843,7 +17915,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="359" spans="1:23">
+    <row r="359" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>358</v>
       </c>
@@ -17882,7 +17954,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="360" spans="1:23">
+    <row r="360" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>359</v>
       </c>
@@ -17922,7 +17994,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="361" spans="1:23">
+    <row r="361" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>360</v>
       </c>
@@ -17965,7 +18037,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="362" spans="1:23">
+    <row r="362" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>361</v>
       </c>
@@ -18002,7 +18074,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="363" spans="1:23">
+    <row r="363" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>362</v>
       </c>
@@ -18041,7 +18113,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="364" spans="1:23">
+    <row r="364" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>363</v>
       </c>
@@ -18080,7 +18152,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="365" spans="1:23">
+    <row r="365" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>364</v>
       </c>
@@ -18117,7 +18189,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="366" spans="1:23">
+    <row r="366" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>365</v>
       </c>
@@ -18156,7 +18228,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="367" spans="1:23">
+    <row r="367" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>366</v>
       </c>
@@ -18195,7 +18267,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="368" spans="1:23">
+    <row r="368" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>367</v>
       </c>
@@ -18232,7 +18304,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="369" spans="1:23">
+    <row r="369" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>368</v>
       </c>
@@ -18269,7 +18341,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="370" spans="1:23">
+    <row r="370" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>369</v>
       </c>
@@ -18306,7 +18378,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="371" spans="1:23">
+    <row r="371" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>370</v>
       </c>
@@ -18349,7 +18421,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="372" spans="1:23">
+    <row r="372" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>371</v>
       </c>
@@ -18386,7 +18458,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="373" spans="1:23">
+    <row r="373" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>372</v>
       </c>
@@ -18423,7 +18495,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="374" spans="1:23">
+    <row r="374" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>373</v>
       </c>
@@ -18466,7 +18538,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="375" spans="1:23">
+    <row r="375" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>374</v>
       </c>
@@ -18503,7 +18575,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="376" spans="1:23">
+    <row r="376" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>375</v>
       </c>
@@ -18546,7 +18618,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="377" spans="1:23">
+    <row r="377" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>376</v>
       </c>
@@ -18586,7 +18658,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="378" spans="1:23">
+    <row r="378" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>377</v>
       </c>
@@ -18623,7 +18695,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="379" spans="1:23">
+    <row r="379" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>378</v>
       </c>
@@ -18660,7 +18732,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="380" spans="1:23">
+    <row r="380" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>379</v>
       </c>
@@ -18697,7 +18769,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="381" spans="1:23">
+    <row r="381" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>380</v>
       </c>
@@ -18737,7 +18809,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="382" spans="1:23">
+    <row r="382" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>381</v>
       </c>
@@ -18777,7 +18849,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="383" spans="1:23">
+    <row r="383" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>382</v>
       </c>
@@ -18814,7 +18886,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="384" spans="1:23">
+    <row r="384" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>383</v>
       </c>
@@ -18853,7 +18925,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="385" spans="1:23">
+    <row r="385" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>384</v>
       </c>
@@ -18892,7 +18964,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="386" spans="1:23">
+    <row r="386" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>385</v>
       </c>
@@ -18931,7 +19003,7 @@
       </c>
       <c r="W386" s="3"/>
     </row>
-    <row r="387" spans="1:23">
+    <row r="387" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>386</v>
       </c>
@@ -18970,7 +19042,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="388" spans="1:23">
+    <row r="388" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>387</v>
       </c>
@@ -19010,7 +19082,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="389" spans="1:23">
+    <row r="389" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>388</v>
       </c>
@@ -19050,7 +19122,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="390" spans="1:23">
+    <row r="390" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>389</v>
       </c>
@@ -19091,7 +19163,7 @@
       </c>
       <c r="W390" s="3"/>
     </row>
-    <row r="391" spans="1:23">
+    <row r="391" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>390</v>
       </c>
@@ -19132,7 +19204,7 @@
       </c>
       <c r="W391" s="3"/>
     </row>
-    <row r="392" spans="1:23">
+    <row r="392" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>391</v>
       </c>
@@ -19173,7 +19245,7 @@
       </c>
       <c r="W392" s="3"/>
     </row>
-    <row r="393" spans="1:23">
+    <row r="393" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>392</v>
       </c>
@@ -19214,7 +19286,7 @@
       </c>
       <c r="W393" s="3"/>
     </row>
-    <row r="394" spans="1:23">
+    <row r="394" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>393</v>
       </c>
@@ -19251,7 +19323,7 @@
       </c>
       <c r="W394" s="3"/>
     </row>
-    <row r="395" spans="1:23">
+    <row r="395" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>394</v>
       </c>
@@ -19286,7 +19358,7 @@
       </c>
       <c r="W395" s="3"/>
     </row>
-    <row r="396" spans="1:23">
+    <row r="396" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>395</v>
       </c>
@@ -19323,7 +19395,7 @@
       </c>
       <c r="W396" s="3"/>
     </row>
-    <row r="397" spans="1:23">
+    <row r="397" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>396</v>
       </c>
@@ -19358,7 +19430,7 @@
       </c>
       <c r="W397" s="3"/>
     </row>
-    <row r="398" spans="1:23">
+    <row r="398" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>397</v>
       </c>
@@ -19393,7 +19465,7 @@
       </c>
       <c r="W398" s="3"/>
     </row>
-    <row r="399" spans="1:23">
+    <row r="399" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>398</v>
       </c>
@@ -19428,7 +19500,7 @@
       </c>
       <c r="W399" s="3"/>
     </row>
-    <row r="400" spans="1:23">
+    <row r="400" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>399</v>
       </c>
@@ -19463,7 +19535,7 @@
       </c>
       <c r="W400" s="3"/>
     </row>
-    <row r="401" spans="1:23">
+    <row r="401" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>400</v>
       </c>
@@ -19504,7 +19576,7 @@
       </c>
       <c r="W401" s="3"/>
     </row>
-    <row r="402" spans="1:23">
+    <row r="402" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>401</v>
       </c>
@@ -19543,7 +19615,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="403" spans="1:23">
+    <row r="403" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>402</v>
       </c>
@@ -19582,7 +19654,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="404" spans="1:23">
+    <row r="404" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>403</v>
       </c>
@@ -19625,7 +19697,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="405" spans="1:23">
+    <row r="405" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>404</v>
       </c>
@@ -19668,7 +19740,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="406" spans="1:23">
+    <row r="406" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>405</v>
       </c>
@@ -19711,7 +19783,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="407" spans="1:23">
+    <row r="407" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>406</v>
       </c>
@@ -19748,7 +19820,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="408" spans="1:23">
+    <row r="408" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>407</v>
       </c>
@@ -19791,7 +19863,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="409" spans="1:23">
+    <row r="409" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>408</v>
       </c>
@@ -19834,7 +19906,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="410" spans="1:23">
+    <row r="410" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>409</v>
       </c>
@@ -19877,7 +19949,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="411" spans="1:23">
+    <row r="411" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>410</v>
       </c>
@@ -19916,7 +19988,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="412" spans="1:23">
+    <row r="412" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>411</v>
       </c>
@@ -19955,7 +20027,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="413" spans="1:23">
+    <row r="413" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>412</v>
       </c>
@@ -19990,7 +20062,7 @@
       </c>
       <c r="W413" s="3"/>
     </row>
-    <row r="414" spans="1:23">
+    <row r="414" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>413</v>
       </c>
@@ -20029,7 +20101,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="415" spans="1:23">
+    <row r="415" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>414</v>
       </c>
@@ -20072,7 +20144,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="416" spans="1:23">
+    <row r="416" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>415</v>
       </c>
@@ -20111,7 +20183,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="417" spans="1:23">
+    <row r="417" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>416</v>
       </c>
@@ -20154,7 +20226,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="418" spans="1:23">
+    <row r="418" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>417</v>
       </c>
@@ -20193,7 +20265,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="419" spans="1:23">
+    <row r="419" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>418</v>
       </c>
@@ -20230,7 +20302,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="420" spans="1:23">
+    <row r="420" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>419</v>
       </c>
@@ -20273,7 +20345,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="421" spans="1:23">
+    <row r="421" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>420</v>
       </c>
@@ -20313,7 +20385,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="422" spans="1:23">
+    <row r="422" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>421</v>
       </c>
@@ -20350,7 +20422,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="423" spans="1:23">
+    <row r="423" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>422</v>
       </c>
@@ -20393,7 +20465,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="424" spans="1:23">
+    <row r="424" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>423</v>
       </c>
@@ -20436,7 +20508,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="425" spans="1:23">
+    <row r="425" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>424</v>
       </c>
@@ -20479,7 +20551,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="426" spans="1:23">
+    <row r="426" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>425</v>
       </c>
@@ -20520,7 +20592,7 @@
       </c>
       <c r="W426" s="3"/>
     </row>
-    <row r="427" spans="1:23">
+    <row r="427" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>426</v>
       </c>
@@ -20563,7 +20635,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="428" spans="1:23">
+    <row r="428" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>427</v>
       </c>
@@ -20606,7 +20678,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="429" spans="1:23">
+    <row r="429" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>428</v>
       </c>
@@ -20649,7 +20721,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="430" spans="1:23">
+    <row r="430" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>429</v>
       </c>
@@ -20686,7 +20758,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="431" spans="1:23">
+    <row r="431" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>430</v>
       </c>
@@ -20725,7 +20797,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="432" spans="1:23">
+    <row r="432" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>431</v>
       </c>
@@ -20764,7 +20836,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="433" spans="1:23">
+    <row r="433" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>432</v>
       </c>
@@ -20802,7 +20874,7 @@
       </c>
       <c r="W433" s="3"/>
     </row>
-    <row r="434" spans="1:23">
+    <row r="434" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>433</v>
       </c>
@@ -20840,7 +20912,7 @@
       </c>
       <c r="W434" s="3"/>
     </row>
-    <row r="435" spans="1:23">
+    <row r="435" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>434</v>
       </c>
@@ -20878,7 +20950,7 @@
       </c>
       <c r="W435" s="3"/>
     </row>
-    <row r="436" spans="1:23">
+    <row r="436" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>435</v>
       </c>
@@ -20916,7 +20988,7 @@
       </c>
       <c r="W436" s="3"/>
     </row>
-    <row r="437" spans="1:23">
+    <row r="437" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>436</v>
       </c>
@@ -20954,7 +21026,7 @@
       </c>
       <c r="W437" s="3"/>
     </row>
-    <row r="438" spans="1:23">
+    <row r="438" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>437</v>
       </c>
@@ -20989,7 +21061,7 @@
       </c>
       <c r="W438" s="3"/>
     </row>
-    <row r="439" spans="1:23">
+    <row r="439" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>438</v>
       </c>
@@ -21026,7 +21098,7 @@
       </c>
       <c r="W439" s="3"/>
     </row>
-    <row r="440" spans="1:23">
+    <row r="440" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>439</v>
       </c>
@@ -21063,7 +21135,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="441" spans="1:23">
+    <row r="441" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>440</v>
       </c>
@@ -21100,7 +21172,7 @@
       </c>
       <c r="W441" s="3"/>
     </row>
-    <row r="442" spans="1:23">
+    <row r="442" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>441</v>
       </c>
@@ -21137,7 +21209,7 @@
       </c>
       <c r="W442" s="3"/>
     </row>
-    <row r="443" spans="1:23">
+    <row r="443" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>442</v>
       </c>
@@ -21178,7 +21250,7 @@
       </c>
       <c r="W443" s="3"/>
     </row>
-    <row r="444" spans="1:23">
+    <row r="444" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>443</v>
       </c>
@@ -21217,7 +21289,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="445" spans="1:23">
+    <row r="445" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>444</v>
       </c>
@@ -21258,7 +21330,7 @@
       </c>
       <c r="W445" s="3"/>
     </row>
-    <row r="446" spans="1:23">
+    <row r="446" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>445</v>
       </c>
@@ -21298,7 +21370,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="447" spans="1:23">
+    <row r="447" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>446</v>
       </c>
@@ -21338,7 +21410,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="448" spans="1:23">
+    <row r="448" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>447</v>
       </c>
@@ -21375,7 +21447,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="449" spans="1:23">
+    <row r="449" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>448</v>
       </c>
@@ -21414,7 +21486,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="450" spans="1:23">
+    <row r="450" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>449</v>
       </c>
@@ -21453,7 +21525,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="451" spans="1:23">
+    <row r="451" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>450</v>
       </c>
@@ -21492,7 +21564,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="452" spans="1:23">
+    <row r="452" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>451</v>
       </c>
@@ -21532,7 +21604,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="453" spans="1:23">
+    <row r="453" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>452</v>
       </c>
@@ -21569,7 +21641,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="454" spans="1:23">
+    <row r="454" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>453</v>
       </c>
@@ -21604,7 +21676,7 @@
       </c>
       <c r="W454" s="3"/>
     </row>
-    <row r="455" spans="1:23">
+    <row r="455" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>454</v>
       </c>
@@ -21643,7 +21715,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="456" spans="1:23">
+    <row r="456" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>455</v>
       </c>
@@ -21682,7 +21754,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="457" spans="1:23">
+    <row r="457" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>456</v>
       </c>
@@ -21721,7 +21793,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="458" spans="1:23">
+    <row r="458" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>457</v>
       </c>
@@ -21760,7 +21832,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="459" spans="1:23">
+    <row r="459" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>458</v>
       </c>
@@ -21799,7 +21871,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="460" spans="1:23">
+    <row r="460" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>459</v>
       </c>
@@ -21838,7 +21910,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="461" spans="1:23">
+    <row r="461" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>460</v>
       </c>
@@ -21877,7 +21949,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="462" spans="1:23">
+    <row r="462" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>461</v>
       </c>
@@ -21916,7 +21988,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="463" spans="1:23">
+    <row r="463" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>462</v>
       </c>
@@ -21955,7 +22027,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="464" spans="1:23">
+    <row r="464" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>463</v>
       </c>
@@ -21994,7 +22066,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="465" spans="1:23">
+    <row r="465" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>464</v>
       </c>
@@ -22033,7 +22105,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="466" spans="1:23">
+    <row r="466" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>465</v>
       </c>
@@ -22072,7 +22144,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="467" spans="1:23">
+    <row r="467" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>466</v>
       </c>
@@ -22111,7 +22183,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="468" spans="1:23">
+    <row r="468" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>467</v>
       </c>
@@ -22150,7 +22222,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="469" spans="1:23">
+    <row r="469" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>468</v>
       </c>
@@ -22189,7 +22261,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="470" spans="1:23">
+    <row r="470" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>469</v>
       </c>
@@ -22228,7 +22300,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="471" spans="1:23">
+    <row r="471" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>470</v>
       </c>
@@ -22265,7 +22337,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="472" spans="1:23">
+    <row r="472" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>471</v>
       </c>
@@ -22305,7 +22377,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="473" spans="1:23">
+    <row r="473" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>472</v>
       </c>
@@ -22342,7 +22414,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="474" spans="1:23">
+    <row r="474" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>473</v>
       </c>
@@ -22381,7 +22453,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="475" spans="1:23">
+    <row r="475" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>474</v>
       </c>
@@ -22420,7 +22492,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="476" spans="1:23">
+    <row r="476" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>475</v>
       </c>
@@ -22457,7 +22529,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="477" spans="1:23">
+    <row r="477" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>476</v>
       </c>
@@ -22494,7 +22566,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="478" spans="1:23">
+    <row r="478" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>477</v>
       </c>
@@ -22537,7 +22609,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="479" spans="1:23">
+    <row r="479" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>478</v>
       </c>
@@ -22576,7 +22648,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="480" spans="1:23">
+    <row r="480" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>479</v>
       </c>
@@ -22615,7 +22687,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="481" spans="1:23">
+    <row r="481" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>480</v>
       </c>
@@ -22652,7 +22724,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="482" spans="1:23">
+    <row r="482" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>481</v>
       </c>
@@ -22689,7 +22761,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="483" spans="1:23">
+    <row r="483" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>482</v>
       </c>
@@ -22726,7 +22798,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="484" spans="1:23">
+    <row r="484" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>483</v>
       </c>
@@ -22765,7 +22837,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="485" spans="1:23">
+    <row r="485" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>484</v>
       </c>
@@ -22804,7 +22876,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="486" spans="1:23">
+    <row r="486" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>485</v>
       </c>
@@ -22841,7 +22913,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="487" spans="1:23">
+    <row r="487" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>486</v>
       </c>
@@ -22878,7 +22950,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="488" spans="1:23">
+    <row r="488" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>487</v>
       </c>
@@ -22915,7 +22987,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="489" spans="1:23">
+    <row r="489" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>488</v>
       </c>
@@ -22953,7 +23025,7 @@
       </c>
       <c r="W489" s="3"/>
     </row>
-    <row r="490" spans="1:23">
+    <row r="490" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>489</v>
       </c>
@@ -22992,7 +23064,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="491" spans="1:23">
+    <row r="491" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>490</v>
       </c>
@@ -23031,7 +23103,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="492" spans="1:23">
+    <row r="492" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>491</v>
       </c>
@@ -23068,7 +23140,7 @@
       </c>
       <c r="W492" s="3"/>
     </row>
-    <row r="493" spans="1:23">
+    <row r="493" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>492</v>
       </c>
@@ -23105,7 +23177,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="494" spans="1:23">
+    <row r="494" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>493</v>
       </c>
@@ -23143,7 +23215,7 @@
       </c>
       <c r="W494" s="3"/>
     </row>
-    <row r="495" spans="1:23">
+    <row r="495" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>494</v>
       </c>
@@ -23180,7 +23252,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="496" spans="1:23">
+    <row r="496" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>495</v>
       </c>
@@ -23217,7 +23289,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="497" spans="1:23">
+    <row r="497" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>496</v>
       </c>
@@ -23260,7 +23332,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="498" spans="1:23">
+    <row r="498" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>497</v>
       </c>
@@ -23297,7 +23369,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="499" spans="1:23">
+    <row r="499" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>498</v>
       </c>
@@ -23336,7 +23408,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="500" spans="1:23">
+    <row r="500" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>499</v>
       </c>
@@ -23379,7 +23451,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="501" spans="1:23">
+    <row r="501" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>500</v>
       </c>
@@ -23422,7 +23494,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="502" spans="1:23">
+    <row r="502" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>501</v>
       </c>
@@ -23459,7 +23531,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="503" spans="1:23">
+    <row r="503" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>502</v>
       </c>
@@ -23498,7 +23570,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="504" spans="1:23">
+    <row r="504" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>503</v>
       </c>
@@ -23535,7 +23607,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="505" spans="1:23">
+    <row r="505" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>504</v>
       </c>
@@ -23578,7 +23650,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="506" spans="1:23">
+    <row r="506" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>505</v>
       </c>
@@ -23617,7 +23689,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="507" spans="1:23">
+    <row r="507" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>506</v>
       </c>
@@ -23656,7 +23728,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="508" spans="1:23">
+    <row r="508" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>507</v>
       </c>
@@ -23695,7 +23767,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="509" spans="1:23">
+    <row r="509" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>508</v>
       </c>
@@ -23738,7 +23810,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="510" spans="1:23">
+    <row r="510" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>509</v>
       </c>
@@ -23775,7 +23847,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="511" spans="1:23">
+    <row r="511" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>510</v>
       </c>
@@ -23814,7 +23886,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="512" spans="1:23">
+    <row r="512" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>511</v>
       </c>
@@ -23853,7 +23925,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="513" spans="1:23">
+    <row r="513" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>512</v>
       </c>
@@ -23892,7 +23964,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="514" spans="1:23">
+    <row r="514" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>513</v>
       </c>
@@ -23931,7 +24003,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="515" spans="1:23">
+    <row r="515" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>514</v>
       </c>
@@ -23970,7 +24042,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="516" spans="1:23">
+    <row r="516" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>515</v>
       </c>
@@ -24013,7 +24085,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="517" spans="1:23">
+    <row r="517" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>516</v>
       </c>
@@ -24052,7 +24124,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="518" spans="1:23">
+    <row r="518" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A518">
         <v>517</v>
       </c>
@@ -24091,7 +24163,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="519" spans="1:23">
+    <row r="519" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A519">
         <v>518</v>
       </c>
@@ -24128,7 +24200,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="520" spans="1:23">
+    <row r="520" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A520">
         <v>519</v>
       </c>
@@ -24168,7 +24240,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="521" spans="1:23">
+    <row r="521" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A521">
         <v>520</v>
       </c>
@@ -24205,7 +24277,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="522" spans="1:23">
+    <row r="522" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A522">
         <v>521</v>
       </c>
@@ -24248,7 +24320,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="523" spans="1:23">
+    <row r="523" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A523">
         <v>522</v>
       </c>
@@ -24287,7 +24359,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="524" spans="1:23">
+    <row r="524" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A524">
         <v>523</v>
       </c>
@@ -24326,7 +24398,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="525" spans="1:23">
+    <row r="525" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A525">
         <v>524</v>
       </c>
@@ -24363,7 +24435,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="526" spans="1:23">
+    <row r="526" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A526">
         <v>525</v>
       </c>
@@ -24400,7 +24472,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="527" spans="1:23">
+    <row r="527" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A527">
         <v>526</v>
       </c>
@@ -24443,7 +24515,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="528" spans="1:23">
+    <row r="528" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A528">
         <v>527</v>
       </c>
@@ -24486,7 +24558,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="529" spans="1:23">
+    <row r="529" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A529">
         <v>528</v>
       </c>
@@ -24529,7 +24601,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="530" spans="1:23">
+    <row r="530" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A530">
         <v>529</v>
       </c>
@@ -24570,7 +24642,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="531" spans="1:23">
+    <row r="531" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A531">
         <v>530</v>
       </c>
@@ -24609,7 +24681,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="532" spans="1:23">
+    <row r="532" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A532">
         <v>531</v>
       </c>
@@ -24648,7 +24720,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="533" spans="1:23">
+    <row r="533" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A533">
         <v>532</v>
       </c>
@@ -24683,7 +24755,7 @@
       </c>
       <c r="W533" s="3"/>
     </row>
-    <row r="534" spans="1:23">
+    <row r="534" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A534">
         <v>533</v>
       </c>
@@ -24724,7 +24796,7 @@
       </c>
       <c r="W534" s="3"/>
     </row>
-    <row r="535" spans="1:23">
+    <row r="535" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A535">
         <v>534</v>
       </c>
@@ -24762,7 +24834,7 @@
       </c>
       <c r="W535" s="3"/>
     </row>
-    <row r="536" spans="1:23">
+    <row r="536" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A536">
         <v>535</v>
       </c>
@@ -24800,7 +24872,7 @@
       </c>
       <c r="W536" s="3"/>
     </row>
-    <row r="537" spans="1:23">
+    <row r="537" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A537">
         <v>536</v>
       </c>
@@ -24838,7 +24910,7 @@
       </c>
       <c r="W537" s="3"/>
     </row>
-    <row r="538" spans="1:23">
+    <row r="538" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A538">
         <v>537</v>
       </c>
@@ -24876,7 +24948,7 @@
       </c>
       <c r="W538" s="3"/>
     </row>
-    <row r="539" spans="1:23">
+    <row r="539" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A539">
         <v>538</v>
       </c>
@@ -24914,7 +24986,7 @@
       </c>
       <c r="W539" s="3"/>
     </row>
-    <row r="540" spans="1:23">
+    <row r="540" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A540">
         <v>539</v>
       </c>
@@ -24952,7 +25024,7 @@
       </c>
       <c r="W540" s="3"/>
     </row>
-    <row r="541" spans="1:23">
+    <row r="541" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A541">
         <v>540</v>
       </c>
@@ -24993,7 +25065,7 @@
       </c>
       <c r="W541" s="3"/>
     </row>
-    <row r="542" spans="1:23">
+    <row r="542" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A542">
         <v>541</v>
       </c>
@@ -25034,7 +25106,7 @@
       </c>
       <c r="W542" s="3"/>
     </row>
-    <row r="543" spans="1:23">
+    <row r="543" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A543">
         <v>542</v>
       </c>
@@ -25071,7 +25143,7 @@
       </c>
       <c r="W543" s="3"/>
     </row>
-    <row r="544" spans="1:23">
+    <row r="544" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A544">
         <v>543</v>
       </c>
@@ -25110,7 +25182,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="545" spans="1:23">
+    <row r="545" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A545">
         <v>544</v>
       </c>
@@ -25147,7 +25219,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="546" spans="1:23">
+    <row r="546" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A546">
         <v>545</v>
       </c>
@@ -25184,7 +25256,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="547" spans="1:23">
+    <row r="547" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A547">
         <v>546</v>
       </c>
@@ -25224,7 +25296,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="548" spans="1:23">
+    <row r="548" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A548">
         <v>547</v>
       </c>
@@ -25261,7 +25333,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="549" spans="1:23">
+    <row r="549" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A549">
         <v>548</v>
       </c>
@@ -25298,7 +25370,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="550" spans="1:23">
+    <row r="550" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A550">
         <v>549</v>
       </c>
@@ -25335,7 +25407,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="551" spans="1:23">
+    <row r="551" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A551">
         <v>550</v>
       </c>
@@ -25372,7 +25444,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="552" spans="1:23">
+    <row r="552" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A552">
         <v>551</v>
       </c>
@@ -25409,7 +25481,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="553" spans="1:23">
+    <row r="553" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A553">
         <v>552</v>
       </c>
@@ -25446,7 +25518,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="554" spans="1:23">
+    <row r="554" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A554">
         <v>553</v>
       </c>
@@ -25483,7 +25555,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="555" spans="1:23">
+    <row r="555" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A555">
         <v>554</v>
       </c>
@@ -25520,7 +25592,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="556" spans="1:23">
+    <row r="556" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A556">
         <v>555</v>
       </c>
@@ -25557,7 +25629,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="557" spans="1:23">
+    <row r="557" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A557">
         <v>556</v>
       </c>
@@ -25594,7 +25666,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="558" spans="1:23">
+    <row r="558" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A558">
         <v>557</v>
       </c>
@@ -25631,7 +25703,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="559" spans="1:23">
+    <row r="559" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A559">
         <v>558</v>
       </c>
@@ -25668,7 +25740,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="560" spans="1:23">
+    <row r="560" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A560">
         <v>559</v>
       </c>
@@ -25707,7 +25779,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="561" spans="1:23">
+    <row r="561" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A561">
         <v>560</v>
       </c>
@@ -25744,7 +25816,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="562" spans="1:23">
+    <row r="562" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A562">
         <v>561</v>
       </c>
@@ -25779,7 +25851,7 @@
       </c>
       <c r="W562" s="3"/>
     </row>
-    <row r="563" spans="1:23">
+    <row r="563" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A563">
         <v>562</v>
       </c>
@@ -25814,7 +25886,7 @@
       </c>
       <c r="W563" s="3"/>
     </row>
-    <row r="564" spans="1:23">
+    <row r="564" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A564">
         <v>563</v>
       </c>
@@ -25849,7 +25921,7 @@
       </c>
       <c r="W564" s="3"/>
     </row>
-    <row r="565" spans="1:23">
+    <row r="565" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A565">
         <v>564</v>
       </c>
@@ -25884,7 +25956,7 @@
       </c>
       <c r="W565" s="3"/>
     </row>
-    <row r="566" spans="1:23">
+    <row r="566" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A566">
         <v>565</v>
       </c>
@@ -25919,7 +25991,7 @@
       </c>
       <c r="W566" s="3"/>
     </row>
-    <row r="567" spans="1:23">
+    <row r="567" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A567">
         <v>566</v>
       </c>
@@ -25958,7 +26030,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="568" spans="1:23">
+    <row r="568" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A568">
         <v>567</v>
       </c>
@@ -25997,7 +26069,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="569" spans="1:23">
+    <row r="569" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A569">
         <v>568</v>
       </c>
@@ -26036,7 +26108,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="570" spans="1:23">
+    <row r="570" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A570">
         <v>569</v>
       </c>
@@ -26071,7 +26143,7 @@
       </c>
       <c r="W570" s="3"/>
     </row>
-    <row r="571" spans="1:23">
+    <row r="571" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A571">
         <v>570</v>
       </c>
@@ -26110,7 +26182,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="572" spans="1:23">
+    <row r="572" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A572">
         <v>571</v>
       </c>
@@ -26151,7 +26223,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="573" spans="1:23">
+    <row r="573" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A573">
         <v>572</v>
       </c>
@@ -26190,7 +26262,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="574" spans="1:23">
+    <row r="574" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A574">
         <v>573</v>
       </c>
@@ -26227,7 +26299,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="575" spans="1:23">
+    <row r="575" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A575">
         <v>574</v>
       </c>
@@ -26266,7 +26338,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="576" spans="1:23">
+    <row r="576" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A576">
         <v>575</v>
       </c>
@@ -26305,7 +26377,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="577" spans="1:23">
+    <row r="577" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A577">
         <v>576</v>
       </c>
@@ -26342,7 +26414,7 @@
       </c>
       <c r="W577" s="3"/>
     </row>
-    <row r="578" spans="1:23">
+    <row r="578" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A578">
         <v>577</v>
       </c>
@@ -26379,7 +26451,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="579" spans="1:23">
+    <row r="579" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A579">
         <v>578</v>
       </c>
@@ -26418,7 +26490,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="580" spans="1:23">
+    <row r="580" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A580">
         <v>579</v>
       </c>
@@ -26455,7 +26527,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="581" spans="1:23">
+    <row r="581" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A581">
         <v>580</v>
       </c>
@@ -26490,7 +26562,7 @@
       </c>
       <c r="W581" s="3"/>
     </row>
-    <row r="582" spans="1:23">
+    <row r="582" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A582">
         <v>581</v>
       </c>
@@ -26529,7 +26601,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="583" spans="1:23">
+    <row r="583" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A583">
         <v>582</v>
       </c>
@@ -26567,7 +26639,7 @@
       </c>
       <c r="W583" s="3"/>
     </row>
-    <row r="584" spans="1:23">
+    <row r="584" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A584">
         <v>583</v>
       </c>
@@ -26605,7 +26677,7 @@
       </c>
       <c r="W584" s="3"/>
     </row>
-    <row r="585" spans="1:23">
+    <row r="585" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A585">
         <v>584</v>
       </c>
@@ -26640,7 +26712,7 @@
       </c>
       <c r="W585" s="3"/>
     </row>
-    <row r="586" spans="1:23">
+    <row r="586" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A586">
         <v>585</v>
       </c>
@@ -26675,7 +26747,7 @@
       </c>
       <c r="W586" s="3"/>
     </row>
-    <row r="587" spans="1:23">
+    <row r="587" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A587">
         <v>586</v>
       </c>
@@ -26710,7 +26782,7 @@
       </c>
       <c r="W587" s="3"/>
     </row>
-    <row r="588" spans="1:23">
+    <row r="588" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A588">
         <v>587</v>
       </c>
@@ -26745,7 +26817,7 @@
       </c>
       <c r="W588" s="3"/>
     </row>
-    <row r="589" spans="1:23">
+    <row r="589" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A589">
         <v>588</v>
       </c>
@@ -26780,7 +26852,7 @@
       </c>
       <c r="W589" s="3"/>
     </row>
-    <row r="590" spans="1:23">
+    <row r="590" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A590">
         <v>589</v>
       </c>
@@ -26815,7 +26887,7 @@
       </c>
       <c r="W590" s="3"/>
     </row>
-    <row r="591" spans="1:23">
+    <row r="591" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A591">
         <v>590</v>
       </c>
@@ -26850,7 +26922,7 @@
       </c>
       <c r="W591" s="3"/>
     </row>
-    <row r="592" spans="1:23">
+    <row r="592" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A592">
         <v>591</v>
       </c>
@@ -26885,7 +26957,7 @@
       </c>
       <c r="W592" s="3"/>
     </row>
-    <row r="593" spans="1:23">
+    <row r="593" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A593">
         <v>592</v>
       </c>
@@ -26922,7 +26994,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="594" spans="1:23">
+    <row r="594" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A594">
         <v>593</v>
       </c>
@@ -26959,7 +27031,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="595" spans="1:23">
+    <row r="595" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A595">
         <v>594</v>
       </c>
@@ -27002,7 +27074,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="596" spans="1:23">
+    <row r="596" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A596">
         <v>595</v>
       </c>
@@ -27045,7 +27117,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="597" spans="1:23">
+    <row r="597" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A597">
         <v>596</v>
       </c>
@@ -27088,7 +27160,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="598" spans="1:23">
+    <row r="598" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A598">
         <v>597</v>
       </c>
@@ -27131,7 +27203,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="599" spans="1:23">
+    <row r="599" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A599">
         <v>598</v>
       </c>
@@ -27174,7 +27246,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="600" spans="1:23">
+    <row r="600" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A600">
         <v>599</v>
       </c>
@@ -27217,7 +27289,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="601" spans="1:23">
+    <row r="601" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A601">
         <v>600</v>
       </c>
@@ -27257,7 +27329,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="602" spans="1:23">
+    <row r="602" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A602">
         <v>601</v>
       </c>
@@ -27300,7 +27372,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="603" spans="1:23">
+    <row r="603" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A603">
         <v>602</v>
       </c>
@@ -27343,7 +27415,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="604" spans="1:23">
+    <row r="604" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A604">
         <v>605</v>
       </c>
@@ -27381,7 +27453,7 @@
       </c>
       <c r="W604" s="3"/>
     </row>
-    <row r="605" spans="1:23">
+    <row r="605" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A605">
         <v>607</v>
       </c>
@@ -27422,7 +27494,7 @@
       </c>
       <c r="W605" s="3"/>
     </row>
-    <row r="606" spans="1:23">
+    <row r="606" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A606">
         <v>608</v>
       </c>
@@ -27463,7 +27535,7 @@
       </c>
       <c r="W606" s="3"/>
     </row>
-    <row r="607" spans="1:23">
+    <row r="607" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A607">
         <v>611</v>
       </c>
@@ -27501,7 +27573,7 @@
       </c>
       <c r="W607" s="3"/>
     </row>
-    <row r="608" spans="1:23">
+    <row r="608" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A608">
         <v>612</v>
       </c>
@@ -27539,7 +27611,7 @@
       </c>
       <c r="W608" s="3"/>
     </row>
-    <row r="609" spans="1:23">
+    <row r="609" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A609">
         <v>613</v>
       </c>
@@ -27577,7 +27649,7 @@
       </c>
       <c r="W609" s="3"/>
     </row>
-    <row r="610" spans="1:23">
+    <row r="610" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A610">
         <v>614</v>
       </c>
@@ -27615,7 +27687,7 @@
       </c>
       <c r="W610" s="3"/>
     </row>
-    <row r="611" spans="1:23">
+    <row r="611" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A611">
         <v>615</v>
       </c>
@@ -27653,7 +27725,7 @@
       </c>
       <c r="W611" s="3"/>
     </row>
-    <row r="612" spans="1:23">
+    <row r="612" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A612">
         <v>616</v>
       </c>
@@ -27691,7 +27763,7 @@
       </c>
       <c r="W612" s="3"/>
     </row>
-    <row r="613" spans="1:23">
+    <row r="613" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A613">
         <v>617</v>
       </c>
@@ -27732,7 +27804,7 @@
       </c>
       <c r="W613" s="3"/>
     </row>
-    <row r="614" spans="1:23">
+    <row r="614" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A614">
         <v>618</v>
       </c>
@@ -27773,7 +27845,7 @@
       </c>
       <c r="W614" s="3"/>
     </row>
-    <row r="615" spans="1:23">
+    <row r="615" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A615">
         <v>619</v>
       </c>
@@ -27814,7 +27886,7 @@
       </c>
       <c r="W615" s="3"/>
     </row>
-    <row r="616" spans="1:23">
+    <row r="616" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A616">
         <v>620</v>
       </c>
@@ -27855,7 +27927,7 @@
       </c>
       <c r="W616" s="3"/>
     </row>
-    <row r="617" spans="1:23">
+    <row r="617" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A617">
         <v>621</v>
       </c>
@@ -27896,7 +27968,7 @@
       </c>
       <c r="W617" s="3"/>
     </row>
-    <row r="618" spans="1:23">
+    <row r="618" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A618">
         <v>622</v>
       </c>
@@ -27937,7 +28009,7 @@
       </c>
       <c r="W618" s="3"/>
     </row>
-    <row r="619" spans="1:23">
+    <row r="619" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A619">
         <v>623</v>
       </c>
@@ -27978,7 +28050,7 @@
       </c>
       <c r="W619" s="3"/>
     </row>
-    <row r="620" spans="1:23">
+    <row r="620" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A620">
         <v>624</v>
       </c>
@@ -28019,7 +28091,7 @@
       </c>
       <c r="W620" s="3"/>
     </row>
-    <row r="621" spans="1:23">
+    <row r="621" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A621">
         <v>625</v>
       </c>
@@ -28060,7 +28132,7 @@
       </c>
       <c r="W621" s="3"/>
     </row>
-    <row r="622" spans="1:23">
+    <row r="622" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A622">
         <v>626</v>
       </c>
@@ -28101,7 +28173,7 @@
       </c>
       <c r="W622" s="3"/>
     </row>
-    <row r="623" spans="1:23">
+    <row r="623" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A623">
         <v>627</v>
       </c>
@@ -28142,7 +28214,7 @@
       </c>
       <c r="W623" s="3"/>
     </row>
-    <row r="624" spans="1:23">
+    <row r="624" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A624">
         <v>628</v>
       </c>
@@ -28180,7 +28252,7 @@
       </c>
       <c r="W624" s="3"/>
     </row>
-    <row r="625" spans="1:23">
+    <row r="625" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A625">
         <v>629</v>
       </c>
@@ -28218,7 +28290,7 @@
       </c>
       <c r="W625" s="3"/>
     </row>
-    <row r="626" spans="1:23">
+    <row r="626" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A626">
         <v>630</v>
       </c>
@@ -28259,7 +28331,7 @@
       </c>
       <c r="W626" s="3"/>
     </row>
-    <row r="627" spans="1:23">
+    <row r="627" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A627">
         <v>631</v>
       </c>
@@ -28297,7 +28369,7 @@
       </c>
       <c r="W627" s="3"/>
     </row>
-    <row r="628" spans="1:23">
+    <row r="628" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A628">
         <v>632</v>
       </c>
@@ -28335,7 +28407,7 @@
       </c>
       <c r="W628" s="3"/>
     </row>
-    <row r="629" spans="1:23">
+    <row r="629" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A629">
         <v>633</v>
       </c>
@@ -28376,7 +28448,7 @@
       </c>
       <c r="W629" s="3"/>
     </row>
-    <row r="630" spans="1:23">
+    <row r="630" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A630">
         <v>634</v>
       </c>
@@ -28417,7 +28489,7 @@
       </c>
       <c r="W630" s="3"/>
     </row>
-    <row r="631" spans="1:23">
+    <row r="631" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A631">
         <v>635</v>
       </c>
@@ -28456,7 +28528,7 @@
       </c>
       <c r="W631" s="3"/>
     </row>
-    <row r="632" spans="1:23">
+    <row r="632" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A632">
         <v>636</v>
       </c>
@@ -28493,7 +28565,7 @@
       </c>
       <c r="W632" s="3"/>
     </row>
-    <row r="633" spans="1:23">
+    <row r="633" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A633">
         <v>637</v>
       </c>
@@ -28534,7 +28606,7 @@
       </c>
       <c r="W633" s="3"/>
     </row>
-    <row r="634" spans="1:23">
+    <row r="634" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A634">
         <v>638</v>
       </c>
@@ -28575,7 +28647,7 @@
       </c>
       <c r="W634" s="3"/>
     </row>
-    <row r="635" spans="1:23">
+    <row r="635" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A635">
         <v>639</v>
       </c>
@@ -28616,7 +28688,7 @@
       </c>
       <c r="W635" s="3"/>
     </row>
-    <row r="636" spans="1:23">
+    <row r="636" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A636">
         <v>640</v>
       </c>
@@ -28656,7 +28728,7 @@
       </c>
       <c r="W636" s="3"/>
     </row>
-    <row r="637" spans="1:23">
+    <row r="637" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A637">
         <v>641</v>
       </c>
@@ -28697,7 +28769,7 @@
       </c>
       <c r="W637" s="3"/>
     </row>
-    <row r="638" spans="1:23">
+    <row r="638" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A638">
         <v>642</v>
       </c>
@@ -28738,7 +28810,7 @@
       </c>
       <c r="W638" s="3"/>
     </row>
-    <row r="639" spans="1:23">
+    <row r="639" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A639">
         <v>643</v>
       </c>
@@ -28779,7 +28851,7 @@
       </c>
       <c r="W639" s="3"/>
     </row>
-    <row r="640" spans="1:23">
+    <row r="640" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A640">
         <v>644</v>
       </c>
@@ -28816,7 +28888,7 @@
       </c>
       <c r="W640" s="3"/>
     </row>
-    <row r="641" spans="1:23">
+    <row r="641" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A641">
         <v>650</v>
       </c>
@@ -28857,7 +28929,7 @@
       </c>
       <c r="W641" s="3"/>
     </row>
-    <row r="642" spans="1:23">
+    <row r="642" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A642">
         <v>645</v>
       </c>
@@ -28898,7 +28970,7 @@
       </c>
       <c r="W642" s="3"/>
     </row>
-    <row r="643" spans="1:23">
+    <row r="643" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A643">
         <v>646</v>
       </c>
@@ -28934,7 +29006,7 @@
       </c>
       <c r="W643" s="3"/>
     </row>
-    <row r="644" spans="1:23">
+    <row r="644" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A644">
         <v>647</v>
       </c>
@@ -28975,7 +29047,7 @@
       </c>
       <c r="W644" s="3"/>
     </row>
-    <row r="645" spans="1:23">
+    <row r="645" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A645">
         <v>648</v>
       </c>
@@ -29013,7 +29085,7 @@
       </c>
       <c r="W645" s="3"/>
     </row>
-    <row r="646" spans="1:23">
+    <row r="646" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A646">
         <v>649</v>
       </c>
@@ -29054,7 +29126,7 @@
       </c>
       <c r="W646" s="3"/>
     </row>
-    <row r="647" spans="1:23">
+    <row r="647" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A647">
         <v>651</v>
       </c>
@@ -29095,7 +29167,7 @@
       </c>
       <c r="W647" s="3"/>
     </row>
-    <row r="648" spans="1:23">
+    <row r="648" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A648">
         <v>652</v>
       </c>
@@ -29136,7 +29208,7 @@
       </c>
       <c r="W648" s="3"/>
     </row>
-    <row r="649" spans="1:23">
+    <row r="649" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A649">
         <v>653</v>
       </c>
@@ -29177,7 +29249,7 @@
       </c>
       <c r="W649" s="3"/>
     </row>
-    <row r="650" spans="1:23">
+    <row r="650" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A650">
         <v>654</v>
       </c>
@@ -29218,7 +29290,7 @@
       </c>
       <c r="W650" s="3"/>
     </row>
-    <row r="651" spans="1:23">
+    <row r="651" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A651">
         <v>655</v>
       </c>
@@ -29259,7 +29331,7 @@
       </c>
       <c r="W651" s="3"/>
     </row>
-    <row r="652" spans="1:23">
+    <row r="652" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A652">
         <v>656</v>
       </c>
@@ -29300,7 +29372,7 @@
       </c>
       <c r="W652" s="3"/>
     </row>
-    <row r="653" spans="1:23">
+    <row r="653" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A653">
         <v>657</v>
       </c>
@@ -29341,7 +29413,7 @@
       </c>
       <c r="W653" s="3"/>
     </row>
-    <row r="654" spans="1:23">
+    <row r="654" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A654">
         <v>658</v>
       </c>
@@ -29382,7 +29454,7 @@
       </c>
       <c r="W654" s="3"/>
     </row>
-    <row r="655" spans="1:23">
+    <row r="655" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A655">
         <v>659</v>
       </c>
@@ -29419,7 +29491,7 @@
       </c>
       <c r="W655" s="3"/>
     </row>
-    <row r="656" spans="1:23">
+    <row r="656" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A656">
         <v>660</v>
       </c>
@@ -29460,7 +29532,7 @@
       </c>
       <c r="W656" s="3"/>
     </row>
-    <row r="657" spans="1:23">
+    <row r="657" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A657">
         <v>661</v>
       </c>
@@ -29500,7 +29572,7 @@
       </c>
       <c r="W657" s="3"/>
     </row>
-    <row r="658" spans="1:23">
+    <row r="658" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A658">
         <v>662</v>
       </c>
@@ -29541,7 +29613,7 @@
       </c>
       <c r="W658" s="3"/>
     </row>
-    <row r="659" spans="1:23">
+    <row r="659" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A659">
         <v>663</v>
       </c>
@@ -29582,7 +29654,7 @@
       </c>
       <c r="W659" s="3"/>
     </row>
-    <row r="660" spans="1:23">
+    <row r="660" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A660">
         <v>664</v>
       </c>
@@ -29619,7 +29691,7 @@
       </c>
       <c r="W660" s="3"/>
     </row>
-    <row r="661" spans="1:23">
+    <row r="661" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A661">
         <v>665</v>
       </c>
@@ -29660,7 +29732,7 @@
       </c>
       <c r="W661" s="3"/>
     </row>
-    <row r="662" spans="1:23">
+    <row r="662" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A662">
         <v>666</v>
       </c>
@@ -29701,7 +29773,7 @@
       </c>
       <c r="W662" s="3"/>
     </row>
-    <row r="663" spans="1:23">
+    <row r="663" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A663">
         <v>668</v>
       </c>
@@ -29739,7 +29811,7 @@
       </c>
       <c r="W663" s="3"/>
     </row>
-    <row r="664" spans="1:23">
+    <row r="664" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A664">
         <v>667</v>
       </c>
@@ -29780,7 +29852,7 @@
       </c>
       <c r="W664" s="3"/>
     </row>
-    <row r="665" spans="1:23">
+    <row r="665" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A665">
         <v>669</v>
       </c>
@@ -29821,7 +29893,7 @@
       </c>
       <c r="W665" s="3"/>
     </row>
-    <row r="666" spans="1:23">
+    <row r="666" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A666">
         <v>670</v>
       </c>
@@ -29861,7 +29933,7 @@
       </c>
       <c r="W666" s="3"/>
     </row>
-    <row r="667" spans="1:23">
+    <row r="667" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A667">
         <v>671</v>
       </c>
@@ -29902,7 +29974,7 @@
       </c>
       <c r="W667" s="3"/>
     </row>
-    <row r="668" spans="1:23">
+    <row r="668" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A668">
         <v>672</v>
       </c>
@@ -29943,7 +30015,7 @@
       </c>
       <c r="W668" s="3"/>
     </row>
-    <row r="669" spans="1:23">
+    <row r="669" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A669">
         <v>674</v>
       </c>
@@ -29984,7 +30056,7 @@
       </c>
       <c r="W669" s="3"/>
     </row>
-    <row r="670" spans="1:23">
+    <row r="670" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A670">
         <v>675</v>
       </c>
@@ -30025,7 +30097,7 @@
       </c>
       <c r="W670" s="3"/>
     </row>
-    <row r="671" spans="1:23">
+    <row r="671" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A671">
         <v>676</v>
       </c>
@@ -30065,7 +30137,7 @@
       </c>
       <c r="W671" s="3"/>
     </row>
-    <row r="672" spans="1:23">
+    <row r="672" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A672">
         <v>677</v>
       </c>
@@ -30105,7 +30177,7 @@
       </c>
       <c r="W672" s="3"/>
     </row>
-    <row r="673" spans="1:23">
+    <row r="673" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A673">
         <v>678</v>
       </c>
@@ -30145,7 +30217,7 @@
       </c>
       <c r="W673" s="3"/>
     </row>
-    <row r="674" spans="1:23">
+    <row r="674" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A674">
         <v>679</v>
       </c>
@@ -30186,7 +30258,7 @@
       </c>
       <c r="W674" s="3"/>
     </row>
-    <row r="675" spans="1:23">
+    <row r="675" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A675">
         <v>680</v>
       </c>
@@ -30227,7 +30299,7 @@
       </c>
       <c r="W675" s="3"/>
     </row>
-    <row r="676" spans="1:23">
+    <row r="676" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A676">
         <v>681</v>
       </c>
@@ -30268,7 +30340,7 @@
       </c>
       <c r="W676" s="3"/>
     </row>
-    <row r="677" spans="1:23">
+    <row r="677" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A677">
         <v>682</v>
       </c>
@@ -30309,7 +30381,7 @@
       </c>
       <c r="W677" s="3"/>
     </row>
-    <row r="678" spans="1:23">
+    <row r="678" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A678">
         <v>683</v>
       </c>
@@ -30350,7 +30422,7 @@
       </c>
       <c r="W678" s="3"/>
     </row>
-    <row r="679" spans="1:23">
+    <row r="679" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A679">
         <v>684</v>
       </c>
@@ -30391,7 +30463,7 @@
       </c>
       <c r="W679" s="3"/>
     </row>
-    <row r="680" spans="1:23">
+    <row r="680" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A680">
         <v>685</v>
       </c>
@@ -30432,7 +30504,7 @@
       </c>
       <c r="W680" s="3"/>
     </row>
-    <row r="681" spans="1:23">
+    <row r="681" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A681">
         <v>686</v>
       </c>
@@ -30473,7 +30545,7 @@
       </c>
       <c r="W681" s="3"/>
     </row>
-    <row r="682" spans="1:23">
+    <row r="682" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A682">
         <v>687</v>
       </c>
@@ -30514,7 +30586,7 @@
       </c>
       <c r="W682" s="3"/>
     </row>
-    <row r="683" spans="1:23">
+    <row r="683" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A683">
         <v>688</v>
       </c>
@@ -30555,7 +30627,7 @@
       </c>
       <c r="W683" s="3"/>
     </row>
-    <row r="684" spans="1:23">
+    <row r="684" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A684">
         <v>689</v>
       </c>
@@ -30593,7 +30665,7 @@
       </c>
       <c r="W684" s="3"/>
     </row>
-    <row r="685" spans="1:23">
+    <row r="685" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A685">
         <v>690</v>
       </c>
@@ -30634,7 +30706,7 @@
       </c>
       <c r="W685" s="3"/>
     </row>
-    <row r="686" spans="1:23">
+    <row r="686" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A686">
         <v>691</v>
       </c>
@@ -30675,7 +30747,7 @@
       </c>
       <c r="W686" s="3"/>
     </row>
-    <row r="687" spans="1:23">
+    <row r="687" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A687">
         <v>692</v>
       </c>
@@ -30716,7 +30788,7 @@
       </c>
       <c r="W687" s="3"/>
     </row>
-    <row r="688" spans="1:23">
+    <row r="688" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A688">
         <v>693</v>
       </c>
@@ -30757,7 +30829,7 @@
       </c>
       <c r="W688" s="3"/>
     </row>
-    <row r="689" spans="1:23">
+    <row r="689" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A689">
         <v>694</v>
       </c>
@@ -30798,7 +30870,7 @@
       </c>
       <c r="W689" s="3"/>
     </row>
-    <row r="690" spans="1:23">
+    <row r="690" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A690">
         <v>695</v>
       </c>
@@ -30839,7 +30911,7 @@
       </c>
       <c r="W690" s="3"/>
     </row>
-    <row r="691" spans="1:23">
+    <row r="691" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A691">
         <v>696</v>
       </c>
@@ -30880,7 +30952,7 @@
       </c>
       <c r="W691" s="3"/>
     </row>
-    <row r="692" spans="1:23">
+    <row r="692" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A692">
         <v>697</v>
       </c>
@@ -30917,7 +30989,7 @@
       </c>
       <c r="W692" s="3"/>
     </row>
-    <row r="693" spans="1:23">
+    <row r="693" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A693">
         <v>698</v>
       </c>
@@ -30957,7 +31029,7 @@
       </c>
       <c r="W693" s="3"/>
     </row>
-    <row r="694" spans="1:23">
+    <row r="694" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A694">
         <v>699</v>
       </c>
@@ -30998,7 +31070,7 @@
       </c>
       <c r="W694" s="3"/>
     </row>
-    <row r="695" spans="1:23">
+    <row r="695" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A695">
         <v>700</v>
       </c>
@@ -31035,7 +31107,7 @@
       </c>
       <c r="W695" s="3"/>
     </row>
-    <row r="696" spans="1:23">
+    <row r="696" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A696">
         <v>701</v>
       </c>
@@ -31076,7 +31148,7 @@
       </c>
       <c r="W696" s="3"/>
     </row>
-    <row r="697" spans="1:23">
+    <row r="697" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A697">
         <v>702</v>
       </c>
@@ -31117,7 +31189,7 @@
       </c>
       <c r="W697" s="3"/>
     </row>
-    <row r="698" spans="1:23">
+    <row r="698" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A698">
         <v>703</v>
       </c>
@@ -31158,7 +31230,7 @@
       </c>
       <c r="W698" s="3"/>
     </row>
-    <row r="699" spans="1:23">
+    <row r="699" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A699">
         <v>704</v>
       </c>
@@ -31199,7 +31271,7 @@
       </c>
       <c r="W699" s="3"/>
     </row>
-    <row r="700" spans="1:23">
+    <row r="700" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A700">
         <v>705</v>
       </c>
@@ -31240,7 +31312,7 @@
       </c>
       <c r="W700" s="3"/>
     </row>
-    <row r="701" spans="1:23">
+    <row r="701" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A701">
         <v>706</v>
       </c>
@@ -31281,7 +31353,7 @@
       </c>
       <c r="W701" s="3"/>
     </row>
-    <row r="702" spans="1:23">
+    <row r="702" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A702">
         <v>707</v>
       </c>
@@ -31322,7 +31394,7 @@
       </c>
       <c r="W702" s="3"/>
     </row>
-    <row r="703" spans="1:23">
+    <row r="703" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A703">
         <v>708</v>
       </c>
@@ -31363,7 +31435,7 @@
       </c>
       <c r="W703" s="3"/>
     </row>
-    <row r="704" spans="1:23">
+    <row r="704" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A704">
         <v>709</v>
       </c>
@@ -31404,7 +31476,7 @@
       </c>
       <c r="W704" s="3"/>
     </row>
-    <row r="705" spans="1:23">
+    <row r="705" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A705">
         <v>710</v>
       </c>
@@ -31445,7 +31517,7 @@
       </c>
       <c r="W705" s="3"/>
     </row>
-    <row r="706" spans="1:23">
+    <row r="706" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A706">
         <v>711</v>
       </c>
@@ -31486,7 +31558,7 @@
       </c>
       <c r="W706" s="3"/>
     </row>
-    <row r="707" spans="1:23">
+    <row r="707" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A707">
         <v>712</v>
       </c>
@@ -31527,7 +31599,7 @@
       </c>
       <c r="W707" s="3"/>
     </row>
-    <row r="708" spans="1:23">
+    <row r="708" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A708">
         <v>713</v>
       </c>
@@ -31565,7 +31637,7 @@
       </c>
       <c r="W708" s="3"/>
     </row>
-    <row r="709" spans="1:23">
+    <row r="709" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A709">
         <v>714</v>
       </c>
@@ -31603,7 +31675,7 @@
       </c>
       <c r="W709" s="3"/>
     </row>
-    <row r="710" spans="1:23">
+    <row r="710" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A710">
         <v>715</v>
       </c>
@@ -31641,7 +31713,7 @@
       </c>
       <c r="W710" s="3"/>
     </row>
-    <row r="711" spans="1:23">
+    <row r="711" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A711">
         <v>716</v>
       </c>
@@ -31689,7 +31761,7 @@
       </c>
       <c r="W711" s="3"/>
     </row>
-    <row r="712" spans="1:23">
+    <row r="712" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A712">
         <v>717</v>
       </c>
@@ -31730,7 +31802,7 @@
       </c>
       <c r="W712" s="3"/>
     </row>
-    <row r="713" spans="1:23">
+    <row r="713" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A713">
         <v>718</v>
       </c>
@@ -31771,7 +31843,7 @@
       </c>
       <c r="W713" s="3"/>
     </row>
-    <row r="714" spans="1:23">
+    <row r="714" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A714">
         <v>719</v>
       </c>
@@ -31812,7 +31884,7 @@
       </c>
       <c r="W714" s="3"/>
     </row>
-    <row r="715" spans="1:23">
+    <row r="715" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A715">
         <v>720</v>
       </c>
@@ -31853,7 +31925,7 @@
       </c>
       <c r="W715" s="3"/>
     </row>
-    <row r="716" spans="1:23">
+    <row r="716" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A716">
         <v>721</v>
       </c>
@@ -31894,7 +31966,7 @@
       </c>
       <c r="W716" s="3"/>
     </row>
-    <row r="717" spans="1:23">
+    <row r="717" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A717">
         <v>722</v>
       </c>
@@ -31935,7 +32007,7 @@
       </c>
       <c r="W717" s="3"/>
     </row>
-    <row r="718" spans="1:23">
+    <row r="718" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A718">
         <v>723</v>
       </c>
@@ -31985,7 +32057,7 @@
       </c>
       <c r="W718" s="3"/>
     </row>
-    <row r="719" spans="1:23">
+    <row r="719" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A719">
         <v>724</v>
       </c>
@@ -32023,7 +32095,7 @@
       </c>
       <c r="W719" s="3"/>
     </row>
-    <row r="720" spans="1:23">
+    <row r="720" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A720">
         <v>725</v>
       </c>
@@ -32061,7 +32133,7 @@
       </c>
       <c r="W720" s="3"/>
     </row>
-    <row r="721" spans="1:23">
+    <row r="721" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A721">
         <v>726</v>
       </c>
@@ -32099,7 +32171,7 @@
       </c>
       <c r="W721" s="3"/>
     </row>
-    <row r="722" spans="1:23">
+    <row r="722" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A722">
         <v>727</v>
       </c>
@@ -32140,7 +32212,7 @@
       </c>
       <c r="W722" s="3"/>
     </row>
-    <row r="723" spans="1:23">
+    <row r="723" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A723">
         <v>728</v>
       </c>
@@ -32181,7 +32253,7 @@
       </c>
       <c r="W723" s="3"/>
     </row>
-    <row r="724" spans="1:23">
+    <row r="724" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A724">
         <v>729</v>
       </c>
@@ -32222,7 +32294,7 @@
       </c>
       <c r="W724" s="3"/>
     </row>
-    <row r="725" spans="1:23">
+    <row r="725" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A725">
         <v>730</v>
       </c>
@@ -32263,7 +32335,7 @@
       </c>
       <c r="W725" s="3"/>
     </row>
-    <row r="726" spans="1:23">
+    <row r="726" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A726">
         <v>731</v>
       </c>
@@ -32304,7 +32376,7 @@
       </c>
       <c r="W726" s="3"/>
     </row>
-    <row r="727" spans="1:23">
+    <row r="727" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A727">
         <v>732</v>
       </c>
@@ -32345,7 +32417,7 @@
       </c>
       <c r="W727" s="3"/>
     </row>
-    <row r="728" spans="1:23">
+    <row r="728" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A728">
         <v>733</v>
       </c>
@@ -32386,7 +32458,7 @@
       </c>
       <c r="W728" s="3"/>
     </row>
-    <row r="729" spans="1:23">
+    <row r="729" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A729">
         <v>734</v>
       </c>
@@ -32427,7 +32499,7 @@
       </c>
       <c r="W729" s="3"/>
     </row>
-    <row r="730" spans="1:23">
+    <row r="730" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A730">
         <v>735</v>
       </c>
@@ -32477,7 +32549,7 @@
       </c>
       <c r="W730" s="3"/>
     </row>
-    <row r="731" spans="1:23">
+    <row r="731" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A731">
         <v>736</v>
       </c>
@@ -32518,7 +32590,7 @@
       </c>
       <c r="W731" s="3"/>
     </row>
-    <row r="732" spans="1:23">
+    <row r="732" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A732">
         <v>737</v>
       </c>
@@ -32558,7 +32630,7 @@
       </c>
       <c r="W732" s="3"/>
     </row>
-    <row r="733" spans="1:23">
+    <row r="733" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A733">
         <v>738</v>
       </c>
@@ -32599,7 +32671,7 @@
       </c>
       <c r="W733" s="3"/>
     </row>
-    <row r="734" spans="1:23">
+    <row r="734" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A734">
         <v>739</v>
       </c>
@@ -32636,7 +32708,7 @@
       </c>
       <c r="W734" s="3"/>
     </row>
-    <row r="735" spans="1:23">
+    <row r="735" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A735">
         <v>740</v>
       </c>
@@ -32674,7 +32746,7 @@
       </c>
       <c r="W735" s="3"/>
     </row>
-    <row r="736" spans="1:23">
+    <row r="736" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A736">
         <v>741</v>
       </c>
@@ -32715,7 +32787,7 @@
       </c>
       <c r="W736" s="3"/>
     </row>
-    <row r="737" spans="1:23">
+    <row r="737" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A737">
         <v>742</v>
       </c>
@@ -32756,7 +32828,7 @@
       </c>
       <c r="W737" s="3"/>
     </row>
-    <row r="738" spans="1:23">
+    <row r="738" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A738">
         <v>743</v>
       </c>
@@ -32806,7 +32878,7 @@
       </c>
       <c r="W738" s="3"/>
     </row>
-    <row r="739" spans="1:23">
+    <row r="739" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A739">
         <v>744</v>
       </c>
@@ -32843,7 +32915,7 @@
       </c>
       <c r="W739" s="3"/>
     </row>
-    <row r="740" spans="1:23">
+    <row r="740" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A740">
         <v>745</v>
       </c>
@@ -32893,7 +32965,7 @@
       </c>
       <c r="W740" s="3"/>
     </row>
-    <row r="741" spans="1:23">
+    <row r="741" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A741">
         <v>746</v>
       </c>
@@ -32943,7 +33015,7 @@
       </c>
       <c r="W741" s="3"/>
     </row>
-    <row r="742" spans="1:23">
+    <row r="742" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A742">
         <v>747</v>
       </c>
@@ -32984,7 +33056,7 @@
       </c>
       <c r="W742" s="3"/>
     </row>
-    <row r="743" spans="1:23">
+    <row r="743" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A743">
         <v>748</v>
       </c>
@@ -33025,7 +33097,7 @@
       </c>
       <c r="W743" s="3"/>
     </row>
-    <row r="744" spans="1:23">
+    <row r="744" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A744">
         <v>749</v>
       </c>
@@ -33065,7 +33137,7 @@
       </c>
       <c r="W744" s="3"/>
     </row>
-    <row r="745" spans="1:23">
+    <row r="745" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A745">
         <v>750</v>
       </c>
@@ -33106,7 +33178,7 @@
       </c>
       <c r="W745" s="3"/>
     </row>
-    <row r="746" spans="1:23">
+    <row r="746" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A746">
         <v>751</v>
       </c>
@@ -33147,7 +33219,7 @@
       </c>
       <c r="W746" s="3"/>
     </row>
-    <row r="747" spans="1:23">
+    <row r="747" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A747">
         <v>752</v>
       </c>
@@ -33187,7 +33259,7 @@
       </c>
       <c r="W747" s="3"/>
     </row>
-    <row r="748" spans="1:23">
+    <row r="748" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A748">
         <v>753</v>
       </c>
@@ -33228,7 +33300,7 @@
       </c>
       <c r="W748" s="3"/>
     </row>
-    <row r="749" spans="1:23">
+    <row r="749" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A749">
         <v>754</v>
       </c>
@@ -33278,7 +33350,7 @@
       </c>
       <c r="W749" s="3"/>
     </row>
-    <row r="750" spans="1:23">
+    <row r="750" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A750">
         <v>755</v>
       </c>
@@ -33318,7 +33390,7 @@
       </c>
       <c r="W750" s="3"/>
     </row>
-    <row r="751" spans="1:23">
+    <row r="751" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A751">
         <v>756</v>
       </c>
@@ -33359,7 +33431,7 @@
       </c>
       <c r="W751" s="3"/>
     </row>
-    <row r="752" spans="1:23">
+    <row r="752" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A752">
         <v>757</v>
       </c>
@@ -33409,7 +33481,7 @@
       </c>
       <c r="W752" s="3"/>
     </row>
-    <row r="753" spans="1:23">
+    <row r="753" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A753">
         <v>758</v>
       </c>
@@ -33449,7 +33521,7 @@
       </c>
       <c r="W753" s="3"/>
     </row>
-    <row r="754" spans="1:23">
+    <row r="754" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A754">
         <v>759</v>
       </c>
@@ -33490,7 +33562,7 @@
       </c>
       <c r="W754" s="3"/>
     </row>
-    <row r="755" spans="1:23">
+    <row r="755" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A755">
         <v>760</v>
       </c>
@@ -33531,7 +33603,7 @@
       </c>
       <c r="W755" s="3"/>
     </row>
-    <row r="756" spans="1:23">
+    <row r="756" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A756">
         <v>762</v>
       </c>
@@ -33581,7 +33653,7 @@
       </c>
       <c r="W756" s="3"/>
     </row>
-    <row r="757" spans="1:23">
+    <row r="757" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A757">
         <v>763</v>
       </c>
@@ -33631,7 +33703,7 @@
       </c>
       <c r="W757" s="3"/>
     </row>
-    <row r="758" spans="1:23">
+    <row r="758" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A758">
         <v>764</v>
       </c>
@@ -33681,7 +33753,7 @@
       </c>
       <c r="W758" s="3"/>
     </row>
-    <row r="759" spans="1:23">
+    <row r="759" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A759">
         <v>765</v>
       </c>
@@ -33722,7 +33794,7 @@
       </c>
       <c r="W759" s="3"/>
     </row>
-    <row r="760" spans="1:23">
+    <row r="760" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A760">
         <v>766</v>
       </c>
@@ -33763,7 +33835,7 @@
       </c>
       <c r="W760" s="3"/>
     </row>
-    <row r="761" spans="1:23">
+    <row r="761" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A761">
         <v>767</v>
       </c>
@@ -33804,7 +33876,7 @@
       </c>
       <c r="W761" s="3"/>
     </row>
-    <row r="762" spans="1:23">
+    <row r="762" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A762">
         <v>768</v>
       </c>
@@ -33854,7 +33926,7 @@
       </c>
       <c r="W762" s="3"/>
     </row>
-    <row r="763" spans="1:23">
+    <row r="763" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A763">
         <v>769</v>
       </c>
@@ -33895,7 +33967,7 @@
       </c>
       <c r="W763" s="3"/>
     </row>
-    <row r="764" spans="1:23">
+    <row r="764" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A764">
         <v>770</v>
       </c>
@@ -33936,7 +34008,7 @@
       </c>
       <c r="W764" s="3"/>
     </row>
-    <row r="765" spans="1:23">
+    <row r="765" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A765">
         <v>771</v>
       </c>
@@ -33986,7 +34058,7 @@
       </c>
       <c r="W765" s="3"/>
     </row>
-    <row r="766" spans="1:23">
+    <row r="766" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A766">
         <v>772</v>
       </c>
@@ -34036,7 +34108,7 @@
       </c>
       <c r="W766" s="3"/>
     </row>
-    <row r="767" spans="1:23">
+    <row r="767" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A767">
         <v>773</v>
       </c>
@@ -34075,7 +34147,7 @@
       </c>
       <c r="W767" s="3"/>
     </row>
-    <row r="768" spans="1:23">
+    <row r="768" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A768">
         <v>774</v>
       </c>
@@ -34116,7 +34188,7 @@
       </c>
       <c r="W768" s="3"/>
     </row>
-    <row r="769" spans="1:23">
+    <row r="769" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A769">
         <v>775</v>
       </c>
@@ -34157,7 +34229,7 @@
       </c>
       <c r="W769" s="3"/>
     </row>
-    <row r="770" spans="1:23">
+    <row r="770" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A770">
         <v>776</v>
       </c>
@@ -34197,7 +34269,7 @@
       </c>
       <c r="W770" s="3"/>
     </row>
-    <row r="771" spans="1:23">
+    <row r="771" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A771">
         <v>777</v>
       </c>
@@ -34247,7 +34319,7 @@
       </c>
       <c r="W771" s="3"/>
     </row>
-    <row r="772" spans="1:23">
+    <row r="772" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A772">
         <v>778</v>
       </c>
@@ -34288,7 +34360,7 @@
       </c>
       <c r="W772" s="3"/>
     </row>
-    <row r="773" spans="1:23">
+    <row r="773" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A773">
         <v>779</v>
       </c>
@@ -34326,8 +34398,8 @@
       </c>
       <c r="W773" s="3"/>
     </row>
-    <row r="774" spans="1:23">
-      <c r="A774" s="6">
+    <row r="774" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A774">
         <v>780</v>
       </c>
       <c r="B774" s="4">
@@ -34351,20 +34423,12 @@
       <c r="H774" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I774" s="6"/>
-      <c r="J774" s="6" t="s">
+      <c r="J774" t="s">
         <v>914</v>
       </c>
-      <c r="K774" s="6"/>
       <c r="L774" s="3"/>
       <c r="M774" s="3"/>
-      <c r="N774" s="6"/>
-      <c r="O774" s="6"/>
-      <c r="P774" s="6"/>
-      <c r="Q774" s="6"/>
-      <c r="R774" s="6"/>
-      <c r="S774" s="6"/>
-      <c r="T774" s="6">
+      <c r="T774">
         <v>10</v>
       </c>
       <c r="U774" s="3" t="s">
@@ -34375,8 +34439,8 @@
       </c>
       <c r="W774" s="3"/>
     </row>
-    <row r="775" spans="1:23">
-      <c r="A775" s="6">
+    <row r="775" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A775">
         <v>781</v>
       </c>
       <c r="B775" s="4">
@@ -34400,20 +34464,12 @@
       <c r="H775" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I775" s="6"/>
-      <c r="J775" s="6" t="s">
+      <c r="J775" t="s">
         <v>894</v>
       </c>
-      <c r="K775" s="6"/>
       <c r="L775" s="3"/>
       <c r="M775" s="3"/>
-      <c r="N775" s="6"/>
-      <c r="O775" s="6"/>
-      <c r="P775" s="6"/>
-      <c r="Q775" s="6"/>
-      <c r="R775" s="6"/>
-      <c r="S775" s="6"/>
-      <c r="T775" s="6">
+      <c r="T775">
         <v>100</v>
       </c>
       <c r="U775" s="3" t="s">
@@ -34424,8 +34480,8 @@
       </c>
       <c r="W775" s="3"/>
     </row>
-    <row r="776" spans="1:23">
-      <c r="A776" s="6">
+    <row r="776" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A776">
         <v>782</v>
       </c>
       <c r="B776" s="4">
@@ -34449,20 +34505,12 @@
       <c r="H776" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I776" s="6"/>
-      <c r="J776" s="6" t="s">
+      <c r="J776" t="s">
         <v>894</v>
       </c>
-      <c r="K776" s="6"/>
       <c r="L776" s="3"/>
       <c r="M776" s="3"/>
-      <c r="N776" s="6"/>
-      <c r="O776" s="6"/>
-      <c r="P776" s="6"/>
-      <c r="Q776" s="6"/>
-      <c r="R776" s="6"/>
-      <c r="S776" s="6"/>
-      <c r="T776" s="6">
+      <c r="T776">
         <v>15</v>
       </c>
       <c r="U776" s="3" t="s">
@@ -34473,8 +34521,8 @@
       </c>
       <c r="W776" s="3"/>
     </row>
-    <row r="777" spans="1:23">
-      <c r="A777" s="6">
+    <row r="777" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A777">
         <v>783</v>
       </c>
       <c r="B777" s="4">
@@ -34498,20 +34546,12 @@
       <c r="H777" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="I777" s="6"/>
-      <c r="J777" s="6"/>
-      <c r="K777" s="6" t="s">
+      <c r="K777" t="s">
         <v>1132</v>
       </c>
       <c r="L777" s="3"/>
       <c r="M777" s="3"/>
-      <c r="N777" s="6"/>
-      <c r="O777" s="6"/>
-      <c r="P777" s="6"/>
-      <c r="Q777" s="6"/>
-      <c r="R777" s="6"/>
-      <c r="S777" s="6"/>
-      <c r="T777" s="6">
+      <c r="T777">
         <v>210</v>
       </c>
       <c r="U777" s="3" t="s">
@@ -34522,8 +34562,8 @@
       </c>
       <c r="W777" s="3"/>
     </row>
-    <row r="778" spans="1:23">
-      <c r="A778" s="6">
+    <row r="778" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A778">
         <v>784</v>
       </c>
       <c r="B778" s="4">
@@ -34547,20 +34587,12 @@
       <c r="H778" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="I778" s="6"/>
-      <c r="J778" s="6"/>
-      <c r="K778" s="6" t="s">
+      <c r="K778" t="s">
         <v>1008</v>
       </c>
       <c r="L778" s="3"/>
       <c r="M778" s="3"/>
-      <c r="N778" s="6"/>
-      <c r="O778" s="6"/>
-      <c r="P778" s="6"/>
-      <c r="Q778" s="6"/>
-      <c r="R778" s="6"/>
-      <c r="S778" s="6"/>
-      <c r="T778" s="6">
+      <c r="T778">
         <v>69</v>
       </c>
       <c r="U778" s="3" t="s">
@@ -34571,8 +34603,8 @@
       </c>
       <c r="W778" s="3"/>
     </row>
-    <row r="779" spans="1:23">
-      <c r="A779" s="6">
+    <row r="779" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A779">
         <v>785</v>
       </c>
       <c r="B779" s="4">
@@ -34596,20 +34628,12 @@
       <c r="H779" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I779" s="6"/>
-      <c r="J779" s="6" t="s">
+      <c r="J779" t="s">
         <v>1135</v>
       </c>
-      <c r="K779" s="6"/>
       <c r="L779" s="3"/>
       <c r="M779" s="3"/>
-      <c r="N779" s="6"/>
-      <c r="O779" s="6"/>
-      <c r="P779" s="6"/>
-      <c r="Q779" s="6"/>
-      <c r="R779" s="6"/>
-      <c r="S779" s="6"/>
-      <c r="T779" s="6">
+      <c r="T779">
         <v>45</v>
       </c>
       <c r="U779" s="3" t="s">
@@ -34620,8 +34644,8 @@
       </c>
       <c r="W779" s="3"/>
     </row>
-    <row r="780" spans="1:23">
-      <c r="A780" s="6">
+    <row r="780" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A780">
         <v>786</v>
       </c>
       <c r="B780" s="4">
@@ -34645,20 +34669,12 @@
       <c r="H780" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="I780" s="6"/>
-      <c r="J780" s="6"/>
-      <c r="K780" s="6" t="s">
+      <c r="K780" t="s">
         <v>1090</v>
       </c>
       <c r="L780" s="3"/>
       <c r="M780" s="3"/>
-      <c r="N780" s="6"/>
-      <c r="O780" s="6"/>
-      <c r="P780" s="6"/>
-      <c r="Q780" s="6"/>
-      <c r="R780" s="6"/>
-      <c r="S780" s="6"/>
-      <c r="T780" s="6">
+      <c r="T780">
         <v>20</v>
       </c>
       <c r="U780" s="3" t="s">
@@ -34668,6 +34684,644 @@
         <v>308</v>
       </c>
       <c r="W780" s="3"/>
+    </row>
+    <row r="781" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A781">
+        <v>787</v>
+      </c>
+      <c r="B781" s="4">
+        <v>46210.449675925898</v>
+      </c>
+      <c r="C781" s="4">
+        <v>46210.449907407397</v>
+      </c>
+      <c r="D781" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E781" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G781" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H781" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I781" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L781" s="3"/>
+      <c r="M781" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U781" s="3"/>
+      <c r="V781" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W781" s="3"/>
+    </row>
+    <row r="782" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A782">
+        <v>788</v>
+      </c>
+      <c r="B782" s="4">
+        <v>46211.443310185197</v>
+      </c>
+      <c r="C782" s="4">
+        <v>46211.443460648203</v>
+      </c>
+      <c r="D782" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E782" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G782" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H782" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I782" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L782" s="3"/>
+      <c r="M782" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="U782" s="3"/>
+      <c r="V782" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W782" s="3"/>
+    </row>
+    <row r="783" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A783">
+        <v>789</v>
+      </c>
+      <c r="B783" s="4">
+        <v>46211.4758449074</v>
+      </c>
+      <c r="C783" s="4">
+        <v>46211.475937499999</v>
+      </c>
+      <c r="D783" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E783" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G783" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H783" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J783" t="s">
+        <v>914</v>
+      </c>
+      <c r="L783" s="3"/>
+      <c r="M783" s="3"/>
+      <c r="T783">
+        <v>1</v>
+      </c>
+      <c r="U783" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="V783" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="W783" s="3"/>
+    </row>
+    <row r="784" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A784">
+        <v>790</v>
+      </c>
+      <c r="B784" s="4">
+        <v>46211.614560185197</v>
+      </c>
+      <c r="C784" s="4">
+        <v>46211.614641203698</v>
+      </c>
+      <c r="D784" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E784" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G784" s="1">
+        <v>46163</v>
+      </c>
+      <c r="H784" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J784" t="s">
+        <v>914</v>
+      </c>
+      <c r="L784" s="3"/>
+      <c r="M784" s="3"/>
+      <c r="T784">
+        <v>3</v>
+      </c>
+      <c r="U784" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="V784" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="W784" s="3"/>
+    </row>
+    <row r="785" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A785">
+        <v>791</v>
+      </c>
+      <c r="B785" s="4">
+        <v>46211.614664351902</v>
+      </c>
+      <c r="C785" s="4">
+        <v>46211.615023148101</v>
+      </c>
+      <c r="D785" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E785" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G785" s="1">
+        <v>46163</v>
+      </c>
+      <c r="H785" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J785" t="s">
+        <v>914</v>
+      </c>
+      <c r="L785" s="3"/>
+      <c r="M785" s="3"/>
+      <c r="T785">
+        <v>1</v>
+      </c>
+      <c r="U785" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="V785" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="W785" s="3"/>
+    </row>
+    <row r="786" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A786">
+        <v>792</v>
+      </c>
+      <c r="B786" s="4">
+        <v>46212.433009259301</v>
+      </c>
+      <c r="C786" s="4">
+        <v>46212.433078703703</v>
+      </c>
+      <c r="D786" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E786" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F786" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G786" s="1">
+        <v>46184</v>
+      </c>
+      <c r="H786" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="K786" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L786" s="3"/>
+      <c r="M786" s="3"/>
+      <c r="T786">
+        <v>2</v>
+      </c>
+      <c r="U786" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="V786" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="W786" s="3"/>
+    </row>
+    <row r="787" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A787">
+        <v>793</v>
+      </c>
+      <c r="B787" s="4">
+        <v>46212.433113425897</v>
+      </c>
+      <c r="C787" s="4">
+        <v>46212.434525463003</v>
+      </c>
+      <c r="D787" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E787" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F787" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G787" s="1">
+        <v>46190</v>
+      </c>
+      <c r="H787" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J787" t="s">
+        <v>967</v>
+      </c>
+      <c r="L787" s="3"/>
+      <c r="M787" s="3"/>
+      <c r="T787">
+        <v>50</v>
+      </c>
+      <c r="U787" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="V787" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="W787" s="3"/>
+    </row>
+    <row r="788" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A788">
+        <v>794</v>
+      </c>
+      <c r="B788" s="4">
+        <v>46212.434548611098</v>
+      </c>
+      <c r="C788" s="4">
+        <v>46212.436967592599</v>
+      </c>
+      <c r="D788" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E788" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F788" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G788" s="1">
+        <v>46196</v>
+      </c>
+      <c r="H788" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L788" s="3"/>
+      <c r="M788" s="3"/>
+      <c r="O788">
+        <v>1</v>
+      </c>
+      <c r="P788">
+        <v>0</v>
+      </c>
+      <c r="Q788">
+        <v>0</v>
+      </c>
+      <c r="R788">
+        <v>0</v>
+      </c>
+      <c r="T788">
+        <v>1</v>
+      </c>
+      <c r="U788" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V788" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="W788" s="3"/>
+    </row>
+    <row r="789" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A789">
+        <v>795</v>
+      </c>
+      <c r="B789" s="4">
+        <v>46212.5565740741</v>
+      </c>
+      <c r="C789" s="4">
+        <v>46212.557638888902</v>
+      </c>
+      <c r="D789" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E789" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F789" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G789" s="1">
+        <v>46212</v>
+      </c>
+      <c r="H789" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I789" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L789" s="3"/>
+      <c r="M789" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="U789" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="V789" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="W789" s="3"/>
+    </row>
+    <row r="790" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A790">
+        <v>796</v>
+      </c>
+      <c r="B790" s="4">
+        <v>46213.306990740697</v>
+      </c>
+      <c r="C790" s="4">
+        <v>46213.307349536997</v>
+      </c>
+      <c r="D790" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E790" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G790" s="1">
+        <v>46208</v>
+      </c>
+      <c r="H790" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L790" s="3"/>
+      <c r="M790" s="3"/>
+      <c r="O790">
+        <v>2</v>
+      </c>
+      <c r="P790">
+        <v>0</v>
+      </c>
+      <c r="Q790">
+        <v>0</v>
+      </c>
+      <c r="R790">
+        <v>0</v>
+      </c>
+      <c r="T790">
+        <v>1</v>
+      </c>
+      <c r="U790" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="V790" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="W790" s="3"/>
+    </row>
+    <row r="791" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A791">
+        <v>797</v>
+      </c>
+      <c r="B791" s="4">
+        <v>46213.608981481499</v>
+      </c>
+      <c r="C791" s="4">
+        <v>46213.610520833303</v>
+      </c>
+      <c r="D791" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E791" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G791" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H791" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J791" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L791" s="3"/>
+      <c r="M791" s="3"/>
+      <c r="T791">
+        <v>1</v>
+      </c>
+      <c r="U791" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="V791" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W791" s="3"/>
+    </row>
+    <row r="792" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A792">
+        <v>798</v>
+      </c>
+      <c r="B792" s="4">
+        <v>46216.599259259303</v>
+      </c>
+      <c r="C792" s="4">
+        <v>46216.599826388898</v>
+      </c>
+      <c r="D792" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E792" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G792" s="1">
+        <v>46216</v>
+      </c>
+      <c r="H792" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="L792" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="M792" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="U792" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="V792" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W792" s="3"/>
+    </row>
+    <row r="793" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A793">
+        <v>799</v>
+      </c>
+      <c r="B793" s="4">
+        <v>46220.382569444402</v>
+      </c>
+      <c r="C793" s="4">
+        <v>46220.383379629602</v>
+      </c>
+      <c r="D793" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E793" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G793" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H793" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J793" t="s">
+        <v>910</v>
+      </c>
+      <c r="L793" s="3"/>
+      <c r="M793" s="3"/>
+      <c r="T793">
+        <v>25</v>
+      </c>
+      <c r="U793" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="V793" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="W793" s="3"/>
+    </row>
+    <row r="794" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A794" s="6">
+        <v>800</v>
+      </c>
+      <c r="B794" s="4">
+        <v>46223.593622685199</v>
+      </c>
+      <c r="C794" s="4">
+        <v>46223.5938425926</v>
+      </c>
+      <c r="D794" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E794" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G794" s="1">
+        <v>46222</v>
+      </c>
+      <c r="H794" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="I794" s="6"/>
+      <c r="J794" s="6"/>
+      <c r="K794" s="6"/>
+      <c r="L794" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="M794" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="N794" s="6"/>
+      <c r="O794" s="6"/>
+      <c r="P794" s="6"/>
+      <c r="Q794" s="6"/>
+      <c r="R794" s="6"/>
+      <c r="S794" s="6"/>
+      <c r="T794" s="6"/>
+      <c r="U794" s="3"/>
+      <c r="V794" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="W794" s="3"/>
+    </row>
+    <row r="795" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A795" s="6">
+        <v>801</v>
+      </c>
+      <c r="B795" s="4">
+        <v>46223.595972222203</v>
+      </c>
+      <c r="C795" s="4">
+        <v>46223.596574074101</v>
+      </c>
+      <c r="D795" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E795" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G795" s="1">
+        <v>46211</v>
+      </c>
+      <c r="H795" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="I795" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="J795" s="6"/>
+      <c r="K795" s="6"/>
+      <c r="L795" s="3"/>
+      <c r="M795" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="N795" s="6"/>
+      <c r="O795" s="6"/>
+      <c r="P795" s="6"/>
+      <c r="Q795" s="6"/>
+      <c r="R795" s="6"/>
+      <c r="S795" s="6"/>
+      <c r="T795" s="6"/>
+      <c r="U795" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="V795" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="W795" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
